--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F30288B-CD25-4283-BF24-AF52BFDD2B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3556C131-9DDB-4269-80AB-AC6A3B21DED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="598">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1707,6 +1707,114 @@
   </si>
   <si>
     <t>PhotoMeter Board Repairs And Service- Qty 2 Nos. baba</t>
+  </si>
+  <si>
+    <t>Semi Auto Analyazer</t>
+  </si>
+  <si>
+    <t>BioSystem</t>
+  </si>
+  <si>
+    <t>Lens- Qty 1 Pcs</t>
+  </si>
+  <si>
+    <t>Reagent- 2 Box</t>
+  </si>
+  <si>
+    <t>AM/PP/0017/2627</t>
+  </si>
+  <si>
+    <t>Scorpion Express</t>
+  </si>
+  <si>
+    <t>8 ML Rapid System Brown Bottle With Brown Caps- 15x 1000</t>
+  </si>
+  <si>
+    <t>20 ML Rapid System Yellow Bottle With Blue Caps-10x 1000</t>
+  </si>
+  <si>
+    <t>20 ML Rapid System Natural/ Trans Bottle With White Caps-25x 1000</t>
+  </si>
+  <si>
+    <t>25 ML HDPE Brown Bottle With Brown Caps- 12x800 &amp; 1X400</t>
+  </si>
+  <si>
+    <t>50 ML HDPE Natural/ Trans Bottle With Blue Caps- 70x500</t>
+  </si>
+  <si>
+    <t>133 Box</t>
+  </si>
+  <si>
+    <t>White Cement And Liquid (Lamp)</t>
+  </si>
+  <si>
+    <t>Sure Health Invoices (  Nos.)</t>
+  </si>
+  <si>
+    <t>Drics Tech EMSLLP</t>
+  </si>
+  <si>
+    <t>D FLIP FLOP Single 3.5NS TSSOP-5 CP, Brand NEXPERIA, MPN: 74AHC1G79GW 125- Qty 600 Nos.</t>
+  </si>
+  <si>
+    <t>Photometer Programming Tools- Qty 1 Pcs / Main Board Programming Tools -Qty 1 Pcs.</t>
+  </si>
+  <si>
+    <t>Driver Board-2 Pcs / Photometer Board - 1 pcs. / Printer Board 1 Pcs. / NanoPi Board 1 Pcs</t>
+  </si>
+  <si>
+    <t>Communication Cable - 1 Pcs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maruti </t>
+  </si>
+  <si>
+    <t>G4 Lamp Holder- 2 Pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10 July 206</t>
+  </si>
+  <si>
+    <t>240-FAA- Main Board-1 Pcs / RTC Board 1 Pcs / D Soldering Copper Wire - 1Pcs / Solder Flux -1 Pcs./ IC-DDC 112Y- 1 Pcs</t>
+  </si>
+  <si>
+    <t>Printer Cover- qty 15 Pcs.</t>
+  </si>
+  <si>
+    <t>AM/PP/019/2627</t>
+  </si>
+  <si>
+    <t>Lamp Assembly (Elab) 6V/ 10W- Qty 10 Nos.</t>
+  </si>
+  <si>
+    <t>AM/DOM/0006/2627</t>
+  </si>
+  <si>
+    <t>ReDi120 Repairs Servicing -Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>1 Wodden Box</t>
+  </si>
+  <si>
+    <t>100/ 2627</t>
+  </si>
+  <si>
+    <t>133 Boxes</t>
+  </si>
+  <si>
+    <t>Challan 52</t>
+  </si>
+  <si>
+    <t>SS/ms Tanks &amp; Boxes Articles</t>
+  </si>
+  <si>
+    <t>AWB370418864304</t>
+  </si>
+  <si>
+    <t>Homenique</t>
+  </si>
+  <si>
+    <t>LIGHT BULB SOCKET- Qty 20 Pcs.</t>
   </si>
 </sst>
 </file>
@@ -6391,86 +6499,166 @@
       </c>
     </row>
     <row r="160" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C160" s="49"/>
-      <c r="F160" s="49"/>
-      <c r="H160" s="36"/>
-    </row>
-    <row r="161" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A160" s="22">
+        <v>118</v>
+      </c>
+      <c r="B160" s="26">
+        <v>46203</v>
+      </c>
+      <c r="C160" s="49" t="s">
+        <v>591</v>
+      </c>
+      <c r="D160" s="26">
+        <v>46198</v>
+      </c>
+      <c r="E160" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F160" s="49" t="s">
+        <v>220</v>
+      </c>
+      <c r="G160" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="H160" s="29" t="s">
+        <v>568</v>
+      </c>
+      <c r="I160" s="22" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C161" s="49"/>
       <c r="F161" s="49"/>
-      <c r="H161" s="36"/>
-    </row>
-    <row r="162" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="H161" s="29" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C162" s="49"/>
       <c r="F162" s="49"/>
-      <c r="H162" s="36"/>
-    </row>
-    <row r="163" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="H162" s="29" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C163" s="49"/>
       <c r="F163" s="49"/>
-      <c r="H163" s="36"/>
-    </row>
-    <row r="164" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="H163" s="29" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C164" s="49"/>
       <c r="F164" s="49"/>
-      <c r="H164" s="36"/>
-    </row>
-    <row r="165" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C165" s="49"/>
-      <c r="F165" s="49"/>
-      <c r="H165" s="36"/>
-    </row>
-    <row r="166" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C166" s="49"/>
-      <c r="F166" s="49"/>
-      <c r="H166" s="36"/>
-    </row>
-    <row r="167" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="H164" s="29" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A165" s="22">
+        <v>119</v>
+      </c>
+      <c r="B165" s="26">
+        <v>46203</v>
+      </c>
+      <c r="C165" s="49" t="s">
+        <v>593</v>
+      </c>
+      <c r="D165" s="26">
+        <v>46199</v>
+      </c>
+      <c r="E165" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F165" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="G165" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="H165" s="36" t="s">
+        <v>594</v>
+      </c>
+      <c r="I165" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A166" s="22">
+        <v>120</v>
+      </c>
+      <c r="B166" s="26">
+        <v>46204</v>
+      </c>
+      <c r="C166" s="49" t="s">
+        <v>595</v>
+      </c>
+      <c r="D166" s="26">
+        <v>46200</v>
+      </c>
+      <c r="E166" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F166" s="49" t="s">
+        <v>596</v>
+      </c>
+      <c r="G166" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H166" s="36" t="s">
+        <v>597</v>
+      </c>
+      <c r="I166" s="22" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C167" s="49"/>
       <c r="F167" s="49"/>
       <c r="H167" s="36"/>
     </row>
-    <row r="168" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="168" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C168" s="49"/>
       <c r="F168" s="49"/>
       <c r="H168" s="36"/>
     </row>
-    <row r="169" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="169" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C169" s="49"/>
       <c r="F169" s="49"/>
       <c r="H169" s="36"/>
     </row>
-    <row r="170" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="170" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C170" s="49"/>
       <c r="F170" s="49"/>
       <c r="H170" s="36"/>
     </row>
-    <row r="171" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="171" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C171" s="49"/>
       <c r="F171" s="49"/>
       <c r="H171" s="36"/>
     </row>
-    <row r="172" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="172" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C172" s="49"/>
       <c r="F172" s="49"/>
       <c r="H172" s="36"/>
     </row>
-    <row r="173" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="173" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C173" s="49"/>
       <c r="F173" s="49"/>
       <c r="H173" s="36"/>
     </row>
-    <row r="174" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="174" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C174" s="49"/>
       <c r="F174" s="49"/>
       <c r="H174" s="36"/>
     </row>
-    <row r="175" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="175" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C175" s="49"/>
       <c r="F175" s="49"/>
       <c r="H175" s="36"/>
     </row>
-    <row r="176" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="176" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C176" s="49"/>
       <c r="F176" s="49"/>
       <c r="H176" s="36"/>
@@ -10529,13 +10717,13 @@
   <cols>
     <col min="1" max="1" width="8.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.625" style="38" customWidth="1"/>
-    <col min="3" max="3" width="21.125" style="64" customWidth="1"/>
+    <col min="3" max="3" width="22" style="64" customWidth="1"/>
     <col min="4" max="4" width="15.25" style="38" customWidth="1"/>
     <col min="5" max="5" width="17.75" style="2" customWidth="1"/>
     <col min="6" max="6" width="48.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.625" style="38" customWidth="1"/>
     <col min="8" max="8" width="24" style="38" customWidth="1"/>
-    <col min="9" max="9" width="119.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="122.5" style="2" customWidth="1"/>
     <col min="10" max="11" width="14.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="19.25" style="2" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="20" style="2" hidden="1" customWidth="1"/>
@@ -12683,157 +12871,473 @@
       <c r="A77" s="27">
         <v>59</v>
       </c>
-      <c r="B77" s="45"/>
-      <c r="D77" s="45"/>
-      <c r="G77" s="45"/>
-      <c r="H77" s="45"/>
-      <c r="I77" s="29"/>
+      <c r="B77" s="55">
+        <v>46197</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D77" s="55">
+        <v>46197</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G77" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H77" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I77" s="29" t="s">
+        <v>562</v>
+      </c>
+      <c r="J77" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="78" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A78" s="27"/>
-      <c r="B78" s="45"/>
-      <c r="D78" s="45"/>
-      <c r="G78" s="45"/>
-      <c r="H78" s="45"/>
-      <c r="I78" s="29"/>
+      <c r="A78" s="27">
+        <v>60</v>
+      </c>
+      <c r="B78" s="55">
+        <v>46200</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D78" s="55">
+        <v>46200</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="G78" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H78" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="I78" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="J78" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="79" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A79" s="27"/>
-      <c r="B79" s="45"/>
-      <c r="D79" s="45"/>
-      <c r="G79" s="45"/>
-      <c r="H79" s="45"/>
-      <c r="I79" s="29"/>
+      <c r="A79" s="27">
+        <v>61</v>
+      </c>
+      <c r="B79" s="55">
+        <v>46200</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D79" s="55">
+        <v>46200</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G79" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H79" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" s="29" t="s">
+        <v>565</v>
+      </c>
+      <c r="J79" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="80" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A80" s="27"/>
-      <c r="B80" s="45"/>
-      <c r="D80" s="45"/>
-      <c r="G80" s="45"/>
-      <c r="H80" s="45"/>
-      <c r="I80" s="29"/>
-    </row>
-    <row r="81" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A80" s="27">
+        <v>62</v>
+      </c>
+      <c r="B80" s="55">
+        <v>46200</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="D80" s="55">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G80" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H80" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I80" s="29" t="s">
+        <v>568</v>
+      </c>
+      <c r="J80" s="10" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A81" s="27"/>
       <c r="B81" s="45"/>
       <c r="D81" s="45"/>
       <c r="G81" s="45"/>
       <c r="H81" s="45"/>
-      <c r="I81" s="29"/>
-    </row>
-    <row r="82" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="I81" s="29" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A82" s="27"/>
       <c r="B82" s="45"/>
       <c r="D82" s="45"/>
       <c r="G82" s="45"/>
       <c r="H82" s="45"/>
-      <c r="I82" s="29"/>
-    </row>
-    <row r="83" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="I82" s="29" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A83" s="27"/>
       <c r="B83" s="45"/>
       <c r="D83" s="45"/>
       <c r="G83" s="45"/>
       <c r="H83" s="45"/>
-      <c r="I83" s="29"/>
-    </row>
-    <row r="84" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="I83" s="29" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A84" s="27"/>
       <c r="B84" s="45"/>
       <c r="D84" s="45"/>
       <c r="G84" s="45"/>
       <c r="H84" s="45"/>
-      <c r="I84" s="29"/>
-    </row>
-    <row r="85" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A85" s="27"/>
-      <c r="B85" s="45"/>
-      <c r="D85" s="45"/>
-      <c r="G85" s="45"/>
-      <c r="H85" s="45"/>
-      <c r="I85" s="29"/>
-    </row>
-    <row r="86" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="I84" s="29" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A85" s="27">
+        <v>63</v>
+      </c>
+      <c r="B85" s="55">
+        <v>46204</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D85" s="55">
+        <v>46204</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G85" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H85" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="I85" s="29" t="s">
+        <v>574</v>
+      </c>
+      <c r="J85" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A86" s="27"/>
       <c r="B86" s="45"/>
       <c r="D86" s="45"/>
       <c r="G86" s="45"/>
       <c r="H86" s="45"/>
-      <c r="I86" s="29"/>
-    </row>
-    <row r="87" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A87" s="27"/>
-      <c r="B87" s="45"/>
-      <c r="D87" s="45"/>
-      <c r="G87" s="45"/>
-      <c r="H87" s="45"/>
-      <c r="I87" s="29"/>
-    </row>
-    <row r="88" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="I86" s="29" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A87" s="27">
+        <v>64</v>
+      </c>
+      <c r="B87" s="55">
+        <v>46210</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D87" s="55">
+        <v>46210</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G87" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H87" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I87" s="29" t="s">
+        <v>579</v>
+      </c>
+      <c r="J87" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A88" s="27"/>
-      <c r="B88" s="45"/>
-      <c r="D88" s="45"/>
+      <c r="B88" s="55"/>
+      <c r="D88" s="55"/>
       <c r="G88" s="45"/>
       <c r="H88" s="45"/>
-      <c r="I88" s="29"/>
-    </row>
-    <row r="89" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A89" s="27"/>
-      <c r="B89" s="45"/>
-      <c r="D89" s="45"/>
-      <c r="G89" s="45"/>
-      <c r="H89" s="45"/>
-      <c r="I89" s="29"/>
-    </row>
-    <row r="90" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A90" s="27"/>
-      <c r="B90" s="45"/>
-      <c r="D90" s="45"/>
-      <c r="G90" s="45"/>
-      <c r="H90" s="45"/>
-      <c r="I90" s="29"/>
-    </row>
-    <row r="91" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A91" s="27"/>
-      <c r="B91" s="45"/>
-      <c r="D91" s="45"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
-      <c r="I91" s="29"/>
-    </row>
-    <row r="92" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A92" s="27"/>
-      <c r="B92" s="45"/>
-      <c r="D92" s="45"/>
-      <c r="G92" s="45"/>
-      <c r="H92" s="45"/>
-      <c r="I92" s="29"/>
-    </row>
-    <row r="93" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A93" s="27"/>
-      <c r="B93" s="45"/>
-      <c r="D93" s="45"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="45"/>
-      <c r="I93" s="29"/>
-    </row>
-    <row r="94" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A94" s="27"/>
-      <c r="B94" s="45"/>
-      <c r="D94" s="45"/>
-      <c r="G94" s="45"/>
-      <c r="H94" s="45"/>
-      <c r="I94" s="29"/>
-    </row>
-    <row r="95" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A95" s="27"/>
-      <c r="B95" s="45"/>
-      <c r="D95" s="45"/>
-      <c r="G95" s="45"/>
-      <c r="H95" s="45"/>
-      <c r="I95" s="29"/>
-    </row>
-    <row r="96" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="I88" s="29" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A89" s="27">
+        <v>65</v>
+      </c>
+      <c r="B89" s="55">
+        <v>46211</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D89" s="55">
+        <v>46204</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="G89" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H89" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I89" s="29" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A90" s="27">
+        <v>66</v>
+      </c>
+      <c r="B90" s="55">
+        <v>46212</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D90" s="55">
+        <v>46212</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G90" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H90" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I90" s="29" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A91" s="27">
+        <v>67</v>
+      </c>
+      <c r="B91" s="55">
+        <v>46212</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D91" s="55">
+        <v>46212</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="G91" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H91" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I91" s="29" t="s">
+        <v>582</v>
+      </c>
+      <c r="J91" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A92" s="27">
+        <v>68</v>
+      </c>
+      <c r="B92" s="45" t="s">
+        <v>583</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D92" s="55">
+        <v>46213</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G92" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H92" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I92" s="29" t="s">
+        <v>584</v>
+      </c>
+      <c r="J92" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A93" s="27">
+        <v>69</v>
+      </c>
+      <c r="B93" s="55">
+        <v>46214</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D93" s="55">
+        <v>46214</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G93" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H93" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I93" s="29" t="s">
+        <v>585</v>
+      </c>
+      <c r="J93" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A94" s="27">
+        <v>70</v>
+      </c>
+      <c r="B94" s="55">
+        <v>46211</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="D94" s="55">
+        <v>46211</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G94" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H94" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I94" s="29" t="s">
+        <v>587</v>
+      </c>
+      <c r="J94" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A95" s="27">
+        <v>71</v>
+      </c>
+      <c r="B95" s="55">
+        <v>46206</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="D95" s="55">
+        <v>46206</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="G95" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H95" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I95" s="29" t="s">
+        <v>589</v>
+      </c>
+      <c r="J95" s="10" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A96" s="27"/>
       <c r="B96" s="45"/>
       <c r="D96" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3556C131-9DDB-4269-80AB-AC6A3B21DED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B99CA86-735A-4E92-B44C-6B567BEDFE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6614,6 +6614,9 @@
       </c>
     </row>
     <row r="167" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A167" s="22">
+        <v>121</v>
+      </c>
       <c r="C167" s="49"/>
       <c r="F167" s="49"/>
       <c r="H167" s="36"/>
@@ -13338,7 +13341,9 @@
       </c>
     </row>
     <row r="96" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A96" s="27"/>
+      <c r="A96" s="27">
+        <v>72</v>
+      </c>
       <c r="B96" s="45"/>
       <c r="D96" s="45"/>
       <c r="G96" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B99CA86-735A-4E92-B44C-6B567BEDFE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6314784-D8D3-4CFC-92DC-17D7BB5C0121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="620">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1815,6 +1815,72 @@
   </si>
   <si>
     <t>LIGHT BULB SOCKET- Qty 20 Pcs.</t>
+  </si>
+  <si>
+    <t>AWB#7X110866784</t>
+  </si>
+  <si>
+    <t>ONLSCR44976</t>
+  </si>
+  <si>
+    <t>Only Screw</t>
+  </si>
+  <si>
+    <t>Screw (M3x25mm Male to Female Brass Nickel Plating Hex Threaded - Qty 2o Pcs.</t>
+  </si>
+  <si>
+    <t>M.MESTRY Enterprises</t>
+  </si>
+  <si>
+    <t>Timing Pulley_XL63 Teeth - Qty 10 / XL_14T - Qty 15 / MXL_60T- Qty 15 / MXL_30 T- Qty 30 / MXL_15Teeth- Qty 21</t>
+  </si>
+  <si>
+    <t>INV2627/116033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC8UU 8mm Linear Bell Bearing Slide Unit CNC 3D Printer-Qty 5 Nos. / 320mm LongbChrome Plated Smooth Rod Diameter 8mm -Qty5 Nos. </t>
+  </si>
+  <si>
+    <t>Challan JP/035/26-27</t>
+  </si>
+  <si>
+    <t>Jtag with Cable - Qty 1 Nos. / HP Pen Drive 32 GB- Qty 1 Nos. / Photomeyer Programming Tool- Qty 1 Nos./ RFID Card Reader- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>PSI-2627-09023</t>
+  </si>
+  <si>
+    <t>RS Components &amp; Controls (Ind)Ltd</t>
+  </si>
+  <si>
+    <t>Igus JFM-1218-12 12 mm Bore Plain Bearing 18mm O.D- Qty 8 / Igus JSM-0608-06 6?? Bore Plain Bearing 8 O.D- Qty 20</t>
+  </si>
+  <si>
+    <t>VE/0555/2627</t>
+  </si>
+  <si>
+    <t>Volthermic Electricals</t>
+  </si>
+  <si>
+    <t>High Temprature Cement With Hardener (3816)- Qty 1 Set</t>
+  </si>
+  <si>
+    <t>Challan- 62</t>
+  </si>
+  <si>
+    <t>BioSCi HealthCare</t>
+  </si>
+  <si>
+    <t>Glucose Test Reagent-500Ml (N)- 1 Kit / Urea Test Reagent- 100Ml (N)- 5 Kit / Glycosylated Hemoglobin (HbA1c) Turbilatexreag-40Ml (N)- 1 Kit /</t>
+  </si>
+  <si>
+    <t>C- Reactiveprotein (CRP) turbilatex Testreagent-50Ml(N)-1 Kit / Alanine amino Transferase SGPT Test Reagaent- 100 Ml(N) 5 Kit</t>
+  </si>
+  <si>
+    <t>Challan -57</t>
+  </si>
+  <si>
+    <t>Photometer PCB Assembly -Qty 1 Set</t>
   </si>
 </sst>
 </file>
@@ -6617,131 +6683,367 @@
       <c r="A167" s="22">
         <v>121</v>
       </c>
-      <c r="C167" s="49"/>
-      <c r="F167" s="49"/>
-      <c r="H167" s="36"/>
+      <c r="B167" s="26">
+        <v>46206</v>
+      </c>
+      <c r="C167" s="49" t="s">
+        <v>598</v>
+      </c>
+      <c r="D167" s="26">
+        <v>46204</v>
+      </c>
+      <c r="E167" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F167" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G167" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="H167" s="29" t="s">
+        <v>587</v>
+      </c>
+      <c r="I167" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="168" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C168" s="49"/>
-      <c r="F168" s="49"/>
-      <c r="H168" s="36"/>
+      <c r="A168" s="22">
+        <v>122</v>
+      </c>
+      <c r="B168" s="26">
+        <v>46206</v>
+      </c>
+      <c r="C168" s="49" t="s">
+        <v>599</v>
+      </c>
+      <c r="D168" s="26">
+        <v>46204</v>
+      </c>
+      <c r="E168" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F168" s="49" t="s">
+        <v>600</v>
+      </c>
+      <c r="G168" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H168" s="36" t="s">
+        <v>601</v>
+      </c>
+      <c r="I168" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="169" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C169" s="49"/>
-      <c r="F169" s="49"/>
-      <c r="H169" s="36"/>
+      <c r="A169" s="22">
+        <v>123</v>
+      </c>
+      <c r="B169" s="26">
+        <v>46209</v>
+      </c>
+      <c r="C169" s="49">
+        <v>123</v>
+      </c>
+      <c r="D169" s="26">
+        <v>46203</v>
+      </c>
+      <c r="E169" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F169" s="49" t="s">
+        <v>602</v>
+      </c>
+      <c r="G169" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H169" s="36" t="s">
+        <v>603</v>
+      </c>
+      <c r="I169" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="170" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C170" s="49"/>
-      <c r="F170" s="49"/>
-      <c r="H170" s="36"/>
+      <c r="A170" s="22">
+        <v>124</v>
+      </c>
+      <c r="B170" s="26">
+        <v>46206</v>
+      </c>
+      <c r="C170" s="49" t="s">
+        <v>604</v>
+      </c>
+      <c r="D170" s="26">
+        <v>46199</v>
+      </c>
+      <c r="E170" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F170" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="G170" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="H170" s="36" t="s">
+        <v>605</v>
+      </c>
+      <c r="I170" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="171" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C171" s="49"/>
-      <c r="F171" s="49"/>
-      <c r="H171" s="36"/>
+      <c r="A171" s="22">
+        <v>125</v>
+      </c>
+      <c r="B171" s="26">
+        <v>46206</v>
+      </c>
+      <c r="C171" s="49" t="s">
+        <v>606</v>
+      </c>
+      <c r="D171" s="26">
+        <v>46203</v>
+      </c>
+      <c r="E171" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F171" s="49" t="s">
+        <v>354</v>
+      </c>
+      <c r="G171" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H171" s="36" t="s">
+        <v>607</v>
+      </c>
+      <c r="I171" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="172" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C172" s="49"/>
-      <c r="F172" s="49"/>
-      <c r="H172" s="36"/>
+      <c r="A172" s="22">
+        <v>126</v>
+      </c>
+      <c r="B172" s="26">
+        <v>46210</v>
+      </c>
+      <c r="C172" s="49">
+        <v>1089164</v>
+      </c>
+      <c r="D172" s="26">
+        <v>46209</v>
+      </c>
+      <c r="E172" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F172" s="49" t="s">
+        <v>479</v>
+      </c>
+      <c r="G172" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H172" s="29" t="s">
+        <v>577</v>
+      </c>
+      <c r="I172" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="173" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C173" s="49"/>
-      <c r="F173" s="49"/>
-      <c r="H173" s="36"/>
+      <c r="A173" s="22">
+        <v>127</v>
+      </c>
+      <c r="B173" s="26">
+        <v>46210</v>
+      </c>
+      <c r="C173" s="49" t="s">
+        <v>608</v>
+      </c>
+      <c r="D173" s="26">
+        <v>46206</v>
+      </c>
+      <c r="F173" s="49" t="s">
+        <v>609</v>
+      </c>
+      <c r="G173" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H173" s="36" t="s">
+        <v>610</v>
+      </c>
+      <c r="I173" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="174" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C174" s="49"/>
-      <c r="F174" s="49"/>
-      <c r="H174" s="36"/>
+      <c r="A174" s="22">
+        <v>128</v>
+      </c>
+      <c r="B174" s="26">
+        <v>46213</v>
+      </c>
+      <c r="C174" s="49" t="s">
+        <v>611</v>
+      </c>
+      <c r="D174" s="26">
+        <v>46212</v>
+      </c>
+      <c r="E174" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F174" s="49" t="s">
+        <v>612</v>
+      </c>
+      <c r="G174" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H174" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="I174" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="175" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C175" s="49"/>
-      <c r="F175" s="49"/>
-      <c r="H175" s="36"/>
+      <c r="A175" s="22">
+        <v>129</v>
+      </c>
+      <c r="B175" s="26">
+        <v>46217</v>
+      </c>
+      <c r="C175" s="49" t="s">
+        <v>614</v>
+      </c>
+      <c r="D175" s="58">
+        <v>46210</v>
+      </c>
+      <c r="E175" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F175" s="49" t="s">
+        <v>615</v>
+      </c>
+      <c r="G175" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H175" s="36" t="s">
+        <v>616</v>
+      </c>
+      <c r="I175" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="176" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C176" s="49"/>
       <c r="F176" s="49"/>
-      <c r="H176" s="36"/>
-    </row>
-    <row r="177" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C177" s="49"/>
-      <c r="F177" s="49"/>
-      <c r="H177" s="36"/>
-    </row>
-    <row r="178" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="H176" s="36" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A177" s="22">
+        <v>130</v>
+      </c>
+      <c r="B177" s="26">
+        <v>46217</v>
+      </c>
+      <c r="C177" s="49" t="s">
+        <v>618</v>
+      </c>
+      <c r="D177" s="26">
+        <v>46204</v>
+      </c>
+      <c r="E177" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F177" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="G177" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H177" s="36" t="s">
+        <v>619</v>
+      </c>
+      <c r="I177" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C178" s="49"/>
       <c r="F178" s="49"/>
       <c r="H178" s="36"/>
     </row>
-    <row r="179" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="179" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C179" s="49"/>
       <c r="F179" s="49"/>
       <c r="H179" s="36"/>
     </row>
-    <row r="180" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="180" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C180" s="49"/>
       <c r="F180" s="49"/>
       <c r="H180" s="36"/>
     </row>
-    <row r="181" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="181" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C181" s="49"/>
       <c r="F181" s="49"/>
       <c r="H181" s="36"/>
     </row>
-    <row r="182" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="182" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C182" s="49"/>
       <c r="F182" s="49"/>
       <c r="H182" s="36"/>
     </row>
-    <row r="183" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="183" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C183" s="49"/>
       <c r="F183" s="49"/>
       <c r="H183" s="36"/>
     </row>
-    <row r="184" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="184" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C184" s="49"/>
       <c r="F184" s="49"/>
       <c r="H184" s="36"/>
     </row>
-    <row r="185" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="185" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C185" s="49"/>
       <c r="F185" s="49"/>
       <c r="H185" s="36"/>
     </row>
-    <row r="186" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="186" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C186" s="49"/>
       <c r="F186" s="49"/>
       <c r="H186" s="36"/>
     </row>
-    <row r="187" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="187" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C187" s="49"/>
       <c r="F187" s="49"/>
       <c r="H187" s="36"/>
     </row>
-    <row r="188" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="188" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C188" s="49"/>
       <c r="F188" s="49"/>
       <c r="H188" s="36"/>
     </row>
-    <row r="189" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="189" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C189" s="49"/>
       <c r="F189" s="49"/>
       <c r="H189" s="36"/>
     </row>
-    <row r="190" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="190" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C190" s="49"/>
       <c r="F190" s="49"/>
       <c r="H190" s="36"/>
     </row>
-    <row r="191" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="191" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C191" s="49"/>
       <c r="F191" s="49"/>
       <c r="H191" s="36"/>
     </row>
-    <row r="192" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="192" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C192" s="49"/>
       <c r="F192" s="49"/>
       <c r="H192" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6314784-D8D3-4CFC-92DC-17D7BB5C0121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF38E9A5-6A36-44F6-9BC1-122753DC9D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="621">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1817,9 +1817,6 @@
     <t>LIGHT BULB SOCKET- Qty 20 Pcs.</t>
   </si>
   <si>
-    <t>AWB#7X110866784</t>
-  </si>
-  <si>
     <t>ONLSCR44976</t>
   </si>
   <si>
@@ -1881,6 +1878,12 @@
   </si>
   <si>
     <t>Photometer PCB Assembly -Qty 1 Set</t>
+  </si>
+  <si>
+    <t>GST/2026-27/183</t>
+  </si>
+  <si>
+    <t>BioSci Health(Sourabh Panthi)</t>
   </si>
 </sst>
 </file>
@@ -6687,7 +6690,7 @@
         <v>46206</v>
       </c>
       <c r="C167" s="49" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="D167" s="26">
         <v>46204</v>
@@ -6716,7 +6719,7 @@
         <v>46206</v>
       </c>
       <c r="C168" s="49" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D168" s="26">
         <v>46204</v>
@@ -6725,13 +6728,13 @@
         <v>67</v>
       </c>
       <c r="F168" s="49" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G168" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H168" s="36" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="I168" s="22" t="s">
         <v>50</v>
@@ -6754,13 +6757,13 @@
         <v>37</v>
       </c>
       <c r="F169" s="49" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G169" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H169" s="36" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I169" s="22" t="s">
         <v>50</v>
@@ -6774,7 +6777,7 @@
         <v>46206</v>
       </c>
       <c r="C170" s="49" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D170" s="26">
         <v>46199</v>
@@ -6789,7 +6792,7 @@
         <v>86</v>
       </c>
       <c r="H170" s="36" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I170" s="22" t="s">
         <v>50</v>
@@ -6803,7 +6806,7 @@
         <v>46206</v>
       </c>
       <c r="C171" s="49" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D171" s="26">
         <v>46203</v>
@@ -6818,7 +6821,7 @@
         <v>45</v>
       </c>
       <c r="H171" s="36" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I171" s="22" t="s">
         <v>50</v>
@@ -6861,19 +6864,19 @@
         <v>46210</v>
       </c>
       <c r="C173" s="49" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D173" s="26">
         <v>46206</v>
       </c>
       <c r="F173" s="49" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G173" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H173" s="36" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I173" s="22" t="s">
         <v>50</v>
@@ -6887,7 +6890,7 @@
         <v>46213</v>
       </c>
       <c r="C174" s="49" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D174" s="26">
         <v>46212</v>
@@ -6896,13 +6899,13 @@
         <v>252</v>
       </c>
       <c r="F174" s="49" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G174" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="36" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I174" s="22" t="s">
         <v>50</v>
@@ -6916,7 +6919,7 @@
         <v>46217</v>
       </c>
       <c r="C175" s="49" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D175" s="58">
         <v>46210</v>
@@ -6925,13 +6928,13 @@
         <v>56</v>
       </c>
       <c r="F175" s="49" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G175" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H175" s="36" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I175" s="22" t="s">
         <v>50</v>
@@ -6941,7 +6944,7 @@
       <c r="C176" s="49"/>
       <c r="F176" s="49"/>
       <c r="H176" s="36" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="177" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6952,7 +6955,7 @@
         <v>46217</v>
       </c>
       <c r="C177" s="49" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D177" s="26">
         <v>46204</v>
@@ -6967,16 +6970,40 @@
         <v>45</v>
       </c>
       <c r="H177" s="36" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I177" s="22" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="178" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C178" s="49"/>
-      <c r="F178" s="49"/>
-      <c r="H178" s="36"/>
+      <c r="A178" s="22">
+        <v>131</v>
+      </c>
+      <c r="B178" s="26">
+        <v>46218</v>
+      </c>
+      <c r="C178" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D178" s="26">
+        <v>46218</v>
+      </c>
+      <c r="E178" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F178" s="49" t="s">
+        <v>620</v>
+      </c>
+      <c r="G178" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H178" s="36" t="s">
+        <v>480</v>
+      </c>
+      <c r="I178" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="179" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C179" s="49"/>
@@ -13646,14 +13673,35 @@
       <c r="A96" s="27">
         <v>72</v>
       </c>
-      <c r="B96" s="45"/>
-      <c r="D96" s="45"/>
-      <c r="G96" s="45"/>
-      <c r="H96" s="45"/>
-      <c r="I96" s="29"/>
+      <c r="B96" s="55">
+        <v>46218</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D96" s="55">
+        <v>46218</v>
+      </c>
+      <c r="F96" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G96" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H96" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I96" s="29" t="s">
+        <v>587</v>
+      </c>
+      <c r="J96" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="97" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A97" s="27"/>
+      <c r="A97" s="27">
+        <v>73</v>
+      </c>
       <c r="B97" s="45"/>
       <c r="D97" s="45"/>
       <c r="G97" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF38E9A5-6A36-44F6-9BC1-122753DC9D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFEDCFD-A801-49EA-9097-3DF8C29FF2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="621">
   <si>
     <t>Sr No.</t>
   </si>
@@ -13674,13 +13674,16 @@
         <v>72</v>
       </c>
       <c r="B96" s="55">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D96" s="55">
-        <v>46218</v>
+        <v>46219</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="F96" s="49" t="s">
         <v>83</v>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFEDCFD-A801-49EA-9097-3DF8C29FF2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C07479-D12A-4A05-8093-8B31195A5435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="623">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1884,6 +1884,12 @@
   </si>
   <si>
     <t>BioSci Health(Sourabh Panthi)</t>
+  </si>
+  <si>
+    <t>BioSci HeathCare</t>
+  </si>
+  <si>
+    <t>BioSci 50 Neu Analayser / PowerCoad/ Flowcell/ Adaptor -Qty 1 Nos Each</t>
   </si>
 </sst>
 </file>
@@ -7006,9 +7012,30 @@
       </c>
     </row>
     <row r="179" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C179" s="49"/>
-      <c r="F179" s="49"/>
-      <c r="H179" s="36"/>
+      <c r="A179" s="22">
+        <v>132</v>
+      </c>
+      <c r="B179" s="26">
+        <v>46220</v>
+      </c>
+      <c r="C179" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D179" s="26">
+        <v>46220</v>
+      </c>
+      <c r="F179" s="49" t="s">
+        <v>621</v>
+      </c>
+      <c r="G179" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H179" s="36" t="s">
+        <v>622</v>
+      </c>
+      <c r="I179" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="180" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C180" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C07479-D12A-4A05-8093-8B31195A5435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B800B0-FAD9-4078-8D42-3FEC75AC8AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B800B0-FAD9-4078-8D42-3FEC75AC8AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2887DBBA-D9ED-46F6-A96C-28497CD2FB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="627">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1890,6 +1890,18 @@
   </si>
   <si>
     <t>BioSci 50 Neu Analayser / PowerCoad/ Flowcell/ Adaptor -Qty 1 Nos Each</t>
+  </si>
+  <si>
+    <t>DC0069</t>
+  </si>
+  <si>
+    <t>50 SAA Instrument (6V Lamp)-Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Sanket SIr</t>
+  </si>
+  <si>
+    <t>Molding Base Plate- Qty 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -13728,25 +13740,71 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="97" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A97" s="27">
         <v>73</v>
       </c>
-      <c r="B97" s="45"/>
-      <c r="D97" s="45"/>
-      <c r="G97" s="45"/>
-      <c r="H97" s="45"/>
-      <c r="I97" s="29"/>
-    </row>
-    <row r="98" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A98" s="27"/>
-      <c r="B98" s="45"/>
-      <c r="D98" s="45"/>
-      <c r="G98" s="45"/>
-      <c r="H98" s="45"/>
-      <c r="I98" s="29"/>
-    </row>
-    <row r="99" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B97" s="55">
+        <v>46220</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="D97" s="55">
+        <v>46220</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G97" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H97" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I97" s="29" t="s">
+        <v>624</v>
+      </c>
+      <c r="J97" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A98" s="27">
+        <v>74</v>
+      </c>
+      <c r="B98" s="55">
+        <v>46220</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D98" s="55">
+        <v>46220</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G98" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H98" s="45" t="s">
+        <v>625</v>
+      </c>
+      <c r="I98" s="29" t="s">
+        <v>626</v>
+      </c>
+      <c r="J98" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A99" s="27"/>
       <c r="B99" s="45"/>
       <c r="D99" s="45"/>
@@ -13754,7 +13812,7 @@
       <c r="H99" s="45"/>
       <c r="I99" s="29"/>
     </row>
-    <row r="100" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="100" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A100" s="27"/>
       <c r="B100" s="45"/>
       <c r="D100" s="45"/>
@@ -13762,7 +13820,7 @@
       <c r="H100" s="45"/>
       <c r="I100" s="29"/>
     </row>
-    <row r="101" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="101" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A101" s="27"/>
       <c r="B101" s="45"/>
       <c r="D101" s="45"/>
@@ -13770,7 +13828,7 @@
       <c r="H101" s="45"/>
       <c r="I101" s="29"/>
     </row>
-    <row r="102" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="102" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A102" s="27"/>
       <c r="B102" s="45"/>
       <c r="D102" s="45"/>
@@ -13778,7 +13836,7 @@
       <c r="H102" s="45"/>
       <c r="I102" s="29"/>
     </row>
-    <row r="103" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="103" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A103" s="27"/>
       <c r="B103" s="45"/>
       <c r="D103" s="45"/>
@@ -13786,7 +13844,7 @@
       <c r="H103" s="45"/>
       <c r="I103" s="29"/>
     </row>
-    <row r="104" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="104" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A104" s="27"/>
       <c r="B104" s="45"/>
       <c r="D104" s="45"/>
@@ -13794,7 +13852,7 @@
       <c r="H104" s="45"/>
       <c r="I104" s="29"/>
     </row>
-    <row r="105" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="105" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A105" s="27"/>
       <c r="B105" s="45"/>
       <c r="D105" s="45"/>
@@ -13802,7 +13860,7 @@
       <c r="H105" s="45"/>
       <c r="I105" s="29"/>
     </row>
-    <row r="106" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="106" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A106" s="27"/>
       <c r="B106" s="45"/>
       <c r="D106" s="45"/>
@@ -13810,7 +13868,7 @@
       <c r="H106" s="45"/>
       <c r="I106" s="29"/>
     </row>
-    <row r="107" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="107" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A107" s="27"/>
       <c r="B107" s="45"/>
       <c r="D107" s="45"/>
@@ -13818,7 +13876,7 @@
       <c r="H107" s="45"/>
       <c r="I107" s="29"/>
     </row>
-    <row r="108" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="108" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A108" s="27"/>
       <c r="B108" s="45"/>
       <c r="D108" s="45"/>
@@ -13826,7 +13884,7 @@
       <c r="H108" s="45"/>
       <c r="I108" s="29"/>
     </row>
-    <row r="109" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="109" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A109" s="27"/>
       <c r="B109" s="45"/>
       <c r="D109" s="45"/>
@@ -13834,7 +13892,7 @@
       <c r="H109" s="45"/>
       <c r="I109" s="29"/>
     </row>
-    <row r="110" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="110" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A110" s="27"/>
       <c r="B110" s="45"/>
       <c r="D110" s="45"/>
@@ -13842,7 +13900,7 @@
       <c r="H110" s="45"/>
       <c r="I110" s="29"/>
     </row>
-    <row r="111" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="111" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="27"/>
       <c r="B111" s="45"/>
       <c r="D111" s="45"/>
@@ -13850,7 +13908,7 @@
       <c r="H111" s="45"/>
       <c r="I111" s="29"/>
     </row>
-    <row r="112" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="112" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A112" s="27"/>
       <c r="B112" s="45"/>
       <c r="D112" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2887DBBA-D9ED-46F6-A96C-28497CD2FB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8C815D-C2D1-4A88-8755-BE189BFABBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="629">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1902,6 +1902,12 @@
   </si>
   <si>
     <t>Molding Base Plate- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Molding Base Plate- Qty 4 Nos.</t>
+  </si>
+  <si>
+    <t>Mapel Mould &amp; Dies</t>
   </si>
 </sst>
 </file>
@@ -7050,11 +7056,35 @@
       </c>
     </row>
     <row r="180" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C180" s="49"/>
-      <c r="F180" s="49"/>
-      <c r="H180" s="36"/>
+      <c r="A180" s="22">
+        <v>133</v>
+      </c>
+      <c r="B180" s="26">
+        <v>46220</v>
+      </c>
+      <c r="C180" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D180" s="26">
+        <v>46220</v>
+      </c>
+      <c r="F180" s="49" t="s">
+        <v>628</v>
+      </c>
+      <c r="G180" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H180" s="36" t="s">
+        <v>627</v>
+      </c>
+      <c r="I180" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="181" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A181" s="22">
+        <v>134</v>
+      </c>
       <c r="C181" s="49"/>
       <c r="F181" s="49"/>
       <c r="H181" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8C815D-C2D1-4A88-8755-BE189BFABBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D916AFFA-BA3C-4418-990C-C23977151CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D916AFFA-BA3C-4418-990C-C23977151CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C06050-8B2E-4996-8AB2-EC9F5AD1631B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="632">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1908,6 +1908,15 @@
   </si>
   <si>
     <t>Mapel Mould &amp; Dies</t>
+  </si>
+  <si>
+    <t>challan- JP/049/26-27</t>
+  </si>
+  <si>
+    <t>JP Medical System Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Semi Automated Chemistry Analyzer -1 /RFID Card- 2 Nos. / Filter Wheel With Filters-1 Nos./ Filter 340mm-1 Nos. / Filter 405mm- 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7085,9 +7094,30 @@
       <c r="A181" s="22">
         <v>134</v>
       </c>
-      <c r="C181" s="49"/>
-      <c r="F181" s="49"/>
-      <c r="H181" s="36"/>
+      <c r="B181" s="26">
+        <v>46223</v>
+      </c>
+      <c r="C181" s="49" t="s">
+        <v>629</v>
+      </c>
+      <c r="D181" s="26">
+        <v>46219</v>
+      </c>
+      <c r="E181" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F181" s="49" t="s">
+        <v>630</v>
+      </c>
+      <c r="G181" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H181" s="36" t="s">
+        <v>631</v>
+      </c>
+      <c r="I181" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="182" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C182" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C06050-8B2E-4996-8AB2-EC9F5AD1631B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F85D85-E259-4EFF-AA07-5908A37555AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="636">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1917,6 +1917,18 @@
   </si>
   <si>
     <t>Semi Automated Chemistry Analyzer -1 /RFID Card- 2 Nos. / Filter Wheel With Filters-1 Nos./ Filter 340mm-1 Nos. / Filter 405mm- 1 Nos.</t>
+  </si>
+  <si>
+    <t>Kirit SIR</t>
+  </si>
+  <si>
+    <t>VASAI (REVERT)</t>
+  </si>
+  <si>
+    <t>BckSide Cover -Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>By Hand</t>
   </si>
 </sst>
 </file>
@@ -13865,12 +13877,32 @@
       </c>
     </row>
     <row r="99" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A99" s="27"/>
-      <c r="B99" s="45"/>
-      <c r="D99" s="45"/>
+      <c r="A99" s="27">
+        <v>75</v>
+      </c>
+      <c r="B99" s="55">
+        <v>46220</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D99" s="55">
+        <v>46220</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>633</v>
+      </c>
       <c r="G99" s="45"/>
       <c r="H99" s="45"/>
-      <c r="I99" s="29"/>
+      <c r="I99" s="29" t="s">
+        <v>634</v>
+      </c>
+      <c r="J99" s="10" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="100" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A100" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F85D85-E259-4EFF-AA07-5908A37555AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D831C3DC-4BAB-4619-A3DA-F5FC2FF9A0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D831C3DC-4BAB-4619-A3DA-F5FC2FF9A0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B72C78-7882-43D5-8875-3B1663E8B8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="645">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1929,6 +1929,33 @@
   </si>
   <si>
     <t>By Hand</t>
+  </si>
+  <si>
+    <t>Lens Housing For 10mm Lens_400- Qty 5 / Lamp Holder Mount_400- Qty 5 / Spacer For Lens - Qty 5 /  Locking Ring For Lens- Qty 5 /</t>
+  </si>
+  <si>
+    <t>Lamp Holder -Qty 5 / Hex Spacer For Photometer_400- Qty 10 / Bush For Photometer- Qty 5 / Spacer For Lens DIA 6mm- Qty 5 /</t>
+  </si>
+  <si>
+    <t>Spacer For Trough- Qty 50 / Bush For Bearing housing- Qty 15 / Lock Nut_M14-Qty 30 / Bush For Bearing Lock- Qty 15 /</t>
+  </si>
+  <si>
+    <t>Cap For Bearing Housing- Qty 5 / RGT Tray Mount HUB- Qty 10 / Guide Bush For Container- Qty 40 / Round Spacer_ RGT 400- Qty 60 /</t>
+  </si>
+  <si>
+    <t>KNOB For RGT Tray_400- Qty 10 / Center HUB Sample Tray_400- Qty 5</t>
+  </si>
+  <si>
+    <t>INV-929 (400 Materil)</t>
+  </si>
+  <si>
+    <t>INV- 930 ( Washer Material)</t>
+  </si>
+  <si>
+    <t>Base Plate For Vertical assembly_EW- Qty 5 / Vertical Plate_EW- Qty 5 / Top Plate_EW- Qty 5 / Sliding Block_EW-Qty 5 /</t>
+  </si>
+  <si>
+    <t>Guide Rod DIA 6mm_EW- Qty 10 / Idler Pully shaft_EW- Qty 5 / Idler Pully_ER- Qty 5 / Bearing Locking Pin_ER- Qtyn10</t>
   </si>
 </sst>
 </file>
@@ -7132,41 +7159,99 @@
       </c>
     </row>
     <row r="182" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C182" s="49"/>
-      <c r="F182" s="49"/>
-      <c r="H182" s="36"/>
+      <c r="A182" s="22">
+        <v>135</v>
+      </c>
+      <c r="B182" s="26">
+        <v>46223</v>
+      </c>
+      <c r="C182" s="49" t="s">
+        <v>641</v>
+      </c>
+      <c r="D182" s="26">
+        <v>46219</v>
+      </c>
+      <c r="E182" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F182" s="49" t="s">
+        <v>516</v>
+      </c>
+      <c r="G182" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H182" s="36" t="s">
+        <v>636</v>
+      </c>
+      <c r="I182" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="183" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C183" s="49"/>
       <c r="F183" s="49"/>
-      <c r="H183" s="36"/>
+      <c r="H183" s="36" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="184" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C184" s="49"/>
       <c r="F184" s="49"/>
-      <c r="H184" s="36"/>
+      <c r="H184" s="36" t="s">
+        <v>638</v>
+      </c>
     </row>
     <row r="185" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C185" s="49"/>
       <c r="F185" s="49"/>
-      <c r="H185" s="36"/>
+      <c r="H185" s="36" t="s">
+        <v>639</v>
+      </c>
     </row>
     <row r="186" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C186" s="49"/>
       <c r="F186" s="49"/>
-      <c r="H186" s="36"/>
+      <c r="H186" s="36" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="187" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C187" s="49"/>
-      <c r="F187" s="49"/>
-      <c r="H187" s="36"/>
+      <c r="A187" s="22">
+        <v>136</v>
+      </c>
+      <c r="B187" s="26">
+        <v>46223</v>
+      </c>
+      <c r="C187" s="49" t="s">
+        <v>642</v>
+      </c>
+      <c r="D187" s="26">
+        <v>46219</v>
+      </c>
+      <c r="E187" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F187" s="49" t="s">
+        <v>516</v>
+      </c>
+      <c r="G187" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H187" s="36" t="s">
+        <v>643</v>
+      </c>
     </row>
     <row r="188" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C188" s="49"/>
       <c r="F188" s="49"/>
-      <c r="H188" s="36"/>
+      <c r="H188" s="36" t="s">
+        <v>644</v>
+      </c>
     </row>
     <row r="189" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A189" s="22">
+        <v>137</v>
+      </c>
       <c r="C189" s="49"/>
       <c r="F189" s="49"/>
       <c r="H189" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B72C78-7882-43D5-8875-3B1663E8B8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D515938-3C77-40BA-92BC-0C87435A3ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="647">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1956,6 +1956,12 @@
   </si>
   <si>
     <t>Guide Rod DIA 6mm_EW- Qty 10 / Idler Pully shaft_EW- Qty 5 / Idler Pully_ER- Qty 5 / Bearing Locking Pin_ER- Qtyn10</t>
+  </si>
+  <si>
+    <t>H59171039</t>
+  </si>
+  <si>
+    <t>Halogen lamp  Assy BioeLab FA 6V/10W-Qty 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7193,6 +7199,9 @@
       <c r="H183" s="36" t="s">
         <v>637</v>
       </c>
+      <c r="I183" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="184" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C184" s="49"/>
@@ -7240,6 +7249,9 @@
       <c r="H187" s="36" t="s">
         <v>643</v>
       </c>
+      <c r="I187" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="188" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C188" s="49"/>
@@ -7252,9 +7264,30 @@
       <c r="A189" s="22">
         <v>137</v>
       </c>
-      <c r="C189" s="49"/>
-      <c r="F189" s="49"/>
-      <c r="H189" s="36"/>
+      <c r="B189" s="26">
+        <v>46224</v>
+      </c>
+      <c r="C189" s="49" t="s">
+        <v>645</v>
+      </c>
+      <c r="D189" s="26">
+        <v>46220</v>
+      </c>
+      <c r="E189" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F189" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G189" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H189" s="36" t="s">
+        <v>646</v>
+      </c>
+      <c r="I189" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="190" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C190" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D515938-3C77-40BA-92BC-0C87435A3ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24B0E5F-0DBF-41FD-B5D8-ACA9BB99B30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="648">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1962,6 +1962,9 @@
   </si>
   <si>
     <t>Halogen lamp  Assy BioeLab FA 6V/10W-Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>21 July 226</t>
   </si>
 </sst>
 </file>
@@ -14023,12 +14026,36 @@
       </c>
     </row>
     <row r="100" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A100" s="27"/>
-      <c r="B100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="45"/>
-      <c r="I100" s="29"/>
+      <c r="A100" s="27">
+        <v>76</v>
+      </c>
+      <c r="B100" s="45" t="s">
+        <v>647</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D100" s="55">
+        <v>46224</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G100" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H100" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I100" s="29" t="s">
+        <v>646</v>
+      </c>
+      <c r="J100" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="101" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A101" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24B0E5F-0DBF-41FD-B5D8-ACA9BB99B30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C656D-4225-422A-B4E2-D00BA0FFBCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C656D-4225-422A-B4E2-D00BA0FFBCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670CBA1A-1A02-402C-A261-BE1311DBBB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="652">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1965,6 +1965,18 @@
   </si>
   <si>
     <t>21 July 226</t>
+  </si>
+  <si>
+    <t>Lens Housing - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioSystem Diagnostics </t>
+  </si>
+  <si>
+    <t>Send By Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Filter Wheel With Filters-1 Nos./ Filter 340mm-1 Nos. / Filter 405mm- 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -13933,7 +13945,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="97" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A97" s="27">
         <v>73</v>
       </c>
@@ -13965,7 +13977,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="98" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A98" s="27">
         <v>74</v>
       </c>
@@ -13997,7 +14009,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="99" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A99" s="27">
         <v>75</v>
       </c>
@@ -14025,7 +14037,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="100" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="100" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A100" s="27">
         <v>76</v>
       </c>
@@ -14057,23 +14069,74 @@
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A101" s="27"/>
-      <c r="B101" s="45"/>
-      <c r="D101" s="45"/>
-      <c r="G101" s="45"/>
-      <c r="H101" s="45"/>
-      <c r="I101" s="29"/>
-    </row>
-    <row r="102" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A102" s="27"/>
-      <c r="B102" s="45"/>
-      <c r="D102" s="45"/>
-      <c r="G102" s="45"/>
-      <c r="H102" s="45"/>
-      <c r="I102" s="29"/>
-    </row>
-    <row r="103" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="101" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A101" s="27">
+        <v>77</v>
+      </c>
+      <c r="B101" s="55">
+        <v>46226</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D101" s="55">
+        <v>46226</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="G101" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H101" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="I101" s="29" t="s">
+        <v>648</v>
+      </c>
+      <c r="J101" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K101" s="10" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A102" s="27">
+        <v>78</v>
+      </c>
+      <c r="B102" s="55">
+        <v>46226</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D102" s="55">
+        <v>46226</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G102" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H102" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I102" s="29" t="s">
+        <v>651</v>
+      </c>
+      <c r="J102" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A103" s="27"/>
       <c r="B103" s="45"/>
       <c r="D103" s="45"/>
@@ -14081,7 +14144,7 @@
       <c r="H103" s="45"/>
       <c r="I103" s="29"/>
     </row>
-    <row r="104" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="104" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A104" s="27"/>
       <c r="B104" s="45"/>
       <c r="D104" s="45"/>
@@ -14089,7 +14152,7 @@
       <c r="H104" s="45"/>
       <c r="I104" s="29"/>
     </row>
-    <row r="105" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="105" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A105" s="27"/>
       <c r="B105" s="45"/>
       <c r="D105" s="45"/>
@@ -14097,7 +14160,7 @@
       <c r="H105" s="45"/>
       <c r="I105" s="29"/>
     </row>
-    <row r="106" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="106" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A106" s="27"/>
       <c r="B106" s="45"/>
       <c r="D106" s="45"/>
@@ -14105,7 +14168,7 @@
       <c r="H106" s="45"/>
       <c r="I106" s="29"/>
     </row>
-    <row r="107" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="107" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A107" s="27"/>
       <c r="B107" s="45"/>
       <c r="D107" s="45"/>
@@ -14113,7 +14176,7 @@
       <c r="H107" s="45"/>
       <c r="I107" s="29"/>
     </row>
-    <row r="108" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A108" s="27"/>
       <c r="B108" s="45"/>
       <c r="D108" s="45"/>
@@ -14121,7 +14184,7 @@
       <c r="H108" s="45"/>
       <c r="I108" s="29"/>
     </row>
-    <row r="109" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A109" s="27"/>
       <c r="B109" s="45"/>
       <c r="D109" s="45"/>
@@ -14129,7 +14192,7 @@
       <c r="H109" s="45"/>
       <c r="I109" s="29"/>
     </row>
-    <row r="110" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A110" s="27"/>
       <c r="B110" s="45"/>
       <c r="D110" s="45"/>
@@ -14137,7 +14200,7 @@
       <c r="H110" s="45"/>
       <c r="I110" s="29"/>
     </row>
-    <row r="111" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="27"/>
       <c r="B111" s="45"/>
       <c r="D111" s="45"/>
@@ -14145,7 +14208,7 @@
       <c r="H111" s="45"/>
       <c r="I111" s="29"/>
     </row>
-    <row r="112" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="112" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A112" s="27"/>
       <c r="B112" s="45"/>
       <c r="D112" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670CBA1A-1A02-402C-A261-BE1311DBBB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B04FC6-B3A0-4BDF-B5DE-27954BDDDDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="654">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1977,6 +1977,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Filter Wheel With Filters-1 Nos./ Filter 340mm-1 Nos. / Filter 405mm- 1 Nos.</t>
+  </si>
+  <si>
+    <t>Challan No.- 79</t>
+  </si>
+  <si>
+    <t>Photometer PCB Assembly Charges-Qty 1 Nos / Nano Pi M1 Board- Qty 4 Nos / Driver Board - Qty 1 Nos / Printer Board - Qty 2 Nos</t>
   </si>
 </sst>
 </file>
@@ -7305,9 +7311,33 @@
       </c>
     </row>
     <row r="190" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C190" s="49"/>
-      <c r="F190" s="49"/>
-      <c r="H190" s="36"/>
+      <c r="A190" s="22">
+        <v>138</v>
+      </c>
+      <c r="B190" s="26">
+        <v>46226</v>
+      </c>
+      <c r="C190" s="49" t="s">
+        <v>652</v>
+      </c>
+      <c r="D190" s="26">
+        <v>46224</v>
+      </c>
+      <c r="E190" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F190" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="G190" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H190" s="36" t="s">
+        <v>653</v>
+      </c>
+      <c r="I190" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="191" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C191" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B04FC6-B3A0-4BDF-B5DE-27954BDDDDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8397183-FA6C-4A32-8417-9F396ECCBB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="656">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1983,6 +1983,12 @@
   </si>
   <si>
     <t>Photometer PCB Assembly Charges-Qty 1 Nos / Nano Pi M1 Board- Qty 4 Nos / Driver Board - Qty 1 Nos / Printer Board - Qty 2 Nos</t>
+  </si>
+  <si>
+    <t>Challan No.-78</t>
+  </si>
+  <si>
+    <t>Semi Automatic Chemistry Analyzer (BioSci 50) - qty 1 Nos. / Sample Bottle</t>
   </si>
 </sst>
 </file>
@@ -7340,11 +7346,38 @@
       </c>
     </row>
     <row r="191" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C191" s="49"/>
-      <c r="F191" s="49"/>
-      <c r="H191" s="36"/>
+      <c r="A191" s="22">
+        <v>139</v>
+      </c>
+      <c r="B191" s="26">
+        <v>46226</v>
+      </c>
+      <c r="C191" s="49" t="s">
+        <v>654</v>
+      </c>
+      <c r="D191" s="26">
+        <v>46220</v>
+      </c>
+      <c r="E191" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F191" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="G191" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H191" s="36" t="s">
+        <v>655</v>
+      </c>
+      <c r="I191" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="192" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A192" s="22">
+        <v>140</v>
+      </c>
       <c r="C192" s="49"/>
       <c r="F192" s="49"/>
       <c r="H192" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8397183-FA6C-4A32-8417-9F396ECCBB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B43AE7F-A3D1-49BB-A463-06DBD277760F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1988,7 +1988,7 @@
     <t>Challan No.-78</t>
   </si>
   <si>
-    <t>Semi Automatic Chemistry Analyzer (BioSci 50) - qty 1 Nos. / Sample Bottle</t>
+    <t>Semi Automatic Chemistry Analyzer (BioSci 50) - qty 1 Nos. / Flowcell / PowerCod / Adoptor / Sample Bottle</t>
   </si>
 </sst>
 </file>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B43AE7F-A3D1-49BB-A463-06DBD277760F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E1C4F0-4046-4274-8636-7F56FB9C7A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="662">
   <si>
     <t>Sr No.</t>
   </si>
@@ -1989,6 +1989,24 @@
   </si>
   <si>
     <t>Semi Automatic Chemistry Analyzer (BioSci 50) - qty 1 Nos. / Flowcell / PowerCod / Adoptor / Sample Bottle</t>
+  </si>
+  <si>
+    <t>Sample Bottle- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Sample Bottle</t>
+  </si>
+  <si>
+    <t>Zenith Plastics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rashmi Pathak </t>
+  </si>
+  <si>
+    <t>Personal</t>
+  </si>
+  <si>
+    <t>Medicine - Juven Plus- Qty 2 Strips</t>
   </si>
 </sst>
 </file>
@@ -14200,28 +14218,100 @@
       </c>
     </row>
     <row r="103" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A103" s="27"/>
-      <c r="B103" s="45"/>
-      <c r="D103" s="45"/>
-      <c r="G103" s="45"/>
-      <c r="H103" s="45"/>
-      <c r="I103" s="29"/>
+      <c r="A103" s="27">
+        <v>79</v>
+      </c>
+      <c r="B103" s="55">
+        <v>46226</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D103" s="55">
+        <v>46226</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G103" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H103" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I103" s="29" t="s">
+        <v>656</v>
+      </c>
+      <c r="J103" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="104" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A104" s="27"/>
-      <c r="B104" s="45"/>
-      <c r="D104" s="45"/>
-      <c r="G104" s="45"/>
-      <c r="H104" s="45"/>
-      <c r="I104" s="29"/>
+      <c r="A104" s="27">
+        <v>80</v>
+      </c>
+      <c r="B104" s="55">
+        <v>46226</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D104" s="55">
+        <v>46226</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="G104" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H104" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I104" s="29" t="s">
+        <v>657</v>
+      </c>
+      <c r="J104" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="105" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A105" s="27"/>
-      <c r="B105" s="45"/>
-      <c r="D105" s="45"/>
-      <c r="G105" s="45"/>
-      <c r="H105" s="45"/>
-      <c r="I105" s="29"/>
+      <c r="A105" s="27">
+        <v>81</v>
+      </c>
+      <c r="B105" s="55">
+        <v>46226</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D105" s="55">
+        <v>46226</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="G105" s="45" t="s">
+        <v>660</v>
+      </c>
+      <c r="H105" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I105" s="29" t="s">
+        <v>661</v>
+      </c>
+      <c r="J105" s="10" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="106" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A106" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E1C4F0-4046-4274-8636-7F56FB9C7A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DEDBF9-9DC3-4E6A-A8BC-E8B5177BAF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="666">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2007,6 +2007,18 @@
   </si>
   <si>
     <t>Medicine - Juven Plus- Qty 2 Strips</t>
+  </si>
+  <si>
+    <t>Challan No. 26-27-129</t>
+  </si>
+  <si>
+    <t>Gas Spring- Model No. 818 - Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Osram Lamp- 10W-6V-G4- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>LG</t>
   </si>
 </sst>
 </file>
@@ -7396,86 +7408,129 @@
       <c r="A192" s="22">
         <v>140</v>
       </c>
-      <c r="C192" s="49"/>
-      <c r="F192" s="49"/>
-      <c r="H192" s="36"/>
-    </row>
-    <row r="193" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="B192" s="26">
+        <v>46226</v>
+      </c>
+      <c r="C192" s="49" t="s">
+        <v>662</v>
+      </c>
+      <c r="D192" s="58">
+        <v>46223</v>
+      </c>
+      <c r="E192" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F192" s="49" t="s">
+        <v>512</v>
+      </c>
+      <c r="G192" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H192" s="36" t="s">
+        <v>663</v>
+      </c>
+      <c r="I192" s="22" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A193" s="22">
+        <v>141</v>
+      </c>
+      <c r="B193" s="26">
+        <v>46226</v>
+      </c>
       <c r="C193" s="49"/>
-      <c r="F193" s="49"/>
-      <c r="H193" s="36"/>
-    </row>
-    <row r="194" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="D193" s="26">
+        <v>46226</v>
+      </c>
+      <c r="E193" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F193" s="49" t="s">
+        <v>665</v>
+      </c>
+      <c r="G193" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H193" s="36" t="s">
+        <v>664</v>
+      </c>
+      <c r="I193" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C194" s="49"/>
       <c r="F194" s="49"/>
       <c r="H194" s="36"/>
     </row>
-    <row r="195" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="195" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C195" s="49"/>
       <c r="F195" s="49"/>
       <c r="H195" s="36"/>
     </row>
-    <row r="196" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="196" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C196" s="49"/>
       <c r="F196" s="49"/>
       <c r="H196" s="36"/>
     </row>
-    <row r="197" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="197" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C197" s="49"/>
       <c r="F197" s="49"/>
       <c r="H197" s="36"/>
     </row>
-    <row r="198" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="198" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C198" s="49"/>
       <c r="F198" s="49"/>
       <c r="H198" s="36"/>
     </row>
-    <row r="199" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="199" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C199" s="49"/>
       <c r="F199" s="49"/>
       <c r="H199" s="36"/>
     </row>
-    <row r="200" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="200" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C200" s="49"/>
       <c r="F200" s="49"/>
       <c r="H200" s="36"/>
     </row>
-    <row r="201" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="201" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C201" s="49"/>
       <c r="F201" s="49"/>
       <c r="H201" s="36"/>
     </row>
-    <row r="202" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="202" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C202" s="49"/>
       <c r="F202" s="49"/>
       <c r="H202" s="36"/>
     </row>
-    <row r="203" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="203" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C203" s="49"/>
       <c r="F203" s="49"/>
       <c r="H203" s="36"/>
     </row>
-    <row r="204" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="204" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C204" s="49"/>
       <c r="F204" s="49"/>
       <c r="H204" s="36"/>
     </row>
-    <row r="205" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="205" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C205" s="49"/>
       <c r="F205" s="49"/>
       <c r="H205" s="36"/>
     </row>
-    <row r="206" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="206" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C206" s="49"/>
       <c r="F206" s="49"/>
       <c r="H206" s="36"/>
     </row>
-    <row r="207" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="207" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C207" s="49"/>
       <c r="F207" s="49"/>
       <c r="H207" s="36"/>
     </row>
-    <row r="208" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="208" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C208" s="49"/>
       <c r="F208" s="49"/>
       <c r="H208" s="36"/>
@@ -14314,7 +14369,9 @@
       </c>
     </row>
     <row r="106" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A106" s="27"/>
+      <c r="A106" s="27">
+        <v>82</v>
+      </c>
       <c r="B106" s="45"/>
       <c r="D106" s="45"/>
       <c r="G106" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DEDBF9-9DC3-4E6A-A8BC-E8B5177BAF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A41CBA-4393-4333-B0CE-917344C222B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="669">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2019,6 +2019,15 @@
   </si>
   <si>
     <t>LG</t>
+  </si>
+  <si>
+    <t>MPPL/30/26-27 &amp; Challan No.- 18</t>
+  </si>
+  <si>
+    <t>Mapel Polymer India Pvt Ltd</t>
+  </si>
+  <si>
+    <t>Top Cover- Qty 50 Nos. / Lever - Qty 50 Nos. / Locking Bracket - 100 Nos. / Outer Box - Qty 50 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7082,7 +7091,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="177" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="177" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A177" s="22">
         <v>130</v>
       </c>
@@ -7111,7 +7120,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="178" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A178" s="22">
         <v>131</v>
       </c>
@@ -7140,7 +7149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="179" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="179" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A179" s="22">
         <v>132</v>
       </c>
@@ -7166,7 +7175,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="180" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A180" s="22">
         <v>133</v>
       </c>
@@ -7192,7 +7201,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="181" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="181" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A181" s="22">
         <v>134</v>
       </c>
@@ -7221,7 +7230,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="182" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="182" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="22">
         <v>135</v>
       </c>
@@ -7250,7 +7259,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="183" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="183" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C183" s="49"/>
       <c r="F183" s="49"/>
       <c r="H183" s="36" t="s">
@@ -7260,28 +7269,28 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="184" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C184" s="49"/>
       <c r="F184" s="49"/>
       <c r="H184" s="36" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="185" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="185" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C185" s="49"/>
       <c r="F185" s="49"/>
       <c r="H185" s="36" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="186" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="186" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C186" s="49"/>
       <c r="F186" s="49"/>
       <c r="H186" s="36" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="187" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="187" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A187" s="22">
         <v>136</v>
       </c>
@@ -7310,14 +7319,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="188" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="188" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C188" s="49"/>
       <c r="F188" s="49"/>
       <c r="H188" s="36" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="189" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="189" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A189" s="22">
         <v>137</v>
       </c>
@@ -7346,7 +7355,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="190" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="190" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A190" s="22">
         <v>138</v>
       </c>
@@ -7375,7 +7384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="191" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="191" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A191" s="22">
         <v>139</v>
       </c>
@@ -7404,7 +7413,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="192" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="192" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A192" s="22">
         <v>140</v>
       </c>
@@ -7431,6 +7440,9 @@
       </c>
       <c r="I192" s="22" t="s">
         <v>185</v>
+      </c>
+      <c r="J192" s="22" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="193" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -7461,9 +7473,33 @@
       </c>
     </row>
     <row r="194" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C194" s="49"/>
-      <c r="F194" s="49"/>
-      <c r="H194" s="36"/>
+      <c r="A194" s="22">
+        <v>142</v>
+      </c>
+      <c r="B194" s="26">
+        <v>46227</v>
+      </c>
+      <c r="C194" s="49" t="s">
+        <v>666</v>
+      </c>
+      <c r="D194" s="26">
+        <v>46227</v>
+      </c>
+      <c r="E194" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F194" s="49" t="s">
+        <v>667</v>
+      </c>
+      <c r="G194" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H194" s="36" t="s">
+        <v>668</v>
+      </c>
+      <c r="I194" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="195" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C195" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A41CBA-4393-4333-B0CE-917344C222B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5BA0F9-E161-4315-86F0-A8788E1C30D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="671">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2028,6 +2028,12 @@
   </si>
   <si>
     <t>Top Cover- Qty 50 Nos. / Lever - Qty 50 Nos. / Locking Bracket - 100 Nos. / Outer Box - Qty 50 Nos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Challan DC No- 72982</t>
+  </si>
+  <si>
+    <t>ALANINE Aminotransferase (ALT/GPT) 200 ml- Qty 1 Nos. / ASPARTATE Aminotransferase (AST/GOT) 200 ml- Qty 1 Nos. &amp; Photometer PCB- Qty 2 Nos</t>
   </si>
 </sst>
 </file>
@@ -2904,8 +2910,8 @@
     <col min="5" max="5" width="18.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="45.5" style="51" customWidth="1"/>
     <col min="7" max="7" width="22.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="165.125" style="38" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="179.125" style="38" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="28.375" style="2" customWidth="1"/>
     <col min="11" max="11" width="19.625" style="2" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="33.5" style="2" hidden="1" customWidth="1"/>
@@ -7502,9 +7508,33 @@
       </c>
     </row>
     <row r="195" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C195" s="49"/>
-      <c r="F195" s="49"/>
-      <c r="H195" s="36"/>
+      <c r="A195" s="22">
+        <v>143</v>
+      </c>
+      <c r="B195" s="26">
+        <v>46227</v>
+      </c>
+      <c r="C195" s="49" t="s">
+        <v>669</v>
+      </c>
+      <c r="D195" s="26">
+        <v>46225</v>
+      </c>
+      <c r="E195" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F195" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="G195" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H195" s="36" t="s">
+        <v>670</v>
+      </c>
+      <c r="I195" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="196" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C196" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5BA0F9-E161-4315-86F0-A8788E1C30D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A64567F-3302-4803-A120-2C9DCA83A6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="674">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2034,6 +2034,15 @@
   </si>
   <si>
     <t>ALANINE Aminotransferase (ALT/GPT) 200 ml- Qty 1 Nos. / ASPARTATE Aminotransferase (AST/GOT) 200 ml- Qty 1 Nos. &amp; Photometer PCB- Qty 2 Nos</t>
+  </si>
+  <si>
+    <t>Darshi Biomedicals</t>
+  </si>
+  <si>
+    <t>Sahard</t>
+  </si>
+  <si>
+    <t>Philips Projection Lamp Type 6605 (6V-10W-G4) - Qty 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7537,9 +7546,33 @@
       </c>
     </row>
     <row r="196" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C196" s="49"/>
-      <c r="F196" s="49"/>
-      <c r="H196" s="36"/>
+      <c r="A196" s="22">
+        <v>144</v>
+      </c>
+      <c r="B196" s="26">
+        <v>46227</v>
+      </c>
+      <c r="C196" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D196" s="26">
+        <v>46227</v>
+      </c>
+      <c r="E196" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F196" s="49" t="s">
+        <v>671</v>
+      </c>
+      <c r="G196" s="22" t="s">
+        <v>672</v>
+      </c>
+      <c r="H196" s="36" t="s">
+        <v>673</v>
+      </c>
+      <c r="I196" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="197" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C197" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A64567F-3302-4803-A120-2C9DCA83A6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7148C24F-1352-4829-AEB1-41E5CAA5FA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="675">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2043,6 +2043,9 @@
   </si>
   <si>
     <t>Philips Projection Lamp Type 6605 (6V-10W-G4) - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Flowcell -Qty 1 Nos. / Photometer Board - Qty 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -14471,11 +14474,33 @@
       <c r="A106" s="27">
         <v>82</v>
       </c>
-      <c r="B106" s="45"/>
-      <c r="D106" s="45"/>
-      <c r="G106" s="45"/>
-      <c r="H106" s="45"/>
-      <c r="I106" s="29"/>
+      <c r="B106" s="55">
+        <v>46228</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D106" s="55">
+        <v>46227</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="G106" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H106" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I106" s="29" t="s">
+        <v>674</v>
+      </c>
+      <c r="J106" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="107" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A107" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7148C24F-1352-4829-AEB1-41E5CAA5FA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B51DC8-1849-4A3C-9E58-E9C95EC5DEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2045,7 +2045,7 @@
     <t>Philips Projection Lamp Type 6605 (6V-10W-G4) - Qty 1 Nos.</t>
   </si>
   <si>
-    <t>Flowcell -Qty 1 Nos. / Photometer Board - Qty 2 Nos.</t>
+    <t xml:space="preserve">  Photometer Board - Qty 2 Nos.</t>
   </si>
 </sst>
 </file>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B51DC8-1849-4A3C-9E58-E9C95EC5DEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD8D86D-85A5-4CA3-B50E-41A0504D6897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="676">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2046,6 +2046,9 @@
   </si>
   <si>
     <t xml:space="preserve">  Photometer Board - Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Mapel Inv. &amp; Challan</t>
   </si>
 </sst>
 </file>
@@ -14503,12 +14506,34 @@
       </c>
     </row>
     <row r="107" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A107" s="27"/>
-      <c r="B107" s="45"/>
-      <c r="D107" s="45"/>
+      <c r="A107" s="27">
+        <v>83</v>
+      </c>
+      <c r="B107" s="55">
+        <v>46230</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="D107" s="55">
+        <v>46230</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>208</v>
+      </c>
       <c r="G107" s="45"/>
-      <c r="H107" s="45"/>
-      <c r="I107" s="29"/>
+      <c r="H107" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I107" s="36" t="s">
+        <v>668</v>
+      </c>
+      <c r="J107" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A108" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD8D86D-85A5-4CA3-B50E-41A0504D6897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9088FF40-9A6C-45E4-8A22-D4ADEE9166FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="678">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2049,6 +2049,12 @@
   </si>
   <si>
     <t>Mapel Inv. &amp; Challan</t>
+  </si>
+  <si>
+    <t>NV-200 Bulbe- Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Challan- 000255</t>
   </si>
 </sst>
 </file>
@@ -7581,9 +7587,33 @@
       </c>
     </row>
     <row r="197" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C197" s="49"/>
-      <c r="F197" s="49"/>
-      <c r="H197" s="36"/>
+      <c r="A197" s="22">
+        <v>145</v>
+      </c>
+      <c r="B197" s="26">
+        <v>46231</v>
+      </c>
+      <c r="C197" s="49" t="s">
+        <v>677</v>
+      </c>
+      <c r="D197" s="26">
+        <v>46226</v>
+      </c>
+      <c r="E197" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F197" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="G197" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H197" s="36" t="s">
+        <v>676</v>
+      </c>
+      <c r="I197" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="198" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C198" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9088FF40-9A6C-45E4-8A22-D4ADEE9166FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C68065-41F2-4DB7-8B48-86A435F467A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C68065-41F2-4DB7-8B48-86A435F467A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA14658-EC04-4B91-B814-80F55A89647D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="684">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2055,6 +2055,24 @@
   </si>
   <si>
     <t>Challan- 000255</t>
+  </si>
+  <si>
+    <t>Challan No.- 944</t>
+  </si>
+  <si>
+    <t>Outer Cover- Qty 2 Nos. / Base Plate- Qty 2 Nos. / Printer Box Cover- Qty 10 Nos. / Switch - Qty 15 Nos.</t>
+  </si>
+  <si>
+    <t>AM/PP/0021/2627</t>
+  </si>
+  <si>
+    <t>BioSci 240 Reagent Compartment Sensor- Qty 2 Nos. / Home Sensor Reagent Arm- Qty 2 Nos. / Vertical Sensor- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>BioSci 240 Lamp Assembly 6V-10W- Qty 7 Nos. / stirrer Motor Wiyh Paddle- qty 3 Nos. / Photometer Board Repairs- Qty 2</t>
+  </si>
+  <si>
+    <t>BioSci 240 CRU Mainfold- Qty 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7616,9 +7634,33 @@
       </c>
     </row>
     <row r="198" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C198" s="49"/>
-      <c r="F198" s="49"/>
-      <c r="H198" s="36"/>
+      <c r="A198" s="22">
+        <v>146</v>
+      </c>
+      <c r="B198" s="26">
+        <v>46231</v>
+      </c>
+      <c r="C198" s="49" t="s">
+        <v>678</v>
+      </c>
+      <c r="D198" s="26">
+        <v>46231</v>
+      </c>
+      <c r="E198" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F198" s="49" t="s">
+        <v>511</v>
+      </c>
+      <c r="G198" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H198" s="36" t="s">
+        <v>679</v>
+      </c>
+      <c r="I198" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="199" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C199" s="49"/>
@@ -14566,12 +14608,36 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A108" s="27"/>
-      <c r="B108" s="45"/>
-      <c r="D108" s="45"/>
-      <c r="G108" s="45"/>
-      <c r="H108" s="45"/>
-      <c r="I108" s="29"/>
+      <c r="A108" s="27">
+        <v>84</v>
+      </c>
+      <c r="B108" s="55">
+        <v>46231</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="D108" s="55">
+        <v>46231</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G108" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H108" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I108" s="29" t="s">
+        <v>681</v>
+      </c>
+      <c r="J108" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A109" s="27"/>
@@ -14579,7 +14645,9 @@
       <c r="D109" s="45"/>
       <c r="G109" s="45"/>
       <c r="H109" s="45"/>
-      <c r="I109" s="29"/>
+      <c r="I109" s="29" t="s">
+        <v>682</v>
+      </c>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A110" s="27"/>
@@ -14587,10 +14655,14 @@
       <c r="D110" s="45"/>
       <c r="G110" s="45"/>
       <c r="H110" s="45"/>
-      <c r="I110" s="29"/>
+      <c r="I110" s="29" t="s">
+        <v>683</v>
+      </c>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A111" s="27"/>
+      <c r="A111" s="27">
+        <v>85</v>
+      </c>
       <c r="B111" s="45"/>
       <c r="D111" s="45"/>
       <c r="G111" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA14658-EC04-4B91-B814-80F55A89647D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AB47F3-980A-408B-8ED3-19A7F025DAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="693">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2073,6 +2073,33 @@
   </si>
   <si>
     <t>BioSci 240 CRU Mainfold- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Challan ( Chllan No. Not mention)</t>
+  </si>
+  <si>
+    <t>potral</t>
+  </si>
+  <si>
+    <t>Mapel Polymer India Pvt .</t>
+  </si>
+  <si>
+    <t>Sharaad</t>
+  </si>
+  <si>
+    <t>Base plate (Antide Sample) - qty 3 Nos.</t>
+  </si>
+  <si>
+    <t>L26IN033884</t>
+  </si>
+  <si>
+    <t>WR-MM Female Angled Connector Wiyh Polarization- Qty 3 Nos.</t>
+  </si>
+  <si>
+    <t>Documents ( Neel Vadvekar)</t>
+  </si>
+  <si>
+    <t>Neel Vadvekar</t>
   </si>
 </sst>
 </file>
@@ -7663,14 +7690,62 @@
       </c>
     </row>
     <row r="199" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C199" s="49"/>
-      <c r="F199" s="49"/>
-      <c r="H199" s="36"/>
+      <c r="A199" s="22">
+        <v>147</v>
+      </c>
+      <c r="B199" s="26">
+        <v>46232</v>
+      </c>
+      <c r="C199" s="49" t="s">
+        <v>684</v>
+      </c>
+      <c r="D199" s="26">
+        <v>46232</v>
+      </c>
+      <c r="E199" s="22" t="s">
+        <v>685</v>
+      </c>
+      <c r="F199" s="49" t="s">
+        <v>686</v>
+      </c>
+      <c r="G199" s="22" t="s">
+        <v>687</v>
+      </c>
+      <c r="H199" s="36" t="s">
+        <v>688</v>
+      </c>
+      <c r="I199" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="200" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C200" s="49"/>
-      <c r="F200" s="49"/>
-      <c r="H200" s="36"/>
+      <c r="A200" s="22">
+        <v>148</v>
+      </c>
+      <c r="B200" s="26">
+        <v>46233</v>
+      </c>
+      <c r="C200" s="49" t="s">
+        <v>689</v>
+      </c>
+      <c r="D200" s="26">
+        <v>46232</v>
+      </c>
+      <c r="E200" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F200" s="49" t="s">
+        <v>291</v>
+      </c>
+      <c r="G200" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H200" s="36" t="s">
+        <v>690</v>
+      </c>
+      <c r="I200" s="22" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="201" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C201" s="49"/>
@@ -14663,14 +14738,38 @@
       <c r="A111" s="27">
         <v>85</v>
       </c>
-      <c r="B111" s="45"/>
-      <c r="D111" s="45"/>
-      <c r="G111" s="45"/>
-      <c r="H111" s="45"/>
-      <c r="I111" s="29"/>
+      <c r="B111" s="55">
+        <v>46232</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D111" s="55">
+        <v>46232</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="G111" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H111" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I111" s="29" t="s">
+        <v>691</v>
+      </c>
+      <c r="J111" s="10" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="112" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A112" s="27"/>
+      <c r="A112" s="27">
+        <v>86</v>
+      </c>
       <c r="B112" s="45"/>
       <c r="D112" s="45"/>
       <c r="G112" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AB47F3-980A-408B-8ED3-19A7F025DAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EF93AB-1D02-4773-9B16-856EF6691FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="695">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2100,6 +2100,12 @@
   </si>
   <si>
     <t>Neel Vadvekar</t>
+  </si>
+  <si>
+    <t>SLF/26-27/G415</t>
+  </si>
+  <si>
+    <t>Tray Housing Frame - Qty 2 Nos. / Tray Bottom Plate - Qty 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7748,11 +7754,38 @@
       </c>
     </row>
     <row r="201" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C201" s="49"/>
-      <c r="F201" s="49"/>
-      <c r="H201" s="36"/>
+      <c r="A201" s="22">
+        <v>149</v>
+      </c>
+      <c r="B201" s="26">
+        <v>46233</v>
+      </c>
+      <c r="C201" s="49" t="s">
+        <v>693</v>
+      </c>
+      <c r="D201" s="26">
+        <v>46221</v>
+      </c>
+      <c r="E201" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F201" s="49" t="s">
+        <v>445</v>
+      </c>
+      <c r="G201" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H201" s="36" t="s">
+        <v>694</v>
+      </c>
+      <c r="I201" s="22" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="202" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A202" s="22">
+        <v>150</v>
+      </c>
       <c r="C202" s="49"/>
       <c r="F202" s="49"/>
       <c r="H202" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EF93AB-1D02-4773-9B16-856EF6691FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CE9AB7-3E43-4196-860A-165E0C88A85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="697">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2106,6 +2106,12 @@
   </si>
   <si>
     <t>Tray Housing Frame - Qty 2 Nos. / Tray Bottom Plate - Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>PSI-2627-11419</t>
+  </si>
+  <si>
+    <t>Igus JFM-1218-12 12mm Bore Plain Bearing 18mm O.D- Qty 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7786,11 +7792,35 @@
       <c r="A202" s="22">
         <v>150</v>
       </c>
-      <c r="C202" s="49"/>
-      <c r="F202" s="49"/>
-      <c r="H202" s="36"/>
+      <c r="B202" s="26">
+        <v>46234</v>
+      </c>
+      <c r="C202" s="49" t="s">
+        <v>695</v>
+      </c>
+      <c r="D202" s="26">
+        <v>46232</v>
+      </c>
+      <c r="E202" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F202" s="49" t="s">
+        <v>608</v>
+      </c>
+      <c r="G202" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H202" s="36" t="s">
+        <v>696</v>
+      </c>
+      <c r="I202" s="22" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="203" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A203" s="22">
+        <v>151</v>
+      </c>
       <c r="C203" s="49"/>
       <c r="F203" s="49"/>
       <c r="H203" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CE9AB7-3E43-4196-860A-165E0C88A85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14CA886-E39E-4250-AD70-C97AB24B3D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="701">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2084,9 +2084,6 @@
     <t>Mapel Polymer India Pvt .</t>
   </si>
   <si>
-    <t>Sharaad</t>
-  </si>
-  <si>
     <t>Base plate (Antide Sample) - qty 3 Nos.</t>
   </si>
   <si>
@@ -2112,6 +2109,21 @@
   </si>
   <si>
     <t>Igus JFM-1218-12 12mm Bore Plain Bearing 18mm O.D- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>PTW/26-27/012</t>
+  </si>
+  <si>
+    <t>Lamp Bush_oem-Qty 150 Nos. / Filter Holder- Qty 5 Nos. / Lens Housing- Qty 10 Nos. / Lens Locking ring- Qty 10 nos. / Spacer For Lens- Qty 10 Nos.</t>
+  </si>
+  <si>
+    <t>31 July 32026</t>
+  </si>
+  <si>
+    <t>BioSci Health Care ( Sourabh Tiwari Sir)</t>
+  </si>
+  <si>
+    <t>Sample Bottle- Qty 8 Nos. &amp; Sure Health Invoice For the Month of July 2026</t>
   </si>
 </sst>
 </file>
@@ -7721,10 +7733,10 @@
         <v>686</v>
       </c>
       <c r="G199" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H199" s="36" t="s">
         <v>687</v>
-      </c>
-      <c r="H199" s="36" t="s">
-        <v>688</v>
       </c>
       <c r="I199" s="22" t="s">
         <v>50</v>
@@ -7738,7 +7750,7 @@
         <v>46233</v>
       </c>
       <c r="C200" s="49" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D200" s="26">
         <v>46232</v>
@@ -7753,7 +7765,7 @@
         <v>45</v>
       </c>
       <c r="H200" s="36" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="I200" s="22" t="s">
         <v>185</v>
@@ -7767,7 +7779,7 @@
         <v>46233</v>
       </c>
       <c r="C201" s="49" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D201" s="26">
         <v>46221</v>
@@ -7782,7 +7794,7 @@
         <v>52</v>
       </c>
       <c r="H201" s="36" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="I201" s="22" t="s">
         <v>635</v>
@@ -7796,7 +7808,7 @@
         <v>46234</v>
       </c>
       <c r="C202" s="49" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D202" s="26">
         <v>46232</v>
@@ -7811,7 +7823,7 @@
         <v>210</v>
       </c>
       <c r="H202" s="36" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="I202" s="22" t="s">
         <v>185</v>
@@ -7821,11 +7833,35 @@
       <c r="A203" s="22">
         <v>151</v>
       </c>
-      <c r="C203" s="49"/>
-      <c r="F203" s="49"/>
-      <c r="H203" s="36"/>
+      <c r="B203" s="26">
+        <v>46234</v>
+      </c>
+      <c r="C203" s="49" t="s">
+        <v>696</v>
+      </c>
+      <c r="D203" s="26">
+        <v>46233</v>
+      </c>
+      <c r="E203" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F203" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="G203" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H203" s="36" t="s">
+        <v>697</v>
+      </c>
+      <c r="I203" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="204" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A204" s="22">
+        <v>152</v>
+      </c>
       <c r="C204" s="49"/>
       <c r="F204" s="49"/>
       <c r="H204" s="36"/>
@@ -14814,7 +14850,7 @@
         <v>13</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G111" s="45" t="s">
         <v>47</v>
@@ -14823,7 +14859,7 @@
         <v>52</v>
       </c>
       <c r="I111" s="29" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J111" s="10" t="s">
         <v>129</v>
@@ -14833,11 +14869,33 @@
       <c r="A112" s="27">
         <v>86</v>
       </c>
-      <c r="B112" s="45"/>
-      <c r="D112" s="45"/>
-      <c r="G112" s="45"/>
-      <c r="H112" s="45"/>
-      <c r="I112" s="29"/>
+      <c r="B112" s="45" t="s">
+        <v>698</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="D112" s="55">
+        <v>46234</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="G112" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H112" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I112" s="29" t="s">
+        <v>700</v>
+      </c>
+      <c r="J112" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="113" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A113" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14CA886-E39E-4250-AD70-C97AB24B3D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA7B046-FE3A-4FF0-9396-134EA74EAFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="702">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2114,9 +2114,6 @@
     <t>PTW/26-27/012</t>
   </si>
   <si>
-    <t>Lamp Bush_oem-Qty 150 Nos. / Filter Holder- Qty 5 Nos. / Lens Housing- Qty 10 Nos. / Lens Locking ring- Qty 10 nos. / Spacer For Lens- Qty 10 Nos.</t>
-  </si>
-  <si>
     <t>31 July 32026</t>
   </si>
   <si>
@@ -2124,6 +2121,12 @@
   </si>
   <si>
     <t>Sample Bottle- Qty 8 Nos. &amp; Sure Health Invoice For the Month of July 2026</t>
+  </si>
+  <si>
+    <t>PTW/26-27/013</t>
+  </si>
+  <si>
+    <t>Heat Sink For G4 Lamp- Qty 5 Nos./ Opto Pin_er - Qty 5 Nos./ Block For Tray housing_er - Qty 5 Nos./ Cover Fr Lens_er- Qty 5 Nos.</t>
   </si>
 </sst>
 </file>
@@ -6497,7 +6500,7 @@
         <v>46184</v>
       </c>
       <c r="C146" s="49" t="s">
-        <v>40</v>
+        <v>696</v>
       </c>
       <c r="D146" s="26">
         <v>46184</v>
@@ -7837,7 +7840,7 @@
         <v>46234</v>
       </c>
       <c r="C203" s="49" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D203" s="26">
         <v>46233</v>
@@ -7852,7 +7855,7 @@
         <v>210</v>
       </c>
       <c r="H203" s="36" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="I203" s="22" t="s">
         <v>50</v>
@@ -7862,7 +7865,9 @@
       <c r="A204" s="22">
         <v>152</v>
       </c>
+      <c r="B204" s="26"/>
       <c r="C204" s="49"/>
+      <c r="D204" s="26"/>
       <c r="F204" s="49"/>
       <c r="H204" s="36"/>
     </row>
@@ -14870,7 +14875,7 @@
         <v>86</v>
       </c>
       <c r="B112" s="45" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>469</v>
@@ -14882,7 +14887,7 @@
         <v>13</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G112" s="45" t="s">
         <v>125</v>
@@ -14891,7 +14896,7 @@
         <v>48</v>
       </c>
       <c r="I112" s="29" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J112" s="10" t="s">
         <v>50</v>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA7B046-FE3A-4FF0-9396-134EA74EAFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25891175-3C06-447C-BD8C-F6DC26E19593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="704">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2127,6 +2127,12 @@
   </si>
   <si>
     <t>Heat Sink For G4 Lamp- Qty 5 Nos./ Opto Pin_er - Qty 5 Nos./ Block For Tray housing_er - Qty 5 Nos./ Cover Fr Lens_er- Qty 5 Nos.</t>
+  </si>
+  <si>
+    <t>Challan No. 91</t>
+  </si>
+  <si>
+    <t>Urine Analysis Strip 10P (N)- Qty 2 Nos. / Urine Analysis Strip 14P (N)- Qty 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7865,11 +7871,30 @@
       <c r="A204" s="22">
         <v>152</v>
       </c>
-      <c r="B204" s="26"/>
-      <c r="C204" s="49"/>
-      <c r="D204" s="26"/>
-      <c r="F204" s="49"/>
-      <c r="H204" s="36"/>
+      <c r="B204" s="26">
+        <v>46237</v>
+      </c>
+      <c r="C204" s="49" t="s">
+        <v>702</v>
+      </c>
+      <c r="D204" s="26">
+        <v>46234</v>
+      </c>
+      <c r="E204" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F204" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="G204" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H204" s="36" t="s">
+        <v>703</v>
+      </c>
+      <c r="I204" s="22" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="205" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C205" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25891175-3C06-447C-BD8C-F6DC26E19593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C889C85A-5F18-4249-ABFB-362663724AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C889C85A-5F18-4249-ABFB-362663724AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7854469F-F963-4391-A870-92197A447D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="706">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2133,6 +2133,12 @@
   </si>
   <si>
     <t>Urine Analysis Strip 10P (N)- Qty 2 Nos. / Urine Analysis Strip 14P (N)- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Science House ( Sourabh panti)</t>
+  </si>
+  <si>
+    <t>Dryer Chips - Qty 15 Nos.</t>
   </si>
 </sst>
 </file>
@@ -14927,15 +14933,39 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A113" s="27"/>
-      <c r="B113" s="45"/>
-      <c r="D113" s="45"/>
-      <c r="G113" s="45"/>
-      <c r="H113" s="45"/>
-      <c r="I113" s="29"/>
-    </row>
-    <row r="114" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="113" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A113" s="27">
+        <v>87</v>
+      </c>
+      <c r="B113" s="55">
+        <v>46239</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D113" s="55">
+        <v>46239</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="G113" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H113" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="I113" s="29" t="s">
+        <v>705</v>
+      </c>
+      <c r="J113" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A114" s="27"/>
       <c r="B114" s="45"/>
       <c r="D114" s="45"/>
@@ -14943,7 +14973,7 @@
       <c r="H114" s="45"/>
       <c r="I114" s="29"/>
     </row>
-    <row r="115" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="115" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A115" s="27"/>
       <c r="B115" s="45"/>
       <c r="D115" s="45"/>
@@ -14951,7 +14981,7 @@
       <c r="H115" s="45"/>
       <c r="I115" s="29"/>
     </row>
-    <row r="116" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="116" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A116" s="27"/>
       <c r="B116" s="45"/>
       <c r="D116" s="45"/>
@@ -14959,7 +14989,7 @@
       <c r="H116" s="45"/>
       <c r="I116" s="29"/>
     </row>
-    <row r="117" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="117" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A117" s="27"/>
       <c r="B117" s="45"/>
       <c r="D117" s="45"/>
@@ -14967,7 +14997,7 @@
       <c r="H117" s="45"/>
       <c r="I117" s="29"/>
     </row>
-    <row r="118" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="118" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A118" s="27"/>
       <c r="B118" s="45"/>
       <c r="D118" s="45"/>
@@ -14975,7 +15005,7 @@
       <c r="H118" s="45"/>
       <c r="I118" s="29"/>
     </row>
-    <row r="119" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="119" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A119" s="27"/>
       <c r="B119" s="45"/>
       <c r="D119" s="45"/>
@@ -14983,7 +15013,7 @@
       <c r="H119" s="45"/>
       <c r="I119" s="29"/>
     </row>
-    <row r="120" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="120" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A120" s="27"/>
       <c r="B120" s="45"/>
       <c r="D120" s="45"/>
@@ -14991,7 +15021,7 @@
       <c r="H120" s="45"/>
       <c r="I120" s="29"/>
     </row>
-    <row r="121" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="121" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A121" s="27"/>
       <c r="B121" s="45"/>
       <c r="D121" s="45"/>
@@ -14999,7 +15029,7 @@
       <c r="H121" s="45"/>
       <c r="I121" s="29"/>
     </row>
-    <row r="122" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="122" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A122" s="27"/>
       <c r="B122" s="45"/>
       <c r="D122" s="45"/>
@@ -15007,7 +15037,7 @@
       <c r="H122" s="45"/>
       <c r="I122" s="29"/>
     </row>
-    <row r="123" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="123" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A123" s="27"/>
       <c r="B123" s="45"/>
       <c r="D123" s="45"/>
@@ -15015,7 +15045,7 @@
       <c r="H123" s="45"/>
       <c r="I123" s="29"/>
     </row>
-    <row r="124" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A124" s="27"/>
       <c r="B124" s="45"/>
       <c r="D124" s="45"/>
@@ -15023,7 +15053,7 @@
       <c r="H124" s="45"/>
       <c r="I124" s="29"/>
     </row>
-    <row r="125" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A125" s="27"/>
       <c r="B125" s="45"/>
       <c r="D125" s="45"/>
@@ -15031,7 +15061,7 @@
       <c r="H125" s="45"/>
       <c r="I125" s="29"/>
     </row>
-    <row r="126" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="27"/>
       <c r="B126" s="45"/>
       <c r="D126" s="45"/>
@@ -15039,7 +15069,7 @@
       <c r="H126" s="45"/>
       <c r="I126" s="29"/>
     </row>
-    <row r="127" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="127" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A127" s="27"/>
       <c r="B127" s="45"/>
       <c r="D127" s="45"/>
@@ -15047,7 +15077,7 @@
       <c r="H127" s="45"/>
       <c r="I127" s="29"/>
     </row>
-    <row r="128" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="128" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A128" s="27"/>
       <c r="B128" s="45"/>
       <c r="D128" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7854469F-F963-4391-A870-92197A447D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33321D3-94A8-4F55-B68D-F23B56E63FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14966,7 +14966,9 @@
       </c>
     </row>
     <row r="114" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A114" s="27"/>
+      <c r="A114" s="27">
+        <v>88</v>
+      </c>
       <c r="B114" s="45"/>
       <c r="D114" s="45"/>
       <c r="G114" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33321D3-94A8-4F55-B68D-F23B56E63FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FBBE54-E8D0-41D8-B451-78AC3BD5CF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="710">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2139,6 +2139,18 @@
   </si>
   <si>
     <t>Dryer Chips - Qty 15 Nos.</t>
+  </si>
+  <si>
+    <t>MHI2600241483</t>
+  </si>
+  <si>
+    <t>HP India Sales Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>I Pckt</t>
+  </si>
+  <si>
+    <t>HP Tri- Color GT Printhead -Qty 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7903,9 +7915,33 @@
       </c>
     </row>
     <row r="205" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C205" s="49"/>
-      <c r="F205" s="49"/>
-      <c r="H205" s="36"/>
+      <c r="A205" s="22">
+        <v>153</v>
+      </c>
+      <c r="B205" s="26">
+        <v>46240</v>
+      </c>
+      <c r="C205" s="49" t="s">
+        <v>706</v>
+      </c>
+      <c r="D205" s="26">
+        <v>46239</v>
+      </c>
+      <c r="E205" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F205" s="49" t="s">
+        <v>707</v>
+      </c>
+      <c r="G205" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H205" s="36" t="s">
+        <v>709</v>
+      </c>
+      <c r="I205" s="22" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="206" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C206" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FBBE54-E8D0-41D8-B451-78AC3BD5CF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F709D2-67D3-419B-88CE-BD2CA40AF0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="712">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2151,6 +2151,12 @@
   </si>
   <si>
     <t>HP Tri- Color GT Printhead -Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>AWB#7X110881151</t>
+  </si>
+  <si>
+    <t>Halogen Lamp PhotpMeter Bioelab FA 6V/10W - Qty 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7944,9 +7950,33 @@
       </c>
     </row>
     <row r="206" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C206" s="49"/>
-      <c r="F206" s="49"/>
-      <c r="H206" s="36"/>
+      <c r="A206" s="22">
+        <v>154</v>
+      </c>
+      <c r="B206" s="26">
+        <v>46240</v>
+      </c>
+      <c r="C206" s="49" t="s">
+        <v>710</v>
+      </c>
+      <c r="D206" s="26">
+        <v>46238</v>
+      </c>
+      <c r="E206" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F206" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G206" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H206" s="36" t="s">
+        <v>711</v>
+      </c>
+      <c r="I206" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="207" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C207" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F709D2-67D3-419B-88CE-BD2CA40AF0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17F8BF7-A620-40B6-B838-C3627AE1FFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4830" yWindow="0" windowWidth="10200" windowHeight="10920" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -7472,7 +7472,7 @@
         <v>37</v>
       </c>
       <c r="F189" s="49" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G189" s="22" t="s">
         <v>48</v>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17F8BF7-A620-40B6-B838-C3627AE1FFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1695A2F5-F434-4318-A758-F19137623094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4830" yWindow="0" windowWidth="10200" windowHeight="10920" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="714">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2157,6 +2157,12 @@
   </si>
   <si>
     <t>Halogen Lamp PhotpMeter Bioelab FA 6V/10W - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>JP/066/26-27</t>
+  </si>
+  <si>
+    <t>Display Bracket - qty 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -7979,9 +7985,33 @@
       </c>
     </row>
     <row r="207" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C207" s="49"/>
-      <c r="F207" s="49"/>
-      <c r="H207" s="36"/>
+      <c r="A207" s="22">
+        <v>155</v>
+      </c>
+      <c r="B207" s="26">
+        <v>46240</v>
+      </c>
+      <c r="C207" s="49" t="s">
+        <v>712</v>
+      </c>
+      <c r="D207" s="26">
+        <v>46238</v>
+      </c>
+      <c r="E207" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F207" s="49" t="s">
+        <v>549</v>
+      </c>
+      <c r="G207" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H207" s="36" t="s">
+        <v>713</v>
+      </c>
+      <c r="I207" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="208" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C208" s="49"/>
@@ -15035,11 +15065,33 @@
       <c r="A114" s="27">
         <v>88</v>
       </c>
-      <c r="B114" s="45"/>
-      <c r="D114" s="45"/>
-      <c r="G114" s="45"/>
-      <c r="H114" s="45"/>
-      <c r="I114" s="29"/>
+      <c r="B114" s="55">
+        <v>46240</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D114" s="55">
+        <v>46240</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G114" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H114" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I114" s="36" t="s">
+        <v>711</v>
+      </c>
+      <c r="J114" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="115" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A115" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1695A2F5-F434-4318-A758-F19137623094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D30CA67-C4F8-466A-9AD7-A0CBB3FC6565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="717">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2163,6 +2163,15 @@
   </si>
   <si>
     <t>Display Bracket - qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>AWB No. FMPP4178121467</t>
+  </si>
+  <si>
+    <t>Shree Balaji Traders ( Flipkart)</t>
+  </si>
+  <si>
+    <t>KJM Tip Box (combo) 2-200 ul</t>
   </si>
 </sst>
 </file>
@@ -8014,9 +8023,30 @@
       </c>
     </row>
     <row r="208" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C208" s="49"/>
-      <c r="F208" s="49"/>
-      <c r="H208" s="36"/>
+      <c r="A208" s="22">
+        <v>156</v>
+      </c>
+      <c r="B208" s="26">
+        <v>46241</v>
+      </c>
+      <c r="C208" s="49" t="s">
+        <v>714</v>
+      </c>
+      <c r="D208" s="26">
+        <v>46234</v>
+      </c>
+      <c r="F208" s="49" t="s">
+        <v>715</v>
+      </c>
+      <c r="G208" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="H208" s="36" t="s">
+        <v>716</v>
+      </c>
+      <c r="I208" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="209" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C209" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D30CA67-C4F8-466A-9AD7-A0CBB3FC6565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6CBBEC-5AFE-402E-898D-93C4A4B2497C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="720">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2172,6 +2172,15 @@
   </si>
   <si>
     <t>KJM Tip Box (combo) 2-200 ul</t>
+  </si>
+  <si>
+    <t>MH-BOM5-918080915-2627</t>
+  </si>
+  <si>
+    <t>Spigen India Pvt Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB-C TO USB-C Cable (Black) - Qty 1 Nos </t>
   </si>
 </sst>
 </file>
@@ -8048,82 +8057,103 @@
         <v>50</v>
       </c>
     </row>
-    <row r="209" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C209" s="49"/>
-      <c r="F209" s="49"/>
-      <c r="H209" s="36"/>
-    </row>
-    <row r="210" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="209" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A209" s="22">
+        <v>157</v>
+      </c>
+      <c r="B209" s="26">
+        <v>46241</v>
+      </c>
+      <c r="C209" s="49" t="s">
+        <v>717</v>
+      </c>
+      <c r="D209" s="26">
+        <v>46239</v>
+      </c>
+      <c r="E209" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="F209" s="49" t="s">
+        <v>718</v>
+      </c>
+      <c r="H209" s="36" t="s">
+        <v>719</v>
+      </c>
+      <c r="I209" s="22" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C210" s="49"/>
       <c r="F210" s="49"/>
       <c r="H210" s="36"/>
     </row>
-    <row r="211" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="211" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C211" s="49"/>
       <c r="F211" s="49"/>
       <c r="H211" s="36"/>
     </row>
-    <row r="212" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="212" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C212" s="49"/>
       <c r="F212" s="49"/>
       <c r="H212" s="36"/>
     </row>
-    <row r="213" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="213" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C213" s="49"/>
       <c r="F213" s="49"/>
       <c r="H213" s="36"/>
     </row>
-    <row r="214" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="214" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C214" s="49"/>
       <c r="F214" s="49"/>
       <c r="H214" s="36"/>
     </row>
-    <row r="215" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="215" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C215" s="49"/>
       <c r="F215" s="49"/>
       <c r="H215" s="36"/>
     </row>
-    <row r="216" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="216" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C216" s="49"/>
       <c r="F216" s="49"/>
       <c r="H216" s="36"/>
     </row>
-    <row r="217" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="217" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C217" s="49"/>
       <c r="F217" s="49"/>
       <c r="H217" s="36"/>
     </row>
-    <row r="218" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="218" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C218" s="49"/>
       <c r="F218" s="49"/>
       <c r="H218" s="36"/>
     </row>
-    <row r="219" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="219" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C219" s="49"/>
       <c r="F219" s="49"/>
       <c r="H219" s="36"/>
     </row>
-    <row r="220" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="220" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C220" s="49"/>
       <c r="F220" s="49"/>
       <c r="H220" s="36"/>
     </row>
-    <row r="221" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="221" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C221" s="49"/>
       <c r="F221" s="49"/>
       <c r="H221" s="36"/>
     </row>
-    <row r="222" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="222" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C222" s="49"/>
       <c r="F222" s="49"/>
       <c r="H222" s="36"/>
     </row>
-    <row r="223" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="223" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C223" s="49"/>
       <c r="F223" s="49"/>
       <c r="H223" s="36"/>
     </row>
-    <row r="224" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="224" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C224" s="49"/>
       <c r="F224" s="49"/>
       <c r="H224" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6CBBEC-5AFE-402E-898D-93C4A4B2497C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E81CDD0-A5B0-4DD6-90E6-BD5EEB7ED0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="728">
   <si>
     <t>Sr No.</t>
   </si>
@@ -761,9 +761,6 @@
     <t>Prt No.-860010372006 (WCAP-ATG8 Aluminum Electroytic Capactiors) - Qty - 10 Pcs</t>
   </si>
   <si>
-    <t>PTW/26-27/003</t>
-  </si>
-  <si>
     <t>BSHRD-018 LampBush_OEM -- Qty 150</t>
   </si>
   <si>
@@ -1022,9 +1019,6 @@
     <t>BioSci Reader PHM Component</t>
   </si>
   <si>
-    <t>PTW/26-27/002</t>
-  </si>
-  <si>
     <t>Aram Base &amp;LLS Pcb QTY 1+1</t>
   </si>
   <si>
@@ -2181,6 +2175,36 @@
   </si>
   <si>
     <t xml:space="preserve">USB-C TO USB-C Cable (Black) - Qty 1 Nos </t>
+  </si>
+  <si>
+    <t>JP/072/26-27</t>
+  </si>
+  <si>
+    <t>Display (Capacitive)- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Challan No. 68</t>
+  </si>
+  <si>
+    <t>Shree Diagnostics Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>Test Tube Plastic - Qty 1x100 = 5 pach</t>
+  </si>
+  <si>
+    <t>Lens Housing- Qty 9 Nos. / lens Locking Ring -Qty 9 Nos. / Spacer For Lens Housing - Qty 9 Nos. (Revert) / Lamp Bush_oem - Qty 150</t>
+  </si>
+  <si>
+    <t>PTW/26-27/002 &amp; PTW/26-27/015 (DT-31-07-26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTW/26-27/003 &amp; </t>
+  </si>
+  <si>
+    <t>PTW/26-27/015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter Holder- Qty 5 Nos. </t>
   </si>
 </sst>
 </file>
@@ -3052,7 +3076,7 @@
   <cols>
     <col min="1" max="1" width="8.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="45.875" style="51" customWidth="1"/>
+    <col min="3" max="3" width="57.75" style="51" customWidth="1"/>
     <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="45.5" style="51" customWidth="1"/>
@@ -3068,7 +3092,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
       <c r="A1" s="65" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -3106,7 +3130,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="48" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>5</v>
@@ -4195,7 +4219,7 @@
         <v>46128</v>
       </c>
       <c r="C51" s="49" t="s">
-        <v>333</v>
+        <v>724</v>
       </c>
       <c r="D51" s="26">
         <v>46126</v>
@@ -4288,7 +4312,7 @@
         <v>46134</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>246</v>
+        <v>725</v>
       </c>
       <c r="D54" s="26">
         <v>46133</v>
@@ -4303,7 +4327,7 @@
         <v>45</v>
       </c>
       <c r="H54" s="36" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I54" s="22" t="s">
         <v>50</v>
@@ -4317,22 +4341,22 @@
         <v>46136</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D55" s="26">
         <v>46135</v>
       </c>
       <c r="E55" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="F55" s="49" t="s">
         <v>252</v>
-      </c>
-      <c r="F55" s="49" t="s">
-        <v>253</v>
       </c>
       <c r="G55" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H55" s="36" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I55" s="22" t="s">
         <v>50</v>
@@ -4346,7 +4370,7 @@
         <v>46137</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D56" s="26">
         <v>46137</v>
@@ -4355,16 +4379,16 @@
         <v>134</v>
       </c>
       <c r="F56" s="49" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G56" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H56" s="36" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J56" s="22" t="s">
         <v>45</v>
@@ -4374,7 +4398,7 @@
       <c r="C57" s="49"/>
       <c r="F57" s="49"/>
       <c r="H57" s="36" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -4385,25 +4409,25 @@
         <v>46137</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D58" s="26">
         <v>46136</v>
       </c>
       <c r="E58" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F58" s="49" t="s">
         <v>260</v>
-      </c>
-      <c r="F58" s="49" t="s">
-        <v>261</v>
       </c>
       <c r="G58" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H58" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="I58" s="22" t="s">
         <v>262</v>
-      </c>
-      <c r="I58" s="22" t="s">
-        <v>263</v>
       </c>
       <c r="J58" s="22" t="s">
         <v>218</v>
@@ -4417,7 +4441,7 @@
         <v>46139</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D59" s="26">
         <v>46137</v>
@@ -4426,13 +4450,13 @@
         <v>67</v>
       </c>
       <c r="F59" s="49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G59" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H59" s="36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I59" s="22" t="s">
         <v>50</v>
@@ -4449,22 +4473,22 @@
         <v>46140</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D60" s="26">
         <v>46136</v>
       </c>
       <c r="E60" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="F60" s="49" t="s">
         <v>272</v>
-      </c>
-      <c r="F60" s="49" t="s">
-        <v>273</v>
       </c>
       <c r="G60" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H60" s="36" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I60" s="22" t="s">
         <v>50</v>
@@ -4478,22 +4502,22 @@
         <v>46140</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D61" s="26">
         <v>46136</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F61" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G61" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H61" s="36" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I61" s="22" t="s">
         <v>50</v>
@@ -4507,7 +4531,7 @@
         <v>46142</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D62" s="26">
         <v>46140</v>
@@ -4516,13 +4540,13 @@
         <v>102</v>
       </c>
       <c r="F62" s="49" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G62" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H62" s="36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I62" s="22" t="s">
         <v>50</v>
@@ -4536,7 +4560,7 @@
         <v>46142</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D63" s="26">
         <v>46140</v>
@@ -4545,13 +4569,13 @@
         <v>67</v>
       </c>
       <c r="F63" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G63" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H63" s="36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I63" s="22" t="s">
         <v>50</v>
@@ -4565,7 +4589,7 @@
         <v>46146</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D64" s="26">
         <v>46146</v>
@@ -4574,13 +4598,13 @@
         <v>67</v>
       </c>
       <c r="F64" s="49" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G64" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H64" s="36" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I64" s="22" t="s">
         <v>50</v>
@@ -4603,13 +4627,13 @@
         <v>37</v>
       </c>
       <c r="F65" s="49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G65" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H65" s="36" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I65" s="22" t="s">
         <v>50</v>
@@ -4638,7 +4662,7 @@
         <v>45</v>
       </c>
       <c r="H66" s="36" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I66" s="22" t="s">
         <v>50</v>
@@ -4652,7 +4676,7 @@
         <v>46146</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D67" s="26">
         <v>46142</v>
@@ -4661,13 +4685,13 @@
         <v>64</v>
       </c>
       <c r="F67" s="49" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G67" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I67" s="22" t="s">
         <v>50</v>
@@ -4681,7 +4705,7 @@
         <v>46146</v>
       </c>
       <c r="C68" s="49" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D68" s="26">
         <v>46142</v>
@@ -4696,10 +4720,10 @@
         <v>45</v>
       </c>
       <c r="H68" s="36" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -4707,21 +4731,21 @@
       <c r="C69" s="49"/>
       <c r="F69" s="49"/>
       <c r="H69" s="36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C70" s="49"/>
       <c r="F70" s="49"/>
       <c r="H70" s="36" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C71" s="49"/>
       <c r="F71" s="49"/>
       <c r="H71" s="36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -4738,19 +4762,19 @@
         <v>46144</v>
       </c>
       <c r="E72" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="F72" s="49" t="s">
         <v>311</v>
       </c>
-      <c r="F72" s="49" t="s">
+      <c r="G72" s="22" t="s">
         <v>312</v>
       </c>
-      <c r="G72" s="22" t="s">
+      <c r="H72" s="36" t="s">
         <v>313</v>
       </c>
-      <c r="H72" s="36" t="s">
-        <v>314</v>
-      </c>
       <c r="I72" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="73" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -4776,7 +4800,7 @@
         <v>45</v>
       </c>
       <c r="H73" s="36" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I73" s="22" t="s">
         <v>50</v>
@@ -4790,7 +4814,7 @@
         <v>46146</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D74" s="26">
         <v>46142</v>
@@ -4799,13 +4823,13 @@
         <v>37</v>
       </c>
       <c r="F74" s="49" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G74" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H74" s="36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I74" s="22" t="s">
         <v>50</v>
@@ -4819,25 +4843,25 @@
         <v>46147</v>
       </c>
       <c r="C75" s="49" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D75" s="26">
         <v>46142</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F75" s="49" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G75" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="36" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="76" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -4848,16 +4872,16 @@
         <v>46147</v>
       </c>
       <c r="C76" s="49" t="s">
+        <v>323</v>
+      </c>
+      <c r="F76" s="49" t="s">
         <v>324</v>
-      </c>
-      <c r="F76" s="49" t="s">
-        <v>325</v>
       </c>
       <c r="G76" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H76" s="36" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I76" s="22" t="s">
         <v>50</v>
@@ -4871,7 +4895,7 @@
         <v>46147</v>
       </c>
       <c r="C77" s="49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D77" s="26">
         <v>46143</v>
@@ -4880,13 +4904,13 @@
         <v>78</v>
       </c>
       <c r="F77" s="49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G77" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="36" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I77" s="22" t="s">
         <v>50</v>
@@ -4900,7 +4924,7 @@
         <v>46147</v>
       </c>
       <c r="C78" s="49" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D78" s="26">
         <v>46143</v>
@@ -4909,13 +4933,13 @@
         <v>78</v>
       </c>
       <c r="F78" s="49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G78" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="36" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I78" s="22" t="s">
         <v>50</v>
@@ -4929,7 +4953,7 @@
         <v>46148</v>
       </c>
       <c r="C79" s="49" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D79" s="26">
         <v>46142</v>
@@ -4938,13 +4962,13 @@
         <v>64</v>
       </c>
       <c r="F79" s="49" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G79" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H79" s="36" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I79" s="22" t="s">
         <v>185</v>
@@ -4958,7 +4982,7 @@
         <v>46148</v>
       </c>
       <c r="C80" s="49" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D80" s="26">
         <v>46143</v>
@@ -4973,35 +4997,35 @@
         <v>127</v>
       </c>
       <c r="H80" s="36" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C81" s="49"/>
       <c r="F81" s="49"/>
       <c r="H81" s="36" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C82" s="49"/>
       <c r="F82" s="49"/>
       <c r="H82" s="36" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C83" s="49"/>
       <c r="F83" s="49"/>
       <c r="H83" s="36" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C84" s="49"/>
       <c r="F84" s="49"/>
       <c r="H84" s="36" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5012,7 +5036,7 @@
         <v>46149</v>
       </c>
       <c r="C85" s="49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D85" s="26">
         <v>46147</v>
@@ -5021,13 +5045,13 @@
         <v>102</v>
       </c>
       <c r="F85" s="49" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G85" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H85" s="36" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I85" s="22" t="s">
         <v>50</v>
@@ -5041,19 +5065,19 @@
         <v>46149</v>
       </c>
       <c r="C86" s="49" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D86" s="26">
         <v>46142</v>
       </c>
       <c r="E86" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="F86" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="H86" s="36" t="s">
         <v>358</v>
-      </c>
-      <c r="F86" s="49" t="s">
-        <v>359</v>
-      </c>
-      <c r="H86" s="36" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5062,7 +5086,7 @@
       <c r="D87" s="26"/>
       <c r="F87" s="49"/>
       <c r="H87" s="36" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5073,7 +5097,7 @@
         <v>46149</v>
       </c>
       <c r="C88" s="49" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D88" s="26">
         <v>46142</v>
@@ -5082,13 +5106,13 @@
         <v>64</v>
       </c>
       <c r="F88" s="49" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G88" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H88" s="36" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I88" s="22" t="s">
         <v>50</v>
@@ -5098,7 +5122,7 @@
       <c r="C89" s="49"/>
       <c r="F89" s="49"/>
       <c r="H89" s="36" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="90" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5109,7 +5133,7 @@
         <v>46149</v>
       </c>
       <c r="C90" s="49" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D90" s="26">
         <v>46144</v>
@@ -5118,13 +5142,13 @@
         <v>64</v>
       </c>
       <c r="F90" s="49" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G90" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H90" s="36" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I90" s="22" t="s">
         <v>50</v>
@@ -5144,16 +5168,16 @@
         <v>46140</v>
       </c>
       <c r="E91" s="22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F91" s="49" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G91" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H91" s="36" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="I91" s="22" t="s">
         <v>50</v>
@@ -5163,21 +5187,21 @@
       <c r="C92" s="49"/>
       <c r="F92" s="49"/>
       <c r="H92" s="36" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="93" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C93" s="49"/>
       <c r="F93" s="49"/>
       <c r="H93" s="36" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="94" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C94" s="49"/>
       <c r="F94" s="49"/>
       <c r="H94" s="36" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="95" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5197,16 +5221,16 @@
         <v>37</v>
       </c>
       <c r="F95" s="49" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G95" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="36" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I95" s="22" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="96" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5217,7 +5241,7 @@
         <v>46150</v>
       </c>
       <c r="C96" s="49" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D96" s="26">
         <v>46149</v>
@@ -5226,13 +5250,13 @@
         <v>102</v>
       </c>
       <c r="F96" s="49" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G96" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H96" s="36" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I96" s="22" t="s">
         <v>50</v>
@@ -5246,19 +5270,19 @@
         <v>46151</v>
       </c>
       <c r="C97" s="49" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D97" s="26">
         <v>46150</v>
       </c>
       <c r="F97" s="49" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G97" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H97" s="36" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I97" s="22" t="s">
         <v>50</v>
@@ -5272,7 +5296,7 @@
         <v>46153</v>
       </c>
       <c r="C98" s="49" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D98" s="26">
         <v>46150</v>
@@ -5281,13 +5305,13 @@
         <v>67</v>
       </c>
       <c r="F98" s="49" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G98" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I98" s="22" t="s">
         <v>50</v>
@@ -5313,10 +5337,10 @@
         <v>42</v>
       </c>
       <c r="G99" s="22" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H99" s="36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I99" s="22" t="s">
         <v>50</v>
@@ -5330,7 +5354,7 @@
         <v>46155</v>
       </c>
       <c r="C100" s="49" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D100" s="26">
         <v>46150</v>
@@ -5339,13 +5363,13 @@
         <v>64</v>
       </c>
       <c r="F100" s="49" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G100" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="36" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="I100" s="22" t="s">
         <v>50</v>
@@ -5359,7 +5383,7 @@
         <v>46156</v>
       </c>
       <c r="C101" s="49" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D101" s="26">
         <v>46154</v>
@@ -5368,13 +5392,13 @@
         <v>102</v>
       </c>
       <c r="F101" s="49" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G101" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H101" s="36" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I101" s="22" t="s">
         <v>50</v>
@@ -5403,7 +5427,7 @@
         <v>45</v>
       </c>
       <c r="H102" s="36" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I102" s="22" t="s">
         <v>50</v>
@@ -5417,7 +5441,7 @@
         <v>46160</v>
       </c>
       <c r="C103" s="49" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D103" s="26">
         <v>46157</v>
@@ -5426,13 +5450,13 @@
         <v>67</v>
       </c>
       <c r="F103" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G103" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H103" s="36" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I103" s="22" t="s">
         <v>129</v>
@@ -5446,7 +5470,7 @@
         <v>46160</v>
       </c>
       <c r="C104" s="49" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D104" s="26">
         <v>46158</v>
@@ -5455,13 +5479,13 @@
         <v>78</v>
       </c>
       <c r="F104" s="49" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G104" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H104" s="36" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I104" s="22" t="s">
         <v>50</v>
@@ -5475,7 +5499,7 @@
         <v>46160</v>
       </c>
       <c r="C105" s="49" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D105" s="26">
         <v>46157</v>
@@ -5484,13 +5508,13 @@
         <v>41</v>
       </c>
       <c r="F105" s="49" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G105" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H105" s="36" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I105" s="22" t="s">
         <v>50</v>
@@ -5504,7 +5528,7 @@
         <v>46163</v>
       </c>
       <c r="C106" s="49" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D106" s="26">
         <v>46161</v>
@@ -5513,13 +5537,13 @@
         <v>102</v>
       </c>
       <c r="F106" s="49" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G106" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H106" s="36" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I106" s="22" t="s">
         <v>50</v>
@@ -5542,13 +5566,13 @@
         <v>37</v>
       </c>
       <c r="F107" s="49" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G107" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H107" s="36" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I107" s="22" t="s">
         <v>50</v>
@@ -5564,13 +5588,13 @@
       <c r="C108" s="49"/>
       <c r="D108" s="26"/>
       <c r="F108" s="49" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G108" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H108" s="36" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I108" s="22" t="s">
         <v>129</v>
@@ -5584,22 +5608,22 @@
         <v>46167</v>
       </c>
       <c r="C109" s="49" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D109" s="26">
         <v>46165</v>
       </c>
       <c r="E109" s="22" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F109" s="49" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G109" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H109" s="36" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I109" s="22" t="s">
         <v>185</v>
@@ -5610,10 +5634,10 @@
         <v>78</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C110" s="49" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D110" s="26">
         <v>46165</v>
@@ -5622,13 +5646,13 @@
         <v>102</v>
       </c>
       <c r="F110" s="49" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G110" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H110" s="36" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I110" s="22" t="s">
         <v>50</v>
@@ -5652,7 +5676,7 @@
         <v>45</v>
       </c>
       <c r="H111" s="36" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I111" s="22" t="s">
         <v>50</v>
@@ -5666,7 +5690,7 @@
         <v>46167</v>
       </c>
       <c r="C112" s="49" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D112" s="26">
         <v>46164</v>
@@ -5675,21 +5699,21 @@
         <v>67</v>
       </c>
       <c r="F112" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G112" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H112" s="36" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I112" s="22" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="113" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C113" s="49" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D113" s="26">
         <v>46164</v>
@@ -5698,40 +5722,40 @@
         <v>67</v>
       </c>
       <c r="F113" s="49" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G113" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H113" s="36" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I113" s="22" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="114" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C114" s="49"/>
       <c r="F114" s="49"/>
       <c r="H114" s="36" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I114" s="22" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C115" s="49"/>
       <c r="F115" s="49"/>
       <c r="H115" s="36" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="116" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C116" s="49"/>
       <c r="F116" s="49"/>
       <c r="H116" s="36" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="117" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5742,22 +5766,22 @@
         <v>46168</v>
       </c>
       <c r="C117" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D117" s="26">
         <v>46167</v>
       </c>
       <c r="E117" s="22" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F117" s="49" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G117" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H117" s="36" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="118" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5777,13 +5801,13 @@
         <v>37</v>
       </c>
       <c r="F118" s="49" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G118" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H118" s="36" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I118" s="22" t="s">
         <v>50</v>
@@ -5797,7 +5821,7 @@
         <v>46169</v>
       </c>
       <c r="C119" s="49" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D119" s="26">
         <v>46163</v>
@@ -5806,19 +5830,19 @@
         <v>37</v>
       </c>
       <c r="F119" s="49" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G119" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H119" s="36" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I119" s="22" t="s">
         <v>50</v>
       </c>
       <c r="J119" s="22" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="120" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5826,10 +5850,10 @@
         <v>84</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C120" s="49" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D120" s="26">
         <v>46167</v>
@@ -5844,7 +5868,7 @@
         <v>45</v>
       </c>
       <c r="H120" s="36" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I120" s="22" t="s">
         <v>50</v>
@@ -5858,7 +5882,7 @@
         <v>46169</v>
       </c>
       <c r="C121" s="49" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D121" s="26">
         <v>46166</v>
@@ -5873,7 +5897,7 @@
         <v>45</v>
       </c>
       <c r="H121" s="36" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I121" s="22" t="s">
         <v>50</v>
@@ -5887,7 +5911,7 @@
         <v>46169</v>
       </c>
       <c r="C122" s="49" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D122" s="26">
         <v>46165</v>
@@ -5896,13 +5920,13 @@
         <v>78</v>
       </c>
       <c r="F122" s="49" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G122" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H122" s="36" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="123" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5928,7 +5952,7 @@
         <v>22</v>
       </c>
       <c r="H123" s="36" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I123" s="22" t="s">
         <v>50</v>
@@ -5942,7 +5966,7 @@
         <v>46170</v>
       </c>
       <c r="C124" s="49" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D124" s="26">
         <v>46168</v>
@@ -5951,13 +5975,13 @@
         <v>102</v>
       </c>
       <c r="F124" s="49" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G124" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H124" s="36" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I124" s="22" t="s">
         <v>50</v>
@@ -5971,7 +5995,7 @@
         <v>46170</v>
       </c>
       <c r="C125" s="49" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D125" s="26">
         <v>46169</v>
@@ -5980,13 +6004,13 @@
         <v>102</v>
       </c>
       <c r="F125" s="49" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G125" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H125" s="36" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I125" s="22" t="s">
         <v>50</v>
@@ -6009,13 +6033,13 @@
         <v>78</v>
       </c>
       <c r="F126" s="49" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G126" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H126" s="36" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I126" s="22" t="s">
         <v>185</v>
@@ -6032,7 +6056,7 @@
         <v>47268</v>
       </c>
       <c r="C127" s="49" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D127" s="26">
         <v>46170</v>
@@ -6041,13 +6065,13 @@
         <v>41</v>
       </c>
       <c r="F127" s="49" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G127" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H127" s="36" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I127" s="22" t="s">
         <v>50</v>
@@ -6070,13 +6094,13 @@
         <v>13</v>
       </c>
       <c r="F128" s="49" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G128" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H128" s="36" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I128" s="22" t="s">
         <v>50</v>
@@ -6108,7 +6132,7 @@
         <v>45</v>
       </c>
       <c r="H129" s="36" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I129" s="22" t="s">
         <v>50</v>
@@ -6122,7 +6146,7 @@
         <v>46174</v>
       </c>
       <c r="C130" s="49" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D130" s="26">
         <v>46172</v>
@@ -6131,13 +6155,13 @@
         <v>102</v>
       </c>
       <c r="F130" s="49" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G130" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H130" s="36" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I130" s="22" t="s">
         <v>50</v>
@@ -6160,13 +6184,13 @@
         <v>13</v>
       </c>
       <c r="F131" s="49" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G131" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H131" s="36" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I131" s="22" t="s">
         <v>50</v>
@@ -6180,7 +6204,7 @@
         <v>46176</v>
       </c>
       <c r="C132" s="49" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D132" s="26">
         <v>46171</v>
@@ -6189,10 +6213,10 @@
         <v>67</v>
       </c>
       <c r="F132" s="49" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H132" s="36" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I132" s="22" t="s">
         <v>50</v>
@@ -6206,13 +6230,13 @@
         <v>46177</v>
       </c>
       <c r="C133" s="49" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D133" s="22" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E133" s="22" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F133" s="49" t="s">
         <v>42</v>
@@ -6221,7 +6245,7 @@
         <v>210</v>
       </c>
       <c r="H133" s="36" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I133" s="22" t="s">
         <v>50</v>
@@ -6241,16 +6265,16 @@
         <v>46175</v>
       </c>
       <c r="E134" s="22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F134" s="49" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G134" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H134" s="36" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I134" s="22" t="s">
         <v>50</v>
@@ -6264,7 +6288,7 @@
         <v>46181</v>
       </c>
       <c r="C135" s="49" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D135" s="26">
         <v>46178</v>
@@ -6273,13 +6297,13 @@
         <v>67</v>
       </c>
       <c r="F135" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G135" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H135" s="36" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I135" s="22" t="s">
         <v>129</v>
@@ -6293,7 +6317,7 @@
         <v>46181</v>
       </c>
       <c r="C136" s="49" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D136" s="26">
         <v>46178</v>
@@ -6302,13 +6326,13 @@
         <v>67</v>
       </c>
       <c r="F136" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G136" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="36" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="I136" s="22" t="s">
         <v>129</v>
@@ -6322,7 +6346,7 @@
         <v>46181</v>
       </c>
       <c r="C137" s="49" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D137" s="26">
         <v>46177</v>
@@ -6331,13 +6355,13 @@
         <v>67</v>
       </c>
       <c r="F137" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G137" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H137" s="36" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I137" s="22" t="s">
         <v>129</v>
@@ -6347,7 +6371,7 @@
       <c r="C138" s="49"/>
       <c r="F138" s="49"/>
       <c r="H138" s="36" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6358,7 +6382,7 @@
         <v>46181</v>
       </c>
       <c r="C139" s="49" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D139" s="26">
         <v>46177</v>
@@ -6367,13 +6391,13 @@
         <v>37</v>
       </c>
       <c r="F139" s="49" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G139" s="22" t="s">
         <v>43</v>
       </c>
       <c r="H139" s="36" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="I139" s="22" t="s">
         <v>50</v>
@@ -6386,7 +6410,7 @@
       <c r="C140" s="49"/>
       <c r="F140" s="49"/>
       <c r="H140" s="36" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="141" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6397,7 +6421,7 @@
         <v>46181</v>
       </c>
       <c r="C141" s="49" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D141" s="26">
         <v>46169</v>
@@ -6406,13 +6430,13 @@
         <v>64</v>
       </c>
       <c r="F141" s="49" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G141" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H141" s="36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="I141" s="22" t="s">
         <v>50</v>
@@ -6435,16 +6459,16 @@
         <v>46181</v>
       </c>
       <c r="E142" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="F142" s="49" t="s">
         <v>509</v>
-      </c>
-      <c r="F142" s="49" t="s">
-        <v>511</v>
       </c>
       <c r="G142" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H142" s="36" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I142" s="22" t="s">
         <v>50</v>
@@ -6458,7 +6482,7 @@
         <v>46181</v>
       </c>
       <c r="C143" s="49" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D143" s="26">
         <v>46178</v>
@@ -6467,13 +6491,13 @@
         <v>41</v>
       </c>
       <c r="F143" s="49" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G143" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H143" s="36" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="I143" s="22" t="s">
         <v>119</v>
@@ -6490,7 +6514,7 @@
         <v>46182</v>
       </c>
       <c r="C144" s="49" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D144" s="26">
         <v>46181</v>
@@ -6499,13 +6523,13 @@
         <v>41</v>
       </c>
       <c r="F144" s="49" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G144" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H144" s="36" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I144" s="22" t="s">
         <v>50</v>
@@ -6514,7 +6538,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="145" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="145" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A145" s="22">
         <v>107</v>
       </c>
@@ -6522,7 +6546,7 @@
         <v>46182</v>
       </c>
       <c r="C145" s="49" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D145" s="58">
         <v>46177</v>
@@ -6531,22 +6555,22 @@
         <v>52</v>
       </c>
       <c r="F145" s="49" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G145" s="22" t="s">
         <v>43</v>
       </c>
       <c r="H145" s="36" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="I145" s="22" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J145" s="22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="146" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="146" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A146" s="22">
         <v>108</v>
       </c>
@@ -6554,7 +6578,7 @@
         <v>46184</v>
       </c>
       <c r="C146" s="49" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D146" s="26">
         <v>46184</v>
@@ -6569,13 +6593,19 @@
         <v>45</v>
       </c>
       <c r="H146" s="36" t="s">
-        <v>524</v>
+        <v>723</v>
       </c>
       <c r="I146" s="22" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="J146" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="M146" s="22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A147" s="22">
         <v>109</v>
       </c>
@@ -6583,7 +6613,7 @@
         <v>46184</v>
       </c>
       <c r="C147" s="49" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D147" s="26">
         <v>46182</v>
@@ -6592,13 +6622,13 @@
         <v>67</v>
       </c>
       <c r="F147" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G147" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H147" s="36" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I147" s="22" t="s">
         <v>50</v>
@@ -6606,8 +6636,11 @@
       <c r="J147" s="22" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="M147" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A148" s="22">
         <v>110</v>
       </c>
@@ -6615,7 +6648,7 @@
         <v>46185</v>
       </c>
       <c r="C148" s="49" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D148" s="26">
         <v>46184</v>
@@ -6624,22 +6657,25 @@
         <v>102</v>
       </c>
       <c r="F148" s="49" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G148" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H148" s="36" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="I148" s="22" t="s">
         <v>50</v>
       </c>
       <c r="J148" s="22" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>529</v>
+      </c>
+      <c r="M148" s="22" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A149" s="22">
         <v>111</v>
       </c>
@@ -6656,19 +6692,19 @@
         <v>37</v>
       </c>
       <c r="F149" s="49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G149" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H149" s="36" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="I149" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="150" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="150" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A150" s="22">
         <v>112</v>
       </c>
@@ -6685,16 +6721,16 @@
         <v>37</v>
       </c>
       <c r="F150" s="49" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G150" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="36" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A151" s="22">
         <v>113</v>
       </c>
@@ -6702,7 +6738,7 @@
         <v>46189</v>
       </c>
       <c r="C151" s="49" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D151" s="26">
         <v>46186</v>
@@ -6711,26 +6747,26 @@
         <v>37</v>
       </c>
       <c r="F151" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G151" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H151" s="36" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I151" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="152" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C152" s="49"/>
       <c r="F152" s="49"/>
       <c r="H152" s="36" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A153" s="22">
         <v>114</v>
       </c>
@@ -6738,25 +6774,25 @@
         <v>46190</v>
       </c>
       <c r="C153" s="49" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D153" s="26">
         <v>46168</v>
       </c>
       <c r="E153" s="22" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F153" s="49" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G153" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H153" s="36" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="22">
         <v>115</v>
       </c>
@@ -6764,7 +6800,7 @@
         <v>46191</v>
       </c>
       <c r="C154" s="49" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D154" s="26">
         <v>46188</v>
@@ -6779,34 +6815,34 @@
         <v>86</v>
       </c>
       <c r="H154" s="36" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C155" s="49"/>
       <c r="F155" s="49"/>
       <c r="H155" s="36" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I155" s="22" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="156" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="156" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C156" s="49"/>
       <c r="F156" s="49"/>
       <c r="H156" s="36" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C157" s="49"/>
       <c r="F157" s="49"/>
       <c r="H157" s="36" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A158" s="22">
         <v>116</v>
       </c>
@@ -6814,7 +6850,7 @@
         <v>46191</v>
       </c>
       <c r="C158" s="49" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D158" s="26">
         <v>46190</v>
@@ -6823,19 +6859,19 @@
         <v>102</v>
       </c>
       <c r="F158" s="49" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G158" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H158" s="36" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I158" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="159" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="159" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A159" s="22">
         <v>117</v>
       </c>
@@ -6843,7 +6879,7 @@
         <v>46192</v>
       </c>
       <c r="C159" s="49" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D159" s="26">
         <v>46191</v>
@@ -6852,19 +6888,19 @@
         <v>67</v>
       </c>
       <c r="F159" s="49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G159" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H159" s="36" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I159" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="160" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="160" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="22">
         <v>118</v>
       </c>
@@ -6872,7 +6908,7 @@
         <v>46203</v>
       </c>
       <c r="C160" s="49" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D160" s="26">
         <v>46198</v>
@@ -6887,38 +6923,38 @@
         <v>86</v>
       </c>
       <c r="H160" s="29" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I160" s="22" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="161" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C161" s="49"/>
       <c r="F161" s="49"/>
       <c r="H161" s="29" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="162" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C162" s="49"/>
       <c r="F162" s="49"/>
       <c r="H162" s="29" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="163" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C163" s="49"/>
       <c r="F163" s="49"/>
       <c r="H163" s="29" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C164" s="49"/>
       <c r="F164" s="49"/>
       <c r="H164" s="29" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="165" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6929,7 +6965,7 @@
         <v>46203</v>
       </c>
       <c r="C165" s="49" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D165" s="26">
         <v>46199</v>
@@ -6944,7 +6980,7 @@
         <v>86</v>
       </c>
       <c r="H165" s="36" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I165" s="22" t="s">
         <v>50</v>
@@ -6958,7 +6994,7 @@
         <v>46204</v>
       </c>
       <c r="C166" s="49" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D166" s="26">
         <v>46200</v>
@@ -6967,13 +7003,13 @@
         <v>37</v>
       </c>
       <c r="F166" s="49" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G166" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H166" s="36" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="I166" s="22" t="s">
         <v>185</v>
@@ -6987,7 +7023,7 @@
         <v>46206</v>
       </c>
       <c r="C167" s="49" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D167" s="26">
         <v>46204</v>
@@ -7002,7 +7038,7 @@
         <v>86</v>
       </c>
       <c r="H167" s="29" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I167" s="22" t="s">
         <v>50</v>
@@ -7016,7 +7052,7 @@
         <v>46206</v>
       </c>
       <c r="C168" s="49" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D168" s="26">
         <v>46204</v>
@@ -7025,13 +7061,13 @@
         <v>67</v>
       </c>
       <c r="F168" s="49" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G168" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H168" s="36" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I168" s="22" t="s">
         <v>50</v>
@@ -7054,13 +7090,13 @@
         <v>37</v>
       </c>
       <c r="F169" s="49" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G169" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H169" s="36" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I169" s="22" t="s">
         <v>50</v>
@@ -7074,7 +7110,7 @@
         <v>46206</v>
       </c>
       <c r="C170" s="49" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D170" s="26">
         <v>46199</v>
@@ -7089,7 +7125,7 @@
         <v>86</v>
       </c>
       <c r="H170" s="36" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="I170" s="22" t="s">
         <v>50</v>
@@ -7103,7 +7139,7 @@
         <v>46206</v>
       </c>
       <c r="C171" s="49" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D171" s="26">
         <v>46203</v>
@@ -7112,13 +7148,13 @@
         <v>102</v>
       </c>
       <c r="F171" s="49" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G171" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H171" s="36" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="I171" s="22" t="s">
         <v>50</v>
@@ -7141,13 +7177,13 @@
         <v>67</v>
       </c>
       <c r="F172" s="49" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G172" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H172" s="29" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="I172" s="22" t="s">
         <v>50</v>
@@ -7161,19 +7197,19 @@
         <v>46210</v>
       </c>
       <c r="C173" s="49" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D173" s="26">
         <v>46206</v>
       </c>
       <c r="F173" s="49" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G173" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H173" s="36" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="I173" s="22" t="s">
         <v>50</v>
@@ -7187,22 +7223,22 @@
         <v>46213</v>
       </c>
       <c r="C174" s="49" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D174" s="26">
         <v>46212</v>
       </c>
       <c r="E174" s="22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F174" s="49" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G174" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="36" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="I174" s="22" t="s">
         <v>50</v>
@@ -7216,7 +7252,7 @@
         <v>46217</v>
       </c>
       <c r="C175" s="49" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D175" s="58">
         <v>46210</v>
@@ -7225,13 +7261,13 @@
         <v>56</v>
       </c>
       <c r="F175" s="49" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G175" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H175" s="36" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="I175" s="22" t="s">
         <v>50</v>
@@ -7241,7 +7277,7 @@
       <c r="C176" s="49"/>
       <c r="F176" s="49"/>
       <c r="H176" s="36" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="177" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -7252,7 +7288,7 @@
         <v>46217</v>
       </c>
       <c r="C177" s="49" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D177" s="26">
         <v>46204</v>
@@ -7267,7 +7303,7 @@
         <v>45</v>
       </c>
       <c r="H177" s="36" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="I177" s="22" t="s">
         <v>50</v>
@@ -7290,13 +7326,13 @@
         <v>37</v>
       </c>
       <c r="F178" s="49" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G178" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H178" s="36" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I178" s="22" t="s">
         <v>50</v>
@@ -7316,13 +7352,13 @@
         <v>46220</v>
       </c>
       <c r="F179" s="49" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G179" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H179" s="36" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I179" s="22" t="s">
         <v>50</v>
@@ -7342,13 +7378,13 @@
         <v>46220</v>
       </c>
       <c r="F180" s="49" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G180" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H180" s="36" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="I180" s="22" t="s">
         <v>50</v>
@@ -7362,7 +7398,7 @@
         <v>46223</v>
       </c>
       <c r="C181" s="49" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D181" s="26">
         <v>46219</v>
@@ -7371,13 +7407,13 @@
         <v>102</v>
       </c>
       <c r="F181" s="49" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G181" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="36" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="I181" s="22" t="s">
         <v>50</v>
@@ -7391,7 +7427,7 @@
         <v>46223</v>
       </c>
       <c r="C182" s="49" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D182" s="26">
         <v>46219</v>
@@ -7400,13 +7436,13 @@
         <v>37</v>
       </c>
       <c r="F182" s="49" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G182" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H182" s="36" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="I182" s="22" t="s">
         <v>50</v>
@@ -7416,7 +7452,7 @@
       <c r="C183" s="49"/>
       <c r="F183" s="49"/>
       <c r="H183" s="36" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="I183" s="22" t="s">
         <v>50</v>
@@ -7426,21 +7462,21 @@
       <c r="C184" s="49"/>
       <c r="F184" s="49"/>
       <c r="H184" s="36" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="185" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C185" s="49"/>
       <c r="F185" s="49"/>
       <c r="H185" s="36" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="186" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C186" s="49"/>
       <c r="F186" s="49"/>
       <c r="H186" s="36" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -7451,7 +7487,7 @@
         <v>46223</v>
       </c>
       <c r="C187" s="49" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D187" s="26">
         <v>46219</v>
@@ -7460,13 +7496,13 @@
         <v>37</v>
       </c>
       <c r="F187" s="49" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G187" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H187" s="36" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="I187" s="22" t="s">
         <v>50</v>
@@ -7476,7 +7512,7 @@
       <c r="C188" s="49"/>
       <c r="F188" s="49"/>
       <c r="H188" s="36" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="189" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -7487,7 +7523,7 @@
         <v>46224</v>
       </c>
       <c r="C189" s="49" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D189" s="26">
         <v>46220</v>
@@ -7502,7 +7538,7 @@
         <v>48</v>
       </c>
       <c r="H189" s="36" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="I189" s="22" t="s">
         <v>50</v>
@@ -7516,7 +7552,7 @@
         <v>46226</v>
       </c>
       <c r="C190" s="49" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D190" s="26">
         <v>46224</v>
@@ -7531,7 +7567,7 @@
         <v>45</v>
       </c>
       <c r="H190" s="36" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="I190" s="22" t="s">
         <v>50</v>
@@ -7545,7 +7581,7 @@
         <v>46226</v>
       </c>
       <c r="C191" s="49" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D191" s="26">
         <v>46220</v>
@@ -7560,7 +7596,7 @@
         <v>45</v>
       </c>
       <c r="H191" s="36" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="I191" s="22" t="s">
         <v>50</v>
@@ -7574,22 +7610,22 @@
         <v>46226</v>
       </c>
       <c r="C192" s="49" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D192" s="58">
         <v>46223</v>
       </c>
       <c r="E192" s="22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F192" s="49" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G192" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H192" s="36" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="I192" s="22" t="s">
         <v>185</v>
@@ -7598,7 +7634,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="193" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="193" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A193" s="22">
         <v>141</v>
       </c>
@@ -7610,22 +7646,22 @@
         <v>46226</v>
       </c>
       <c r="E193" s="22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F193" s="49" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G193" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H193" s="36" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="I193" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="194" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A194" s="22">
         <v>142</v>
       </c>
@@ -7633,28 +7669,28 @@
         <v>46227</v>
       </c>
       <c r="C194" s="49" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D194" s="26">
         <v>46227</v>
       </c>
       <c r="E194" s="22" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F194" s="49" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G194" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H194" s="36" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="I194" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="195" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="195" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A195" s="22">
         <v>143</v>
       </c>
@@ -7662,7 +7698,7 @@
         <v>46227</v>
       </c>
       <c r="C195" s="49" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D195" s="26">
         <v>46225</v>
@@ -7671,19 +7707,19 @@
         <v>67</v>
       </c>
       <c r="F195" s="49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G195" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H195" s="36" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I195" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="196" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="196" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A196" s="22">
         <v>144</v>
       </c>
@@ -7700,19 +7736,19 @@
         <v>78</v>
       </c>
       <c r="F196" s="49" t="s">
+        <v>669</v>
+      </c>
+      <c r="G196" s="22" t="s">
+        <v>670</v>
+      </c>
+      <c r="H196" s="36" t="s">
         <v>671</v>
-      </c>
-      <c r="G196" s="22" t="s">
-        <v>672</v>
-      </c>
-      <c r="H196" s="36" t="s">
-        <v>673</v>
       </c>
       <c r="I196" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="197" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="197" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A197" s="22">
         <v>145</v>
       </c>
@@ -7720,7 +7756,7 @@
         <v>46231</v>
       </c>
       <c r="C197" s="49" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D197" s="26">
         <v>46226</v>
@@ -7735,13 +7771,13 @@
         <v>45</v>
       </c>
       <c r="H197" s="36" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="I197" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="198" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="198" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A198" s="22">
         <v>146</v>
       </c>
@@ -7749,28 +7785,28 @@
         <v>46231</v>
       </c>
       <c r="C198" s="49" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D198" s="26">
         <v>46231</v>
       </c>
       <c r="E198" s="22" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F198" s="49" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G198" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H198" s="36" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I198" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="199" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="199" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A199" s="22">
         <v>147</v>
       </c>
@@ -7778,28 +7814,28 @@
         <v>46232</v>
       </c>
       <c r="C199" s="49" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D199" s="26">
         <v>46232</v>
       </c>
       <c r="E199" s="22" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F199" s="49" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G199" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H199" s="36" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="I199" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="200" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="200" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A200" s="22">
         <v>148</v>
       </c>
@@ -7807,7 +7843,7 @@
         <v>46233</v>
       </c>
       <c r="C200" s="49" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D200" s="26">
         <v>46232</v>
@@ -7816,19 +7852,19 @@
         <v>67</v>
       </c>
       <c r="F200" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G200" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H200" s="36" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="I200" s="22" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="201" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="201" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A201" s="22">
         <v>149</v>
       </c>
@@ -7836,7 +7872,7 @@
         <v>46233</v>
       </c>
       <c r="C201" s="49" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D201" s="26">
         <v>46221</v>
@@ -7845,19 +7881,19 @@
         <v>52</v>
       </c>
       <c r="F201" s="49" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G201" s="22" t="s">
         <v>52</v>
       </c>
       <c r="H201" s="36" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="I201" s="22" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A202" s="22">
         <v>150</v>
       </c>
@@ -7865,7 +7901,7 @@
         <v>46234</v>
       </c>
       <c r="C202" s="49" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D202" s="26">
         <v>46232</v>
@@ -7874,19 +7910,19 @@
         <v>67</v>
       </c>
       <c r="F202" s="49" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G202" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H202" s="36" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="I202" s="22" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="203" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="203" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A203" s="22">
         <v>151</v>
       </c>
@@ -7894,7 +7930,7 @@
         <v>46234</v>
       </c>
       <c r="C203" s="49" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D203" s="26">
         <v>46233</v>
@@ -7909,13 +7945,16 @@
         <v>210</v>
       </c>
       <c r="H203" s="36" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="I203" s="22" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="204" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="M203" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A204" s="22">
         <v>152</v>
       </c>
@@ -7923,7 +7962,7 @@
         <v>46237</v>
       </c>
       <c r="C204" s="49" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D204" s="26">
         <v>46234</v>
@@ -7938,13 +7977,13 @@
         <v>45</v>
       </c>
       <c r="H204" s="36" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="I204" s="22" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A205" s="22">
         <v>153</v>
       </c>
@@ -7952,7 +7991,7 @@
         <v>46240</v>
       </c>
       <c r="C205" s="49" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D205" s="26">
         <v>46239</v>
@@ -7961,19 +8000,19 @@
         <v>67</v>
       </c>
       <c r="F205" s="49" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G205" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H205" s="36" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="I205" s="22" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A206" s="22">
         <v>154</v>
       </c>
@@ -7981,7 +8020,7 @@
         <v>46240</v>
       </c>
       <c r="C206" s="49" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D206" s="26">
         <v>46238</v>
@@ -7996,13 +8035,13 @@
         <v>45</v>
       </c>
       <c r="H206" s="36" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="I206" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="207" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="207" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A207" s="22">
         <v>155</v>
       </c>
@@ -8010,7 +8049,7 @@
         <v>46240</v>
       </c>
       <c r="C207" s="49" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D207" s="26">
         <v>46238</v>
@@ -8019,19 +8058,19 @@
         <v>102</v>
       </c>
       <c r="F207" s="49" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G207" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H207" s="36" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="I207" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="208" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="208" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A208" s="22">
         <v>156</v>
       </c>
@@ -8039,25 +8078,25 @@
         <v>46241</v>
       </c>
       <c r="C208" s="49" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D208" s="26">
         <v>46234</v>
       </c>
       <c r="F208" s="49" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G208" s="22" t="s">
         <v>218</v>
       </c>
       <c r="H208" s="36" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="I208" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="209" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="209" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A209" s="22">
         <v>157</v>
       </c>
@@ -8065,95 +8104,167 @@
         <v>46241</v>
       </c>
       <c r="C209" s="49" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D209" s="26">
         <v>46239</v>
       </c>
       <c r="E209" s="22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F209" s="49" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H209" s="36" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="I209" s="22" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="210" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C210" s="49"/>
-      <c r="F210" s="49"/>
-      <c r="H210" s="36"/>
-    </row>
-    <row r="211" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C211" s="49"/>
-      <c r="F211" s="49"/>
-      <c r="H211" s="36"/>
-    </row>
-    <row r="212" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C212" s="49"/>
-      <c r="F212" s="49"/>
-      <c r="H212" s="36"/>
-    </row>
-    <row r="213" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="210" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A210" s="22">
+        <v>158</v>
+      </c>
+      <c r="B210" s="26">
+        <v>46241</v>
+      </c>
+      <c r="C210" s="49" t="s">
+        <v>718</v>
+      </c>
+      <c r="D210" s="26">
+        <v>46240</v>
+      </c>
+      <c r="E210" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F210" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="G210" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H210" s="36" t="s">
+        <v>719</v>
+      </c>
+      <c r="I210" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A211" s="22">
+        <v>159</v>
+      </c>
+      <c r="B211" s="26">
+        <v>46241</v>
+      </c>
+      <c r="C211" s="49" t="s">
+        <v>720</v>
+      </c>
+      <c r="D211" s="26">
+        <v>46239</v>
+      </c>
+      <c r="E211" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F211" s="49" t="s">
+        <v>721</v>
+      </c>
+      <c r="G211" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="H211" s="36" t="s">
+        <v>722</v>
+      </c>
+      <c r="I211" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A212" s="22">
+        <v>160</v>
+      </c>
+      <c r="B212" s="26">
+        <v>46241</v>
+      </c>
+      <c r="C212" s="49" t="s">
+        <v>726</v>
+      </c>
+      <c r="D212" s="26">
+        <v>46234</v>
+      </c>
+      <c r="E212" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F212" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="G212" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H212" s="36" t="s">
+        <v>727</v>
+      </c>
+      <c r="M212" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C213" s="49"/>
       <c r="F213" s="49"/>
       <c r="H213" s="36"/>
     </row>
-    <row r="214" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="214" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C214" s="49"/>
       <c r="F214" s="49"/>
       <c r="H214" s="36"/>
     </row>
-    <row r="215" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="215" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C215" s="49"/>
       <c r="F215" s="49"/>
       <c r="H215" s="36"/>
     </row>
-    <row r="216" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="216" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C216" s="49"/>
       <c r="F216" s="49"/>
       <c r="H216" s="36"/>
     </row>
-    <row r="217" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="217" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C217" s="49"/>
       <c r="F217" s="49"/>
       <c r="H217" s="36"/>
     </row>
-    <row r="218" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="218" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C218" s="49"/>
       <c r="F218" s="49"/>
       <c r="H218" s="36"/>
     </row>
-    <row r="219" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="219" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C219" s="49"/>
       <c r="F219" s="49"/>
       <c r="H219" s="36"/>
     </row>
-    <row r="220" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="220" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C220" s="49"/>
       <c r="F220" s="49"/>
       <c r="H220" s="36"/>
     </row>
-    <row r="221" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="221" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C221" s="49"/>
       <c r="F221" s="49"/>
       <c r="H221" s="36"/>
     </row>
-    <row r="222" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="222" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C222" s="49"/>
       <c r="F222" s="49"/>
       <c r="H222" s="36"/>
     </row>
-    <row r="223" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="223" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C223" s="49"/>
       <c r="F223" s="49"/>
       <c r="H223" s="36"/>
     </row>
-    <row r="224" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="224" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C224" s="49"/>
       <c r="F224" s="49"/>
       <c r="H224" s="36"/>
@@ -12625,7 +12736,7 @@
         <v>13</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G24" s="46" t="s">
         <v>47</v>
@@ -12634,7 +12745,7 @@
         <v>48</v>
       </c>
       <c r="I24" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J24" s="27" t="s">
         <v>50</v>
@@ -12992,14 +13103,14 @@
         <v>46132</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D38" s="45"/>
       <c r="E38" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G38" s="45" t="s">
         <v>47</v>
@@ -13008,7 +13119,7 @@
         <v>43</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J38" s="27" t="s">
         <v>50</v>
@@ -13019,10 +13130,10 @@
         <v>26</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D39" s="55">
         <v>46134</v>
@@ -13040,7 +13151,7 @@
         <v>48</v>
       </c>
       <c r="I39" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J39" s="27" t="s">
         <v>50</v>
@@ -13063,7 +13174,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G40" s="45" t="s">
         <v>47</v>
@@ -13072,7 +13183,7 @@
         <v>210</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J40" s="27" t="s">
         <v>50</v>
@@ -13086,7 +13197,7 @@
         <v>46139</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D41" s="55">
         <v>46139</v>
@@ -13101,10 +13212,10 @@
         <v>47</v>
       </c>
       <c r="H41" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="I41" s="29" t="s">
         <v>264</v>
-      </c>
-      <c r="I41" s="29" t="s">
-        <v>265</v>
       </c>
       <c r="J41" s="27" t="s">
         <v>50</v>
@@ -13119,7 +13230,7 @@
       <c r="G42" s="45"/>
       <c r="H42" s="45"/>
       <c r="I42" s="29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13130,7 +13241,7 @@
         <v>46140</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D43" s="55">
         <v>46140</v>
@@ -13139,7 +13250,7 @@
         <v>13</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G43" s="45" t="s">
         <v>47</v>
@@ -13148,7 +13259,7 @@
         <v>48</v>
       </c>
       <c r="I43" s="29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J43" s="10" t="s">
         <v>50</v>
@@ -13171,7 +13282,7 @@
         <v>13</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G44" s="45" t="s">
         <v>47</v>
@@ -13180,7 +13291,7 @@
         <v>22</v>
       </c>
       <c r="I44" s="29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13200,7 +13311,7 @@
         <v>13</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G45" s="45" t="s">
         <v>21</v>
@@ -13209,7 +13320,7 @@
         <v>127</v>
       </c>
       <c r="I45" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J45" s="10" t="s">
         <v>129</v>
@@ -13232,16 +13343,16 @@
         <v>13</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G46" s="45" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H46" s="45" t="s">
         <v>22</v>
       </c>
       <c r="I46" s="29" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J46" s="10" t="s">
         <v>50</v>
@@ -13255,7 +13366,7 @@
         <v>46149</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D47" s="55">
         <v>46148</v>
@@ -13264,7 +13375,7 @@
         <v>67</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G47" s="45" t="s">
         <v>47</v>
@@ -13273,10 +13384,10 @@
         <v>48</v>
       </c>
       <c r="I47" s="29" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13286,10 +13397,10 @@
       <c r="G48" s="45"/>
       <c r="H48" s="45"/>
       <c r="I48" s="29" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13300,7 +13411,7 @@
         <v>46149</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D49" s="55">
         <v>46148</v>
@@ -13318,10 +13429,10 @@
         <v>48</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13331,10 +13442,10 @@
       <c r="G50" s="45"/>
       <c r="H50" s="45"/>
       <c r="I50" s="29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13354,7 +13465,7 @@
         <v>13</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G51" s="45" t="s">
         <v>47</v>
@@ -13363,7 +13474,7 @@
         <v>48</v>
       </c>
       <c r="I51" s="29" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J51" s="10" t="s">
         <v>50</v>
@@ -13386,7 +13497,7 @@
         <v>102</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G52" s="45" t="s">
         <v>47</v>
@@ -13395,7 +13506,7 @@
         <v>52</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J52" s="10" t="s">
         <v>50</v>
@@ -13418,7 +13529,7 @@
         <v>13</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G53" s="45" t="s">
         <v>47</v>
@@ -13427,7 +13538,7 @@
         <v>43</v>
       </c>
       <c r="I53" s="29" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J53" s="10" t="s">
         <v>50</v>
@@ -13450,7 +13561,7 @@
         <v>13</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G54" s="45" t="s">
         <v>47</v>
@@ -13459,7 +13570,7 @@
         <v>43</v>
       </c>
       <c r="I54" s="29" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J54" s="10" t="s">
         <v>50</v>
@@ -13482,7 +13593,7 @@
         <v>102</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G55" s="45" t="s">
         <v>47</v>
@@ -13491,7 +13602,7 @@
         <v>43</v>
       </c>
       <c r="I55" s="36" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J55" s="10" t="s">
         <v>50</v>
@@ -13505,7 +13616,7 @@
         <v>46162</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D56" s="55">
         <v>46162</v>
@@ -13523,7 +13634,7 @@
         <v>48</v>
       </c>
       <c r="I56" s="29" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>50</v>
@@ -13546,16 +13657,16 @@
         <v>102</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G57" s="45" t="s">
         <v>47</v>
       </c>
       <c r="H57" s="45" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I57" s="29" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J57" s="10" t="s">
         <v>50</v>
@@ -13587,7 +13698,7 @@
         <v>22</v>
       </c>
       <c r="I58" s="36" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J58" s="10" t="s">
         <v>50</v>
@@ -13619,7 +13730,7 @@
         <v>22</v>
       </c>
       <c r="I59" s="29" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J59" s="10" t="s">
         <v>50</v>
@@ -13633,7 +13744,7 @@
         <v>46169</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D60" s="55">
         <v>46169</v>
@@ -13651,7 +13762,7 @@
         <v>48</v>
       </c>
       <c r="I60" s="29" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J60" s="10" t="s">
         <v>50</v>
@@ -13664,7 +13775,7 @@
       <c r="G61" s="45"/>
       <c r="H61" s="45"/>
       <c r="I61" s="29" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13684,7 +13795,7 @@
         <v>13</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G62" s="45" t="s">
         <v>47</v>
@@ -13693,7 +13804,7 @@
         <v>43</v>
       </c>
       <c r="I62" s="36" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J62" s="10" t="s">
         <v>50</v>
@@ -13707,7 +13818,7 @@
         <v>46171</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D63" s="55">
         <v>46171</v>
@@ -13719,13 +13830,13 @@
         <v>161</v>
       </c>
       <c r="G63" s="45" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H63" s="45" t="s">
         <v>43</v>
       </c>
       <c r="I63" s="29" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J63" s="10" t="s">
         <v>50</v>
@@ -13745,10 +13856,10 @@
         <v>46172</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G64" s="45" t="s">
         <v>47</v>
@@ -13757,7 +13868,7 @@
         <v>43</v>
       </c>
       <c r="I64" s="29" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J64" s="10" t="s">
         <v>50</v>
@@ -13789,7 +13900,7 @@
         <v>22</v>
       </c>
       <c r="I65" s="29" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J65" s="10" t="s">
         <v>50</v>
@@ -13818,7 +13929,7 @@
         <v>127</v>
       </c>
       <c r="I66" s="29" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J66" s="10" t="s">
         <v>214</v>
@@ -13850,7 +13961,7 @@
         <v>210</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J67" s="10" t="s">
         <v>50</v>
@@ -13873,7 +13984,7 @@
         <v>13</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G68" s="45" t="s">
         <v>47</v>
@@ -13882,7 +13993,7 @@
         <v>210</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J68" s="10" t="s">
         <v>50</v>
@@ -13914,7 +14025,7 @@
         <v>22</v>
       </c>
       <c r="I69" s="29" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J69" s="10" t="s">
         <v>50</v>
@@ -13937,7 +14048,7 @@
         <v>13</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G70" s="45" t="s">
         <v>47</v>
@@ -13946,7 +14057,7 @@
         <v>22</v>
       </c>
       <c r="I70" s="29" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="J70" s="10" t="s">
         <v>50</v>
@@ -13978,7 +14089,7 @@
         <v>22</v>
       </c>
       <c r="I71" s="29" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="J71" s="10" t="s">
         <v>50</v>
@@ -13992,7 +14103,7 @@
         <v>46192</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D72" s="55">
         <v>46191</v>
@@ -14001,7 +14112,7 @@
         <v>67</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G72" s="45" t="s">
         <v>47</v>
@@ -14010,10 +14121,10 @@
         <v>48</v>
       </c>
       <c r="I72" s="29" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14023,7 +14134,7 @@
       <c r="G73" s="45"/>
       <c r="H73" s="45"/>
       <c r="I73" s="36" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14034,7 +14145,7 @@
         <v>46192</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D74" s="55">
         <v>46191</v>
@@ -14052,10 +14163,10 @@
         <v>48</v>
       </c>
       <c r="I74" s="36" t="s">
+        <v>553</v>
+      </c>
+      <c r="J74" s="10" t="s">
         <v>555</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14075,7 +14186,7 @@
         <v>102</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G75" s="45" t="s">
         <v>47</v>
@@ -14084,7 +14195,7 @@
         <v>52</v>
       </c>
       <c r="I75" s="36" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J75" s="10" t="s">
         <v>50</v>
@@ -14098,7 +14209,7 @@
         <v>46196</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D76" s="55">
         <v>46196</v>
@@ -14116,7 +14227,7 @@
         <v>48</v>
       </c>
       <c r="I76" s="29" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J76" s="10" t="s">
         <v>50</v>
@@ -14139,7 +14250,7 @@
         <v>102</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G77" s="45" t="s">
         <v>47</v>
@@ -14148,7 +14259,7 @@
         <v>52</v>
       </c>
       <c r="I77" s="29" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J77" s="10" t="s">
         <v>50</v>
@@ -14171,7 +14282,7 @@
         <v>13</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G78" s="45" t="s">
         <v>47</v>
@@ -14180,7 +14291,7 @@
         <v>43</v>
       </c>
       <c r="I78" s="29" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>50</v>
@@ -14203,7 +14314,7 @@
         <v>102</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G79" s="45" t="s">
         <v>47</v>
@@ -14212,7 +14323,7 @@
         <v>43</v>
       </c>
       <c r="I79" s="29" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J79" s="10" t="s">
         <v>50</v>
@@ -14226,13 +14337,13 @@
         <v>46200</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D80" s="55">
         <v>46200</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>208</v>
@@ -14244,10 +14355,10 @@
         <v>48</v>
       </c>
       <c r="I80" s="29" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14257,7 +14368,7 @@
       <c r="G81" s="45"/>
       <c r="H81" s="45"/>
       <c r="I81" s="29" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14267,7 +14378,7 @@
       <c r="G82" s="45"/>
       <c r="H82" s="45"/>
       <c r="I82" s="29" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14277,7 +14388,7 @@
       <c r="G83" s="45"/>
       <c r="H83" s="45"/>
       <c r="I83" s="29" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14287,7 +14398,7 @@
       <c r="G84" s="45"/>
       <c r="H84" s="45"/>
       <c r="I84" s="29" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14316,7 +14427,7 @@
         <v>43</v>
       </c>
       <c r="I85" s="29" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J85" s="10" t="s">
         <v>50</v>
@@ -14329,7 +14440,7 @@
       <c r="G86" s="45"/>
       <c r="H86" s="45"/>
       <c r="I86" s="29" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14358,7 +14469,7 @@
         <v>22</v>
       </c>
       <c r="I87" s="29" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J87" s="10" t="s">
         <v>50</v>
@@ -14371,7 +14482,7 @@
       <c r="G88" s="45"/>
       <c r="H88" s="45"/>
       <c r="I88" s="29" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14391,7 +14502,7 @@
         <v>13</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G89" s="45" t="s">
         <v>47</v>
@@ -14400,7 +14511,7 @@
         <v>52</v>
       </c>
       <c r="I89" s="29" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="90" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14417,10 +14528,10 @@
         <v>46212</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G90" s="45" t="s">
         <v>47</v>
@@ -14429,7 +14540,7 @@
         <v>22</v>
       </c>
       <c r="I90" s="29" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="91" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14446,10 +14557,10 @@
         <v>46212</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G91" s="45" t="s">
         <v>47</v>
@@ -14458,7 +14569,7 @@
         <v>210</v>
       </c>
       <c r="I91" s="29" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="J91" s="10" t="s">
         <v>50</v>
@@ -14469,7 +14580,7 @@
         <v>68</v>
       </c>
       <c r="B92" s="45" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>40</v>
@@ -14490,7 +14601,7 @@
         <v>22</v>
       </c>
       <c r="I92" s="29" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J92" s="10" t="s">
         <v>50</v>
@@ -14522,7 +14633,7 @@
         <v>210</v>
       </c>
       <c r="I93" s="29" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J93" s="10" t="s">
         <v>50</v>
@@ -14536,7 +14647,7 @@
         <v>46211</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D94" s="55">
         <v>46211</v>
@@ -14554,7 +14665,7 @@
         <v>48</v>
       </c>
       <c r="I94" s="29" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J94" s="10" t="s">
         <v>50</v>
@@ -14568,7 +14679,7 @@
         <v>46206</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D95" s="55">
         <v>46206</v>
@@ -14577,7 +14688,7 @@
         <v>13</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G95" s="45" t="s">
         <v>47</v>
@@ -14586,10 +14697,10 @@
         <v>48</v>
       </c>
       <c r="I95" s="29" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="96" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14618,7 +14729,7 @@
         <v>48</v>
       </c>
       <c r="I96" s="29" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J96" s="10" t="s">
         <v>50</v>
@@ -14632,7 +14743,7 @@
         <v>46220</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D97" s="55">
         <v>46220</v>
@@ -14650,7 +14761,7 @@
         <v>48</v>
       </c>
       <c r="I97" s="29" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="J97" s="10" t="s">
         <v>50</v>
@@ -14673,16 +14784,16 @@
         <v>102</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G98" s="45" t="s">
         <v>47</v>
       </c>
       <c r="H98" s="45" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="I98" s="29" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="J98" s="10" t="s">
         <v>50</v>
@@ -14702,18 +14813,18 @@
         <v>46220</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G99" s="45"/>
       <c r="H99" s="45"/>
       <c r="I99" s="29" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="100" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14721,7 +14832,7 @@
         <v>76</v>
       </c>
       <c r="B100" s="45" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>40</v>
@@ -14742,7 +14853,7 @@
         <v>48</v>
       </c>
       <c r="I100" s="29" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="J100" s="10" t="s">
         <v>50</v>
@@ -14765,7 +14876,7 @@
         <v>13</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G101" s="45" t="s">
         <v>47</v>
@@ -14774,13 +14885,13 @@
         <v>43</v>
       </c>
       <c r="I101" s="29" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="J101" s="10" t="s">
         <v>50</v>
       </c>
       <c r="K101" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14800,7 +14911,7 @@
         <v>102</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G102" s="45" t="s">
         <v>47</v>
@@ -14809,7 +14920,7 @@
         <v>52</v>
       </c>
       <c r="I102" s="29" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="J102" s="10" t="s">
         <v>50</v>
@@ -14841,7 +14952,7 @@
         <v>48</v>
       </c>
       <c r="I103" s="29" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="J103" s="10" t="s">
         <v>50</v>
@@ -14864,7 +14975,7 @@
         <v>13</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G104" s="45" t="s">
         <v>47</v>
@@ -14873,7 +14984,7 @@
         <v>48</v>
       </c>
       <c r="I104" s="29" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="J104" s="10" t="s">
         <v>50</v>
@@ -14896,16 +15007,16 @@
         <v>13</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G105" s="45" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="H105" s="45" t="s">
         <v>48</v>
       </c>
       <c r="I105" s="29" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="J105" s="10" t="s">
         <v>129</v>
@@ -14928,7 +15039,7 @@
         <v>13</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G106" s="45" t="s">
         <v>47</v>
@@ -14937,7 +15048,7 @@
         <v>22</v>
       </c>
       <c r="I106" s="29" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="J106" s="10" t="s">
         <v>50</v>
@@ -14951,7 +15062,7 @@
         <v>46230</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D107" s="55">
         <v>46230</v>
@@ -14967,7 +15078,7 @@
         <v>210</v>
       </c>
       <c r="I107" s="36" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="J107" s="10" t="s">
         <v>50</v>
@@ -14981,7 +15092,7 @@
         <v>46231</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D108" s="55">
         <v>46231</v>
@@ -14999,7 +15110,7 @@
         <v>210</v>
       </c>
       <c r="I108" s="29" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J108" s="10" t="s">
         <v>50</v>
@@ -15012,7 +15123,7 @@
       <c r="G109" s="45"/>
       <c r="H109" s="45"/>
       <c r="I109" s="29" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -15022,7 +15133,7 @@
       <c r="G110" s="45"/>
       <c r="H110" s="45"/>
       <c r="I110" s="29" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -15042,7 +15153,7 @@
         <v>13</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G111" s="45" t="s">
         <v>47</v>
@@ -15051,7 +15162,7 @@
         <v>52</v>
       </c>
       <c r="I111" s="29" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="J111" s="10" t="s">
         <v>129</v>
@@ -15062,10 +15173,10 @@
         <v>86</v>
       </c>
       <c r="B112" s="45" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D112" s="55">
         <v>46234</v>
@@ -15074,7 +15185,7 @@
         <v>13</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G112" s="45" t="s">
         <v>125</v>
@@ -15083,7 +15194,7 @@
         <v>48</v>
       </c>
       <c r="I112" s="29" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="J112" s="10" t="s">
         <v>50</v>
@@ -15106,7 +15217,7 @@
         <v>13</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="G113" s="45" t="s">
         <v>47</v>
@@ -15115,7 +15226,7 @@
         <v>43</v>
       </c>
       <c r="I113" s="29" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="J113" s="10" t="s">
         <v>129</v>
@@ -15147,7 +15258,7 @@
         <v>48</v>
       </c>
       <c r="I114" s="36" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="J114" s="10" t="s">
         <v>50</v>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E81CDD0-A5B0-4DD6-90E6-BD5EEB7ED0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDDFAFD-4CC2-42CE-8225-888BCB8652A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="733">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2201,10 +2201,25 @@
     <t xml:space="preserve">PTW/26-27/003 &amp; </t>
   </si>
   <si>
-    <t>PTW/26-27/015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter Holder- Qty 5 Nos. </t>
+    <t>INV no. -14</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>New Star Engineering Works</t>
+  </si>
+  <si>
+    <t>Water Tank Base, BSHPD-02-MA-01-03-001- Qty 5 Nos. /Water Tank Top bowl, BSHPD-02-MA-01-03-002 - Qty 5 Nos.</t>
+  </si>
+  <si>
+    <t>Clamp Ring for Water Tank, BSHPD-02-MA-01-03-003 - Qty 5 Nos. / RCT Jacket_400, BSHRD-07-MA-02-02-001 -Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>RGT Container_400,BSHRD-07-MA-03-02-001 - Qty 1 Nos. / Sample Tray Container_400, BSHRD-07-MA-04-02-001 - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>RCT Jacket_400 Tooling Cost - Qty 1 Nos. / RGT  Container_400 Tooling cost - Qty 1 Nos. / Sample Tray Container_400 Tooling Cost - Qty 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -8191,19 +8206,22 @@
         <v>726</v>
       </c>
       <c r="D212" s="26">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="E212" s="22" t="s">
-        <v>41</v>
+        <v>727</v>
       </c>
       <c r="F212" s="49" t="s">
-        <v>42</v>
+        <v>728</v>
       </c>
       <c r="G212" s="22" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="H212" s="36" t="s">
-        <v>727</v>
+        <v>729</v>
+      </c>
+      <c r="I212" s="22" t="s">
+        <v>50</v>
       </c>
       <c r="M212" s="22" t="s">
         <v>125</v>
@@ -8212,19 +8230,28 @@
     <row r="213" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C213" s="49"/>
       <c r="F213" s="49"/>
-      <c r="H213" s="36"/>
+      <c r="H213" s="36" t="s">
+        <v>730</v>
+      </c>
     </row>
     <row r="214" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C214" s="49"/>
       <c r="F214" s="49"/>
-      <c r="H214" s="36"/>
+      <c r="H214" s="36" t="s">
+        <v>731</v>
+      </c>
     </row>
     <row r="215" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C215" s="49"/>
       <c r="F215" s="49"/>
-      <c r="H215" s="36"/>
+      <c r="H215" s="36" t="s">
+        <v>732</v>
+      </c>
     </row>
     <row r="216" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A216" s="22">
+        <v>161</v>
+      </c>
       <c r="C216" s="49"/>
       <c r="F216" s="49"/>
       <c r="H216" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDDFAFD-4CC2-42CE-8225-888BCB8652A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCF8C0C-10C6-4DD8-864C-96D746236109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCF8C0C-10C6-4DD8-864C-96D746236109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D189652E-3914-49CB-A45B-21EABECFE323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="736">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2220,6 +2220,15 @@
   </si>
   <si>
     <t>RCT Jacket_400 Tooling Cost - Qty 1 Nos. / RGT  Container_400 Tooling cost - Qty 1 Nos. / Sample Tray Container_400 Tooling Cost - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>CRU ManiFold - Qty 3 Nos. / Stirrer UP- DN Moter Wire - Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Science House Laboratories ( Himanshu Sharma)</t>
+  </si>
+  <si>
+    <t>NanoPi M1 Board (For repair) - Qty 2 Nos. / Shortage Component BioSci 50 Instrument</t>
   </si>
 </sst>
 </file>
@@ -15292,28 +15301,100 @@
       </c>
     </row>
     <row r="115" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A115" s="27"/>
-      <c r="B115" s="45"/>
-      <c r="D115" s="45"/>
-      <c r="G115" s="45"/>
-      <c r="H115" s="45"/>
-      <c r="I115" s="29"/>
+      <c r="A115" s="27">
+        <v>89</v>
+      </c>
+      <c r="B115" s="55">
+        <v>46241</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D115" s="55">
+        <v>46241</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="G115" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H115" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="I115" s="29" t="s">
+        <v>733</v>
+      </c>
+      <c r="J115" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="116" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A116" s="27"/>
-      <c r="B116" s="45"/>
-      <c r="D116" s="45"/>
-      <c r="G116" s="45"/>
-      <c r="H116" s="45"/>
-      <c r="I116" s="29"/>
+      <c r="A116" s="27">
+        <v>90</v>
+      </c>
+      <c r="B116" s="55">
+        <v>46241</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D116" s="55">
+        <v>46241</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F116" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="G116" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H116" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I116" s="36" t="s">
+        <v>719</v>
+      </c>
+      <c r="J116" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="117" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A117" s="27"/>
-      <c r="B117" s="45"/>
-      <c r="D117" s="45"/>
-      <c r="G117" s="45"/>
-      <c r="H117" s="45"/>
-      <c r="I117" s="29"/>
+      <c r="A117" s="27">
+        <v>91</v>
+      </c>
+      <c r="B117" s="55">
+        <v>46242</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D117" s="55">
+        <v>46242</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="G117" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H117" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I117" s="29" t="s">
+        <v>735</v>
+      </c>
+      <c r="J117" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="118" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A118" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D189652E-3914-49CB-A45B-21EABECFE323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DBEB6E-9B0A-4345-973F-038E8888E4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="737">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2229,6 +2229,9 @@
   </si>
   <si>
     <t>NanoPi M1 Board (For repair) - Qty 2 Nos. / Shortage Component BioSci 50 Instrument</t>
+  </si>
+  <si>
+    <t>Memory Card 64 GB- Qty 1 No.</t>
   </si>
 </sst>
 </file>
@@ -8261,9 +8264,30 @@
       <c r="A216" s="22">
         <v>161</v>
       </c>
-      <c r="C216" s="49"/>
-      <c r="F216" s="49"/>
-      <c r="H216" s="36"/>
+      <c r="B216" s="58">
+        <v>46246</v>
+      </c>
+      <c r="C216" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D216" s="26">
+        <v>46246</v>
+      </c>
+      <c r="E216" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F216" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="G216" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H216" s="36" t="s">
+        <v>644</v>
+      </c>
+      <c r="I216" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="217" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C217" s="49"/>
@@ -15397,15 +15421,41 @@
       </c>
     </row>
     <row r="118" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A118" s="27"/>
-      <c r="B118" s="45"/>
-      <c r="D118" s="45"/>
-      <c r="G118" s="45"/>
-      <c r="H118" s="45"/>
-      <c r="I118" s="29"/>
+      <c r="A118" s="27">
+        <v>92</v>
+      </c>
+      <c r="B118" s="55">
+        <v>46247</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D118" s="55">
+        <v>46247</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="G118" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H118" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I118" s="29" t="s">
+        <v>736</v>
+      </c>
+      <c r="J118" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="119" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A119" s="27"/>
+      <c r="A119" s="27">
+        <v>93</v>
+      </c>
       <c r="B119" s="45"/>
       <c r="D119" s="45"/>
       <c r="G119" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DBEB6E-9B0A-4345-973F-038E8888E4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB25C70-F02F-4728-A0F3-F6B995B2C3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="742">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2232,6 +2232,21 @@
   </si>
   <si>
     <t>Memory Card 64 GB- Qty 1 No.</t>
+  </si>
+  <si>
+    <t>AWB# 7X110886272</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Photometer Halogen Lamp Assy Bioelab FA 6V/10W - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>DC0070</t>
+  </si>
+  <si>
+    <t>BioSci HealrhCare</t>
+  </si>
+  <si>
+    <t>Biosci50 Power Supply PCB (Return) - Qty 5 Nos. / NanoPi PCB (Return) - Qty 1 Nos. / Photometer PCB (Return)- Qty 1 No</t>
   </si>
 </sst>
 </file>
@@ -8290,9 +8305,33 @@
       </c>
     </row>
     <row r="217" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C217" s="49"/>
-      <c r="F217" s="49"/>
-      <c r="H217" s="36"/>
+      <c r="A217" s="22">
+        <v>163</v>
+      </c>
+      <c r="B217" s="26">
+        <v>46251</v>
+      </c>
+      <c r="C217" s="49" t="s">
+        <v>737</v>
+      </c>
+      <c r="D217" s="26">
+        <v>46247</v>
+      </c>
+      <c r="E217" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F217" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G217" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H217" s="36" t="s">
+        <v>738</v>
+      </c>
+      <c r="I217" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="218" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C218" s="49"/>
@@ -12149,8 +12188,9 @@
     <col min="6" max="6" width="48.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.625" style="38" customWidth="1"/>
     <col min="8" max="8" width="24" style="38" customWidth="1"/>
-    <col min="9" max="9" width="122.5" style="2" customWidth="1"/>
-    <col min="10" max="11" width="14.125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="124" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="19.25" style="2" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="20" style="2" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="18.75" style="2" customWidth="1"/>
@@ -15456,11 +15496,33 @@
       <c r="A119" s="27">
         <v>93</v>
       </c>
-      <c r="B119" s="45"/>
-      <c r="D119" s="45"/>
-      <c r="G119" s="45"/>
-      <c r="H119" s="45"/>
-      <c r="I119" s="29"/>
+      <c r="B119" s="55">
+        <v>46251</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="D119" s="55">
+        <v>46248</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="G119" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H119" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I119" s="29" t="s">
+        <v>741</v>
+      </c>
+      <c r="J119" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="120" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A120" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB25C70-F02F-4728-A0F3-F6B995B2C3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BE3FB9-D26E-406E-8030-8A01C7F00A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="746">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2247,6 +2247,18 @@
   </si>
   <si>
     <t>Biosci50 Power Supply PCB (Return) - Qty 5 Nos. / NanoPi PCB (Return) - Qty 1 Nos. / Photometer PCB (Return)- Qty 1 No</t>
+  </si>
+  <si>
+    <t>2499303471 (Blinkit)</t>
+  </si>
+  <si>
+    <t>Blinkit</t>
+  </si>
+  <si>
+    <t>Blinkit Commerce Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>Digitek USB Pen Drive V2.0(32 GB) - Qty 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -8334,9 +8346,33 @@
       </c>
     </row>
     <row r="218" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C218" s="49"/>
-      <c r="F218" s="49"/>
-      <c r="H218" s="36"/>
+      <c r="A218" s="22">
+        <v>164</v>
+      </c>
+      <c r="B218" s="26">
+        <v>46251</v>
+      </c>
+      <c r="C218" s="49" t="s">
+        <v>742</v>
+      </c>
+      <c r="D218" s="26">
+        <v>46251</v>
+      </c>
+      <c r="E218" s="22" t="s">
+        <v>743</v>
+      </c>
+      <c r="F218" s="49" t="s">
+        <v>744</v>
+      </c>
+      <c r="G218" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H218" s="36" t="s">
+        <v>745</v>
+      </c>
+      <c r="I218" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="219" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C219" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BE3FB9-D26E-406E-8030-8A01C7F00A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389B9057-43BF-4D91-84B8-44BE1110F015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="746">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2611,7 +2611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2844,6 +2844,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15561,12 +15564,36 @@
       </c>
     </row>
     <row r="120" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A120" s="27"/>
-      <c r="B120" s="45"/>
-      <c r="D120" s="45"/>
-      <c r="G120" s="45"/>
-      <c r="H120" s="45"/>
-      <c r="I120" s="29"/>
+      <c r="A120" s="27">
+        <v>94</v>
+      </c>
+      <c r="B120" s="55">
+        <v>46252</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D120" s="55">
+        <v>46252</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G120" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H120" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I120" s="85" t="s">
+        <v>738</v>
+      </c>
+      <c r="J120" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="121" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A121" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389B9057-43BF-4D91-84B8-44BE1110F015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B015D0F-E3E3-4859-8427-E8F700775D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="750">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2259,6 +2259,18 @@
   </si>
   <si>
     <t>Digitek USB Pen Drive V2.0(32 GB) - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>DC No- 307</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 19 August 2026</t>
+  </si>
+  <si>
+    <t>NU-TEK Optics</t>
+  </si>
+  <si>
+    <t>BSHPD-01-MA-03-02-010 - Dia 10mm, Thickness 3.8mm, Mat : Fused Silica - Qty 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -2785,6 +2797,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2844,9 +2859,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3148,21 +3160,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>360</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="67"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="68"/>
     </row>
     <row r="2" spans="1:13" s="21" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="17">
@@ -3195,10 +3207,10 @@
       <c r="J2" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="68" t="s">
+      <c r="K2" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="69"/>
+      <c r="L2" s="70"/>
       <c r="M2" s="20" t="s">
         <v>10</v>
       </c>
@@ -3329,7 +3341,7 @@
       <c r="F7" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="70" t="s">
+      <c r="G7" s="71" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="37" t="s">
@@ -3344,7 +3356,7 @@
       <c r="C8" s="49"/>
       <c r="D8" s="26"/>
       <c r="F8" s="49"/>
-      <c r="G8" s="71"/>
+      <c r="G8" s="72"/>
       <c r="H8" s="36" t="s">
         <v>60</v>
       </c>
@@ -8378,9 +8390,33 @@
       </c>
     </row>
     <row r="219" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C219" s="49"/>
-      <c r="F219" s="49"/>
-      <c r="H219" s="36"/>
+      <c r="A219" s="22">
+        <v>165</v>
+      </c>
+      <c r="B219" s="26" t="s">
+        <v>747</v>
+      </c>
+      <c r="C219" s="49" t="s">
+        <v>746</v>
+      </c>
+      <c r="D219" s="26">
+        <v>46251</v>
+      </c>
+      <c r="E219" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F219" s="49" t="s">
+        <v>748</v>
+      </c>
+      <c r="G219" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H219" s="36" t="s">
+        <v>749</v>
+      </c>
+      <c r="I219" s="22" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="220" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C220" s="49"/>
@@ -12238,23 +12274,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="74"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="75"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -12320,28 +12356,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="70">
+      <c r="A4" s="71">
         <v>1</v>
       </c>
-      <c r="B4" s="81">
+      <c r="B4" s="82">
         <v>46098</v>
       </c>
-      <c r="C4" s="78" t="s">
+      <c r="C4" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="81">
+      <c r="D4" s="82">
         <v>46098</v>
       </c>
-      <c r="E4" s="78" t="s">
+      <c r="E4" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="78" t="s">
+      <c r="F4" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="75" t="s">
+      <c r="G4" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="75" t="s">
+      <c r="H4" s="76" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="32" t="s">
@@ -12361,14 +12397,14 @@
       </c>
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A5" s="84"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
+      <c r="A5" s="85"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
       <c r="I5" s="32" t="s">
         <v>24</v>
       </c>
@@ -12386,14 +12422,14 @@
       </c>
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A6" s="84"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
+      <c r="A6" s="85"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
       <c r="I6" s="32" t="s">
         <v>25</v>
       </c>
@@ -12411,14 +12447,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="71"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
       <c r="I7" s="32" t="s">
         <v>30</v>
       </c>
@@ -15588,7 +15624,7 @@
       <c r="H120" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="I120" s="85" t="s">
+      <c r="I120" s="65" t="s">
         <v>738</v>
       </c>
       <c r="J120" s="10" t="s">

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B015D0F-E3E3-4859-8427-E8F700775D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D460E74-5015-439B-8C67-7FF2BB43844E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="750">
   <si>
     <t>Sr No.</t>
   </si>
@@ -8417,6 +8417,9 @@
       <c r="I219" s="22" t="s">
         <v>129</v>
       </c>
+      <c r="M219" s="22" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="220" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C220" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D460E74-5015-439B-8C67-7FF2BB43844E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D37D642-CDBC-4751-8643-6A65871A5FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="752">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2271,6 +2271,12 @@
   </si>
   <si>
     <t>BSHPD-01-MA-03-02-010 - Dia 10mm, Thickness 3.8mm, Mat : Fused Silica - Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>AM/PP/0023/2627</t>
+  </si>
+  <si>
+    <t>Laundry System Value - Qty 2 Nos. / Transparent Cup - Qty 10 Nos.</t>
   </si>
 </sst>
 </file>
@@ -15635,12 +15641,36 @@
       </c>
     </row>
     <row r="121" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A121" s="27"/>
-      <c r="B121" s="45"/>
-      <c r="D121" s="45"/>
-      <c r="G121" s="45"/>
-      <c r="H121" s="45"/>
-      <c r="I121" s="29"/>
+      <c r="A121" s="27">
+        <v>95</v>
+      </c>
+      <c r="B121" s="55">
+        <v>46254</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>750</v>
+      </c>
+      <c r="D121" s="55">
+        <v>46254</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G121" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H121" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I121" s="29" t="s">
+        <v>751</v>
+      </c>
+      <c r="J121" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="122" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A122" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D37D642-CDBC-4751-8643-6A65871A5FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1A0D11-EB35-4083-BC31-07EB135FFC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="754">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2277,6 +2277,12 @@
   </si>
   <si>
     <t>Laundry System Value - Qty 2 Nos. / Transparent Cup - Qty 10 Nos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCT Continer -Qty 2 / Dry Chip - Qty 103 /  SS Tube - Qty 50 / Black Shit Acoflex Foam Strip For Pump - Qty 55 </t>
+  </si>
+  <si>
+    <t>Sure HealthCare</t>
   </si>
 </sst>
 </file>
@@ -15673,12 +15679,36 @@
       </c>
     </row>
     <row r="122" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A122" s="27"/>
-      <c r="B122" s="45"/>
-      <c r="D122" s="45"/>
-      <c r="G122" s="45"/>
-      <c r="H122" s="45"/>
-      <c r="I122" s="29"/>
+      <c r="A122" s="27">
+        <v>96</v>
+      </c>
+      <c r="B122" s="55">
+        <v>46256</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D122" s="55">
+        <v>46256</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="G122" s="45" t="s">
+        <v>753</v>
+      </c>
+      <c r="H122" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I122" s="29" t="s">
+        <v>752</v>
+      </c>
+      <c r="J122" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="123" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A123" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1A0D11-EB35-4083-BC31-07EB135FFC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B56279-A55C-49CD-97DF-4D0E3A06C0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
     <sheet name="Outward" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="758">
   <si>
     <t>Sr No.</t>
   </si>
@@ -863,9 +863,6 @@
     <t>AM/PP/0011/2627</t>
   </si>
   <si>
-    <t>RTC Temperature Sensor - Qty 1 Nos.</t>
-  </si>
-  <si>
     <t>Reckon Diagnostics pvt Ltd</t>
   </si>
   <si>
@@ -2283,6 +2280,21 @@
   </si>
   <si>
     <t>Sure HealthCare</t>
+  </si>
+  <si>
+    <t>RCT Temperature Sensor - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Challan No. 950</t>
+  </si>
+  <si>
+    <t>Tempo</t>
+  </si>
+  <si>
+    <t>Mapel Moulds &amp; Dies (India) Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>Reagent Tray Bottom- Qty 12 Nos. / Test Tube  Holder - Qty 135 Nos. / Outer Cover- Qty 03 / Base Plate - Qty 02 / Switch Cover- Qty 3 / Flowcell cover- Qty 3</t>
   </si>
 </sst>
 </file>
@@ -3173,7 +3185,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
       <c r="A1" s="66" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B1" s="67"/>
       <c r="C1" s="67"/>
@@ -3211,7 +3223,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="48" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>5</v>
@@ -4300,7 +4312,7 @@
         <v>46128</v>
       </c>
       <c r="C51" s="49" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D51" s="26">
         <v>46126</v>
@@ -4393,7 +4405,7 @@
         <v>46134</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D54" s="26">
         <v>46133</v>
@@ -4422,7 +4434,7 @@
         <v>46136</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D55" s="26">
         <v>46135</v>
@@ -4437,7 +4449,7 @@
         <v>45</v>
       </c>
       <c r="H55" s="36" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I55" s="22" t="s">
         <v>50</v>
@@ -4612,7 +4624,7 @@
         <v>46142</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D62" s="26">
         <v>46140</v>
@@ -4627,7 +4639,7 @@
         <v>45</v>
       </c>
       <c r="H62" s="36" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I62" s="22" t="s">
         <v>50</v>
@@ -4641,7 +4653,7 @@
         <v>46142</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D63" s="26">
         <v>46140</v>
@@ -4650,13 +4662,13 @@
         <v>67</v>
       </c>
       <c r="F63" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G63" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H63" s="36" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I63" s="22" t="s">
         <v>50</v>
@@ -4670,7 +4682,7 @@
         <v>46146</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D64" s="26">
         <v>46146</v>
@@ -4679,13 +4691,13 @@
         <v>67</v>
       </c>
       <c r="F64" s="49" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G64" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H64" s="36" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I64" s="22" t="s">
         <v>50</v>
@@ -4708,13 +4720,13 @@
         <v>37</v>
       </c>
       <c r="F65" s="49" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G65" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H65" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I65" s="22" t="s">
         <v>50</v>
@@ -4743,7 +4755,7 @@
         <v>45</v>
       </c>
       <c r="H66" s="36" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I66" s="22" t="s">
         <v>50</v>
@@ -4757,7 +4769,7 @@
         <v>46146</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D67" s="26">
         <v>46142</v>
@@ -4766,13 +4778,13 @@
         <v>64</v>
       </c>
       <c r="F67" s="49" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G67" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="36" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I67" s="22" t="s">
         <v>50</v>
@@ -4786,7 +4798,7 @@
         <v>46146</v>
       </c>
       <c r="C68" s="49" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D68" s="26">
         <v>46142</v>
@@ -4801,10 +4813,10 @@
         <v>45</v>
       </c>
       <c r="H68" s="36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -4812,21 +4824,21 @@
       <c r="C69" s="49"/>
       <c r="F69" s="49"/>
       <c r="H69" s="36" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C70" s="49"/>
       <c r="F70" s="49"/>
       <c r="H70" s="36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="71" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C71" s="49"/>
       <c r="F71" s="49"/>
       <c r="H71" s="36" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="72" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -4843,19 +4855,19 @@
         <v>46144</v>
       </c>
       <c r="E72" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="F72" s="49" t="s">
         <v>310</v>
       </c>
-      <c r="F72" s="49" t="s">
+      <c r="G72" s="22" t="s">
         <v>311</v>
       </c>
-      <c r="G72" s="22" t="s">
+      <c r="H72" s="36" t="s">
         <v>312</v>
       </c>
-      <c r="H72" s="36" t="s">
-        <v>313</v>
-      </c>
       <c r="I72" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -4881,7 +4893,7 @@
         <v>45</v>
       </c>
       <c r="H73" s="36" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I73" s="22" t="s">
         <v>50</v>
@@ -4895,7 +4907,7 @@
         <v>46146</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D74" s="26">
         <v>46142</v>
@@ -4904,13 +4916,13 @@
         <v>37</v>
       </c>
       <c r="F74" s="49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G74" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H74" s="36" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I74" s="22" t="s">
         <v>50</v>
@@ -4924,25 +4936,25 @@
         <v>46147</v>
       </c>
       <c r="C75" s="49" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D75" s="26">
         <v>46142</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F75" s="49" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G75" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="36" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="76" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -4953,16 +4965,16 @@
         <v>46147</v>
       </c>
       <c r="C76" s="49" t="s">
+        <v>322</v>
+      </c>
+      <c r="F76" s="49" t="s">
         <v>323</v>
-      </c>
-      <c r="F76" s="49" t="s">
-        <v>324</v>
       </c>
       <c r="G76" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H76" s="36" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I76" s="22" t="s">
         <v>50</v>
@@ -4976,7 +4988,7 @@
         <v>46147</v>
       </c>
       <c r="C77" s="49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D77" s="26">
         <v>46143</v>
@@ -4985,13 +4997,13 @@
         <v>78</v>
       </c>
       <c r="F77" s="49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G77" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="36" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I77" s="22" t="s">
         <v>50</v>
@@ -5005,7 +5017,7 @@
         <v>46147</v>
       </c>
       <c r="C78" s="49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D78" s="26">
         <v>46143</v>
@@ -5014,13 +5026,13 @@
         <v>78</v>
       </c>
       <c r="F78" s="49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G78" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="36" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I78" s="22" t="s">
         <v>50</v>
@@ -5034,7 +5046,7 @@
         <v>46148</v>
       </c>
       <c r="C79" s="49" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D79" s="26">
         <v>46142</v>
@@ -5043,13 +5055,13 @@
         <v>64</v>
       </c>
       <c r="F79" s="49" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G79" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H79" s="36" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I79" s="22" t="s">
         <v>185</v>
@@ -5063,7 +5075,7 @@
         <v>46148</v>
       </c>
       <c r="C80" s="49" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D80" s="26">
         <v>46143</v>
@@ -5078,35 +5090,35 @@
         <v>127</v>
       </c>
       <c r="H80" s="36" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C81" s="49"/>
       <c r="F81" s="49"/>
       <c r="H81" s="36" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C82" s="49"/>
       <c r="F82" s="49"/>
       <c r="H82" s="36" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C83" s="49"/>
       <c r="F83" s="49"/>
       <c r="H83" s="36" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C84" s="49"/>
       <c r="F84" s="49"/>
       <c r="H84" s="36" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5117,7 +5129,7 @@
         <v>46149</v>
       </c>
       <c r="C85" s="49" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D85" s="26">
         <v>46147</v>
@@ -5126,13 +5138,13 @@
         <v>102</v>
       </c>
       <c r="F85" s="49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G85" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H85" s="36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I85" s="22" t="s">
         <v>50</v>
@@ -5146,19 +5158,19 @@
         <v>46149</v>
       </c>
       <c r="C86" s="49" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D86" s="26">
         <v>46142</v>
       </c>
       <c r="E86" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="F86" s="49" t="s">
         <v>356</v>
       </c>
-      <c r="F86" s="49" t="s">
+      <c r="H86" s="36" t="s">
         <v>357</v>
-      </c>
-      <c r="H86" s="36" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5167,7 +5179,7 @@
       <c r="D87" s="26"/>
       <c r="F87" s="49"/>
       <c r="H87" s="36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5178,7 +5190,7 @@
         <v>46149</v>
       </c>
       <c r="C88" s="49" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D88" s="26">
         <v>46142</v>
@@ -5187,13 +5199,13 @@
         <v>64</v>
       </c>
       <c r="F88" s="49" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G88" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H88" s="36" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I88" s="22" t="s">
         <v>50</v>
@@ -5203,7 +5215,7 @@
       <c r="C89" s="49"/>
       <c r="F89" s="49"/>
       <c r="H89" s="36" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="90" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5214,7 +5226,7 @@
         <v>46149</v>
       </c>
       <c r="C90" s="49" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D90" s="26">
         <v>46144</v>
@@ -5223,13 +5235,13 @@
         <v>64</v>
       </c>
       <c r="F90" s="49" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G90" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H90" s="36" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I90" s="22" t="s">
         <v>50</v>
@@ -5252,13 +5264,13 @@
         <v>251</v>
       </c>
       <c r="F91" s="49" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G91" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H91" s="36" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I91" s="22" t="s">
         <v>50</v>
@@ -5268,21 +5280,21 @@
       <c r="C92" s="49"/>
       <c r="F92" s="49"/>
       <c r="H92" s="36" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="93" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C93" s="49"/>
       <c r="F93" s="49"/>
       <c r="H93" s="36" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="94" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C94" s="49"/>
       <c r="F94" s="49"/>
       <c r="H94" s="36" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="95" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5302,16 +5314,16 @@
         <v>37</v>
       </c>
       <c r="F95" s="49" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G95" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="36" t="s">
+        <v>376</v>
+      </c>
+      <c r="I95" s="22" t="s">
         <v>377</v>
-      </c>
-      <c r="I95" s="22" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="96" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5322,7 +5334,7 @@
         <v>46150</v>
       </c>
       <c r="C96" s="49" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D96" s="26">
         <v>46149</v>
@@ -5331,13 +5343,13 @@
         <v>102</v>
       </c>
       <c r="F96" s="49" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G96" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H96" s="36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I96" s="22" t="s">
         <v>50</v>
@@ -5351,19 +5363,19 @@
         <v>46151</v>
       </c>
       <c r="C97" s="49" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D97" s="26">
         <v>46150</v>
       </c>
       <c r="F97" s="49" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G97" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H97" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I97" s="22" t="s">
         <v>50</v>
@@ -5377,7 +5389,7 @@
         <v>46153</v>
       </c>
       <c r="C98" s="49" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D98" s="26">
         <v>46150</v>
@@ -5386,13 +5398,13 @@
         <v>67</v>
       </c>
       <c r="F98" s="49" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G98" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I98" s="22" t="s">
         <v>50</v>
@@ -5418,10 +5430,10 @@
         <v>42</v>
       </c>
       <c r="G99" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="H99" s="36" t="s">
         <v>389</v>
-      </c>
-      <c r="H99" s="36" t="s">
-        <v>390</v>
       </c>
       <c r="I99" s="22" t="s">
         <v>50</v>
@@ -5435,7 +5447,7 @@
         <v>46155</v>
       </c>
       <c r="C100" s="49" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D100" s="26">
         <v>46150</v>
@@ -5444,13 +5456,13 @@
         <v>64</v>
       </c>
       <c r="F100" s="49" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G100" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="36" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I100" s="22" t="s">
         <v>50</v>
@@ -5464,7 +5476,7 @@
         <v>46156</v>
       </c>
       <c r="C101" s="49" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D101" s="26">
         <v>46154</v>
@@ -5473,13 +5485,13 @@
         <v>102</v>
       </c>
       <c r="F101" s="49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G101" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H101" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I101" s="22" t="s">
         <v>50</v>
@@ -5508,7 +5520,7 @@
         <v>45</v>
       </c>
       <c r="H102" s="36" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I102" s="22" t="s">
         <v>50</v>
@@ -5522,7 +5534,7 @@
         <v>46160</v>
       </c>
       <c r="C103" s="49" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D103" s="26">
         <v>46157</v>
@@ -5531,13 +5543,13 @@
         <v>67</v>
       </c>
       <c r="F103" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G103" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H103" s="36" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I103" s="22" t="s">
         <v>129</v>
@@ -5551,7 +5563,7 @@
         <v>46160</v>
       </c>
       <c r="C104" s="49" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D104" s="26">
         <v>46158</v>
@@ -5560,13 +5572,13 @@
         <v>78</v>
       </c>
       <c r="F104" s="49" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G104" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H104" s="36" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I104" s="22" t="s">
         <v>50</v>
@@ -5580,7 +5592,7 @@
         <v>46160</v>
       </c>
       <c r="C105" s="49" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D105" s="26">
         <v>46157</v>
@@ -5589,13 +5601,13 @@
         <v>41</v>
       </c>
       <c r="F105" s="49" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G105" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H105" s="36" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I105" s="22" t="s">
         <v>50</v>
@@ -5609,7 +5621,7 @@
         <v>46163</v>
       </c>
       <c r="C106" s="49" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D106" s="26">
         <v>46161</v>
@@ -5618,13 +5630,13 @@
         <v>102</v>
       </c>
       <c r="F106" s="49" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G106" s="22" t="s">
         <v>127</v>
       </c>
       <c r="H106" s="36" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I106" s="22" t="s">
         <v>50</v>
@@ -5647,13 +5659,13 @@
         <v>37</v>
       </c>
       <c r="F107" s="49" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G107" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H107" s="36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I107" s="22" t="s">
         <v>50</v>
@@ -5669,13 +5681,13 @@
       <c r="C108" s="49"/>
       <c r="D108" s="26"/>
       <c r="F108" s="49" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G108" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H108" s="36" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I108" s="22" t="s">
         <v>129</v>
@@ -5689,22 +5701,22 @@
         <v>46167</v>
       </c>
       <c r="C109" s="49" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D109" s="26">
         <v>46165</v>
       </c>
       <c r="E109" s="22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F109" s="49" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G109" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H109" s="36" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I109" s="22" t="s">
         <v>185</v>
@@ -5715,10 +5727,10 @@
         <v>78</v>
       </c>
       <c r="B110" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="C110" s="49" t="s">
         <v>426</v>
-      </c>
-      <c r="C110" s="49" t="s">
-        <v>427</v>
       </c>
       <c r="D110" s="26">
         <v>46165</v>
@@ -5727,13 +5739,13 @@
         <v>102</v>
       </c>
       <c r="F110" s="49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G110" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H110" s="36" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I110" s="22" t="s">
         <v>50</v>
@@ -5757,7 +5769,7 @@
         <v>45</v>
       </c>
       <c r="H111" s="36" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I111" s="22" t="s">
         <v>50</v>
@@ -5771,7 +5783,7 @@
         <v>46167</v>
       </c>
       <c r="C112" s="49" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D112" s="26">
         <v>46164</v>
@@ -5780,21 +5792,21 @@
         <v>67</v>
       </c>
       <c r="F112" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G112" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H112" s="36" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I112" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="113" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C113" s="49" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D113" s="26">
         <v>46164</v>
@@ -5803,40 +5815,40 @@
         <v>67</v>
       </c>
       <c r="F113" s="49" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G113" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H113" s="36" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I113" s="22" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="114" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C114" s="49"/>
       <c r="F114" s="49"/>
       <c r="H114" s="36" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I114" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="115" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C115" s="49"/>
       <c r="F115" s="49"/>
       <c r="H115" s="36" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="116" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C116" s="49"/>
       <c r="F116" s="49"/>
       <c r="H116" s="36" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="117" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5847,22 +5859,22 @@
         <v>46168</v>
       </c>
       <c r="C117" s="49" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D117" s="26">
         <v>46167</v>
       </c>
       <c r="E117" s="22" t="s">
+        <v>441</v>
+      </c>
+      <c r="F117" s="49" t="s">
         <v>442</v>
-      </c>
-      <c r="F117" s="49" t="s">
-        <v>443</v>
       </c>
       <c r="G117" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H117" s="36" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="118" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5882,13 +5894,13 @@
         <v>37</v>
       </c>
       <c r="F118" s="49" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G118" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H118" s="36" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I118" s="22" t="s">
         <v>50</v>
@@ -5902,7 +5914,7 @@
         <v>46169</v>
       </c>
       <c r="C119" s="49" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D119" s="26">
         <v>46163</v>
@@ -5911,19 +5923,19 @@
         <v>37</v>
       </c>
       <c r="F119" s="49" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G119" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H119" s="36" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I119" s="22" t="s">
         <v>50</v>
       </c>
       <c r="J119" s="22" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="120" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -5931,10 +5943,10 @@
         <v>84</v>
       </c>
       <c r="B120" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="C120" s="49" t="s">
         <v>448</v>
-      </c>
-      <c r="C120" s="49" t="s">
-        <v>449</v>
       </c>
       <c r="D120" s="26">
         <v>46167</v>
@@ -5949,7 +5961,7 @@
         <v>45</v>
       </c>
       <c r="H120" s="36" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I120" s="22" t="s">
         <v>50</v>
@@ -5963,7 +5975,7 @@
         <v>46169</v>
       </c>
       <c r="C121" s="49" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D121" s="26">
         <v>46166</v>
@@ -5978,7 +5990,7 @@
         <v>45</v>
       </c>
       <c r="H121" s="36" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I121" s="22" t="s">
         <v>50</v>
@@ -5992,7 +6004,7 @@
         <v>46169</v>
       </c>
       <c r="C122" s="49" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D122" s="26">
         <v>46165</v>
@@ -6001,13 +6013,13 @@
         <v>78</v>
       </c>
       <c r="F122" s="49" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G122" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H122" s="36" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="123" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6033,7 +6045,7 @@
         <v>22</v>
       </c>
       <c r="H123" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I123" s="22" t="s">
         <v>50</v>
@@ -6047,7 +6059,7 @@
         <v>46170</v>
       </c>
       <c r="C124" s="49" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D124" s="26">
         <v>46168</v>
@@ -6056,13 +6068,13 @@
         <v>102</v>
       </c>
       <c r="F124" s="49" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G124" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H124" s="36" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I124" s="22" t="s">
         <v>50</v>
@@ -6076,7 +6088,7 @@
         <v>46170</v>
       </c>
       <c r="C125" s="49" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D125" s="26">
         <v>46169</v>
@@ -6085,13 +6097,13 @@
         <v>102</v>
       </c>
       <c r="F125" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G125" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H125" s="36" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I125" s="22" t="s">
         <v>50</v>
@@ -6114,13 +6126,13 @@
         <v>78</v>
       </c>
       <c r="F126" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G126" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H126" s="36" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I126" s="22" t="s">
         <v>185</v>
@@ -6137,7 +6149,7 @@
         <v>47268</v>
       </c>
       <c r="C127" s="49" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D127" s="26">
         <v>46170</v>
@@ -6146,13 +6158,13 @@
         <v>41</v>
       </c>
       <c r="F127" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G127" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H127" s="36" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I127" s="22" t="s">
         <v>50</v>
@@ -6175,13 +6187,13 @@
         <v>13</v>
       </c>
       <c r="F128" s="49" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G128" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H128" s="36" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I128" s="22" t="s">
         <v>50</v>
@@ -6213,7 +6225,7 @@
         <v>45</v>
       </c>
       <c r="H129" s="36" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I129" s="22" t="s">
         <v>50</v>
@@ -6227,7 +6239,7 @@
         <v>46174</v>
       </c>
       <c r="C130" s="49" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D130" s="26">
         <v>46172</v>
@@ -6236,13 +6248,13 @@
         <v>102</v>
       </c>
       <c r="F130" s="49" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G130" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H130" s="36" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I130" s="22" t="s">
         <v>50</v>
@@ -6265,13 +6277,13 @@
         <v>13</v>
       </c>
       <c r="F131" s="49" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G131" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H131" s="36" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I131" s="22" t="s">
         <v>50</v>
@@ -6285,7 +6297,7 @@
         <v>46176</v>
       </c>
       <c r="C132" s="49" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D132" s="26">
         <v>46171</v>
@@ -6294,10 +6306,10 @@
         <v>67</v>
       </c>
       <c r="F132" s="49" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H132" s="36" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I132" s="22" t="s">
         <v>50</v>
@@ -6311,13 +6323,13 @@
         <v>46177</v>
       </c>
       <c r="C133" s="49" t="s">
+        <v>485</v>
+      </c>
+      <c r="D133" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="E133" s="22" t="s">
         <v>486</v>
-      </c>
-      <c r="D133" s="22" t="s">
-        <v>490</v>
-      </c>
-      <c r="E133" s="22" t="s">
-        <v>487</v>
       </c>
       <c r="F133" s="49" t="s">
         <v>42</v>
@@ -6326,7 +6338,7 @@
         <v>210</v>
       </c>
       <c r="H133" s="36" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I133" s="22" t="s">
         <v>50</v>
@@ -6349,13 +6361,13 @@
         <v>251</v>
       </c>
       <c r="F134" s="49" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G134" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H134" s="36" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I134" s="22" t="s">
         <v>50</v>
@@ -6369,7 +6381,7 @@
         <v>46181</v>
       </c>
       <c r="C135" s="49" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D135" s="26">
         <v>46178</v>
@@ -6378,13 +6390,13 @@
         <v>67</v>
       </c>
       <c r="F135" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G135" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H135" s="36" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I135" s="22" t="s">
         <v>129</v>
@@ -6398,7 +6410,7 @@
         <v>46181</v>
       </c>
       <c r="C136" s="49" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D136" s="26">
         <v>46178</v>
@@ -6407,13 +6419,13 @@
         <v>67</v>
       </c>
       <c r="F136" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G136" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="36" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I136" s="22" t="s">
         <v>129</v>
@@ -6427,7 +6439,7 @@
         <v>46181</v>
       </c>
       <c r="C137" s="49" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D137" s="26">
         <v>46177</v>
@@ -6436,13 +6448,13 @@
         <v>67</v>
       </c>
       <c r="F137" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G137" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H137" s="36" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I137" s="22" t="s">
         <v>129</v>
@@ -6452,7 +6464,7 @@
       <c r="C138" s="49"/>
       <c r="F138" s="49"/>
       <c r="H138" s="36" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6463,7 +6475,7 @@
         <v>46181</v>
       </c>
       <c r="C139" s="49" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D139" s="26">
         <v>46177</v>
@@ -6472,13 +6484,13 @@
         <v>37</v>
       </c>
       <c r="F139" s="49" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G139" s="22" t="s">
         <v>43</v>
       </c>
       <c r="H139" s="36" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I139" s="22" t="s">
         <v>50</v>
@@ -6491,7 +6503,7 @@
       <c r="C140" s="49"/>
       <c r="F140" s="49"/>
       <c r="H140" s="36" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="141" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6502,7 +6514,7 @@
         <v>46181</v>
       </c>
       <c r="C141" s="49" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D141" s="26">
         <v>46169</v>
@@ -6511,13 +6523,13 @@
         <v>64</v>
       </c>
       <c r="F141" s="49" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G141" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H141" s="36" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I141" s="22" t="s">
         <v>50</v>
@@ -6540,16 +6552,16 @@
         <v>46181</v>
       </c>
       <c r="E142" s="22" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F142" s="49" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G142" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H142" s="36" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I142" s="22" t="s">
         <v>50</v>
@@ -6563,7 +6575,7 @@
         <v>46181</v>
       </c>
       <c r="C143" s="49" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D143" s="26">
         <v>46178</v>
@@ -6572,13 +6584,13 @@
         <v>41</v>
       </c>
       <c r="F143" s="49" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G143" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H143" s="36" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I143" s="22" t="s">
         <v>119</v>
@@ -6595,7 +6607,7 @@
         <v>46182</v>
       </c>
       <c r="C144" s="49" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D144" s="26">
         <v>46181</v>
@@ -6604,13 +6616,13 @@
         <v>41</v>
       </c>
       <c r="F144" s="49" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G144" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H144" s="36" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I144" s="22" t="s">
         <v>50</v>
@@ -6627,7 +6639,7 @@
         <v>46182</v>
       </c>
       <c r="C145" s="49" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D145" s="58">
         <v>46177</v>
@@ -6636,16 +6648,16 @@
         <v>52</v>
       </c>
       <c r="F145" s="49" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G145" s="22" t="s">
         <v>43</v>
       </c>
       <c r="H145" s="36" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I145" s="22" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J145" s="22" t="s">
         <v>47</v>
@@ -6659,7 +6671,7 @@
         <v>46184</v>
       </c>
       <c r="C146" s="49" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D146" s="26">
         <v>46184</v>
@@ -6674,7 +6686,7 @@
         <v>45</v>
       </c>
       <c r="H146" s="36" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="I146" s="22" t="s">
         <v>50</v>
@@ -6694,7 +6706,7 @@
         <v>46184</v>
       </c>
       <c r="C147" s="49" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D147" s="26">
         <v>46182</v>
@@ -6703,13 +6715,13 @@
         <v>67</v>
       </c>
       <c r="F147" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G147" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H147" s="36" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I147" s="22" t="s">
         <v>50</v>
@@ -6729,7 +6741,7 @@
         <v>46185</v>
       </c>
       <c r="C148" s="49" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D148" s="26">
         <v>46184</v>
@@ -6738,22 +6750,22 @@
         <v>102</v>
       </c>
       <c r="F148" s="49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G148" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H148" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I148" s="22" t="s">
         <v>50</v>
       </c>
       <c r="J148" s="22" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M148" s="22" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="149" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6773,13 +6785,13 @@
         <v>37</v>
       </c>
       <c r="F149" s="49" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G149" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H149" s="36" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I149" s="22" t="s">
         <v>50</v>
@@ -6802,13 +6814,13 @@
         <v>37</v>
       </c>
       <c r="F150" s="49" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G150" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="36" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6819,7 +6831,7 @@
         <v>46189</v>
       </c>
       <c r="C151" s="49" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D151" s="26">
         <v>46186</v>
@@ -6828,13 +6840,13 @@
         <v>37</v>
       </c>
       <c r="F151" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G151" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H151" s="36" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I151" s="22" t="s">
         <v>50</v>
@@ -6844,7 +6856,7 @@
       <c r="C152" s="49"/>
       <c r="F152" s="49"/>
       <c r="H152" s="36" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="153" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6855,22 +6867,22 @@
         <v>46190</v>
       </c>
       <c r="C153" s="49" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D153" s="26">
         <v>46168</v>
       </c>
       <c r="E153" s="22" t="s">
+        <v>537</v>
+      </c>
+      <c r="F153" s="49" t="s">
         <v>538</v>
-      </c>
-      <c r="F153" s="49" t="s">
-        <v>539</v>
       </c>
       <c r="G153" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H153" s="36" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6881,7 +6893,7 @@
         <v>46191</v>
       </c>
       <c r="C154" s="49" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D154" s="26">
         <v>46188</v>
@@ -6896,14 +6908,14 @@
         <v>86</v>
       </c>
       <c r="H154" s="36" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="155" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C155" s="49"/>
       <c r="F155" s="49"/>
       <c r="H155" s="36" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I155" s="22" t="s">
         <v>224</v>
@@ -6913,14 +6925,14 @@
       <c r="C156" s="49"/>
       <c r="F156" s="49"/>
       <c r="H156" s="36" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="157" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C157" s="49"/>
       <c r="F157" s="49"/>
       <c r="H157" s="36" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="158" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -6931,7 +6943,7 @@
         <v>46191</v>
       </c>
       <c r="C158" s="49" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D158" s="26">
         <v>46190</v>
@@ -6940,13 +6952,13 @@
         <v>102</v>
       </c>
       <c r="F158" s="49" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G158" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H158" s="36" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I158" s="22" t="s">
         <v>50</v>
@@ -6960,7 +6972,7 @@
         <v>46192</v>
       </c>
       <c r="C159" s="49" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D159" s="26">
         <v>46191</v>
@@ -6975,7 +6987,7 @@
         <v>45</v>
       </c>
       <c r="H159" s="36" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I159" s="22" t="s">
         <v>50</v>
@@ -6989,7 +7001,7 @@
         <v>46203</v>
       </c>
       <c r="C160" s="49" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D160" s="26">
         <v>46198</v>
@@ -7004,38 +7016,38 @@
         <v>86</v>
       </c>
       <c r="H160" s="29" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I160" s="22" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="161" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C161" s="49"/>
       <c r="F161" s="49"/>
       <c r="H161" s="29" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="162" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C162" s="49"/>
       <c r="F162" s="49"/>
       <c r="H162" s="29" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="163" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C163" s="49"/>
       <c r="F163" s="49"/>
       <c r="H163" s="29" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="164" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C164" s="49"/>
       <c r="F164" s="49"/>
       <c r="H164" s="29" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="165" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -7046,7 +7058,7 @@
         <v>46203</v>
       </c>
       <c r="C165" s="49" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D165" s="26">
         <v>46199</v>
@@ -7061,7 +7073,7 @@
         <v>86</v>
       </c>
       <c r="H165" s="36" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="I165" s="22" t="s">
         <v>50</v>
@@ -7075,7 +7087,7 @@
         <v>46204</v>
       </c>
       <c r="C166" s="49" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D166" s="26">
         <v>46200</v>
@@ -7084,13 +7096,13 @@
         <v>37</v>
       </c>
       <c r="F166" s="49" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G166" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H166" s="36" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="I166" s="22" t="s">
         <v>185</v>
@@ -7104,7 +7116,7 @@
         <v>46206</v>
       </c>
       <c r="C167" s="49" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D167" s="26">
         <v>46204</v>
@@ -7119,7 +7131,7 @@
         <v>86</v>
       </c>
       <c r="H167" s="29" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="I167" s="22" t="s">
         <v>50</v>
@@ -7133,7 +7145,7 @@
         <v>46206</v>
       </c>
       <c r="C168" s="49" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D168" s="26">
         <v>46204</v>
@@ -7142,13 +7154,13 @@
         <v>67</v>
       </c>
       <c r="F168" s="49" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G168" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H168" s="36" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I168" s="22" t="s">
         <v>50</v>
@@ -7171,13 +7183,13 @@
         <v>37</v>
       </c>
       <c r="F169" s="49" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G169" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H169" s="36" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="I169" s="22" t="s">
         <v>50</v>
@@ -7191,7 +7203,7 @@
         <v>46206</v>
       </c>
       <c r="C170" s="49" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D170" s="26">
         <v>46199</v>
@@ -7206,7 +7218,7 @@
         <v>86</v>
       </c>
       <c r="H170" s="36" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="I170" s="22" t="s">
         <v>50</v>
@@ -7220,7 +7232,7 @@
         <v>46206</v>
       </c>
       <c r="C171" s="49" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D171" s="26">
         <v>46203</v>
@@ -7229,13 +7241,13 @@
         <v>102</v>
       </c>
       <c r="F171" s="49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G171" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H171" s="36" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I171" s="22" t="s">
         <v>50</v>
@@ -7258,13 +7270,13 @@
         <v>67</v>
       </c>
       <c r="F172" s="49" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G172" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H172" s="29" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I172" s="22" t="s">
         <v>50</v>
@@ -7278,19 +7290,19 @@
         <v>46210</v>
       </c>
       <c r="C173" s="49" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D173" s="26">
         <v>46206</v>
       </c>
       <c r="F173" s="49" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G173" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H173" s="36" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I173" s="22" t="s">
         <v>50</v>
@@ -7304,7 +7316,7 @@
         <v>46213</v>
       </c>
       <c r="C174" s="49" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D174" s="26">
         <v>46212</v>
@@ -7313,13 +7325,13 @@
         <v>251</v>
       </c>
       <c r="F174" s="49" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G174" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="36" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I174" s="22" t="s">
         <v>50</v>
@@ -7333,7 +7345,7 @@
         <v>46217</v>
       </c>
       <c r="C175" s="49" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D175" s="58">
         <v>46210</v>
@@ -7342,13 +7354,13 @@
         <v>56</v>
       </c>
       <c r="F175" s="49" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G175" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H175" s="36" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I175" s="22" t="s">
         <v>50</v>
@@ -7358,7 +7370,7 @@
       <c r="C176" s="49"/>
       <c r="F176" s="49"/>
       <c r="H176" s="36" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="177" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -7369,7 +7381,7 @@
         <v>46217</v>
       </c>
       <c r="C177" s="49" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D177" s="26">
         <v>46204</v>
@@ -7384,7 +7396,7 @@
         <v>45</v>
       </c>
       <c r="H177" s="36" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I177" s="22" t="s">
         <v>50</v>
@@ -7407,13 +7419,13 @@
         <v>37</v>
       </c>
       <c r="F178" s="49" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G178" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H178" s="36" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I178" s="22" t="s">
         <v>50</v>
@@ -7433,13 +7445,13 @@
         <v>46220</v>
       </c>
       <c r="F179" s="49" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G179" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H179" s="36" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I179" s="22" t="s">
         <v>50</v>
@@ -7459,13 +7471,13 @@
         <v>46220</v>
       </c>
       <c r="F180" s="49" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G180" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H180" s="36" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I180" s="22" t="s">
         <v>50</v>
@@ -7479,7 +7491,7 @@
         <v>46223</v>
       </c>
       <c r="C181" s="49" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D181" s="26">
         <v>46219</v>
@@ -7488,13 +7500,13 @@
         <v>102</v>
       </c>
       <c r="F181" s="49" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G181" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="36" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I181" s="22" t="s">
         <v>50</v>
@@ -7508,7 +7520,7 @@
         <v>46223</v>
       </c>
       <c r="C182" s="49" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D182" s="26">
         <v>46219</v>
@@ -7517,13 +7529,13 @@
         <v>37</v>
       </c>
       <c r="F182" s="49" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G182" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H182" s="36" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="I182" s="22" t="s">
         <v>50</v>
@@ -7533,7 +7545,7 @@
       <c r="C183" s="49"/>
       <c r="F183" s="49"/>
       <c r="H183" s="36" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="I183" s="22" t="s">
         <v>50</v>
@@ -7543,21 +7555,21 @@
       <c r="C184" s="49"/>
       <c r="F184" s="49"/>
       <c r="H184" s="36" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="185" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C185" s="49"/>
       <c r="F185" s="49"/>
       <c r="H185" s="36" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="186" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C186" s="49"/>
       <c r="F186" s="49"/>
       <c r="H186" s="36" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -7568,7 +7580,7 @@
         <v>46223</v>
       </c>
       <c r="C187" s="49" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D187" s="26">
         <v>46219</v>
@@ -7577,13 +7589,13 @@
         <v>37</v>
       </c>
       <c r="F187" s="49" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G187" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H187" s="36" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I187" s="22" t="s">
         <v>50</v>
@@ -7593,7 +7605,7 @@
       <c r="C188" s="49"/>
       <c r="F188" s="49"/>
       <c r="H188" s="36" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="189" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -7604,7 +7616,7 @@
         <v>46224</v>
       </c>
       <c r="C189" s="49" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D189" s="26">
         <v>46220</v>
@@ -7619,7 +7631,7 @@
         <v>48</v>
       </c>
       <c r="H189" s="36" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I189" s="22" t="s">
         <v>50</v>
@@ -7633,7 +7645,7 @@
         <v>46226</v>
       </c>
       <c r="C190" s="49" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D190" s="26">
         <v>46224</v>
@@ -7648,7 +7660,7 @@
         <v>45</v>
       </c>
       <c r="H190" s="36" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="I190" s="22" t="s">
         <v>50</v>
@@ -7662,7 +7674,7 @@
         <v>46226</v>
       </c>
       <c r="C191" s="49" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D191" s="26">
         <v>46220</v>
@@ -7677,7 +7689,7 @@
         <v>45</v>
       </c>
       <c r="H191" s="36" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="I191" s="22" t="s">
         <v>50</v>
@@ -7691,7 +7703,7 @@
         <v>46226</v>
       </c>
       <c r="C192" s="49" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D192" s="58">
         <v>46223</v>
@@ -7700,13 +7712,13 @@
         <v>251</v>
       </c>
       <c r="F192" s="49" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G192" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H192" s="36" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I192" s="22" t="s">
         <v>185</v>
@@ -7730,13 +7742,13 @@
         <v>251</v>
       </c>
       <c r="F193" s="49" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G193" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H193" s="36" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I193" s="22" t="s">
         <v>50</v>
@@ -7750,22 +7762,22 @@
         <v>46227</v>
       </c>
       <c r="C194" s="49" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D194" s="26">
         <v>46227</v>
       </c>
       <c r="E194" s="22" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F194" s="49" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G194" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H194" s="36" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I194" s="22" t="s">
         <v>50</v>
@@ -7779,7 +7791,7 @@
         <v>46227</v>
       </c>
       <c r="C195" s="49" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D195" s="26">
         <v>46225</v>
@@ -7794,7 +7806,7 @@
         <v>45</v>
       </c>
       <c r="H195" s="36" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I195" s="22" t="s">
         <v>50</v>
@@ -7817,13 +7829,13 @@
         <v>78</v>
       </c>
       <c r="F196" s="49" t="s">
+        <v>668</v>
+      </c>
+      <c r="G196" s="22" t="s">
         <v>669</v>
       </c>
-      <c r="G196" s="22" t="s">
+      <c r="H196" s="36" t="s">
         <v>670</v>
-      </c>
-      <c r="H196" s="36" t="s">
-        <v>671</v>
       </c>
       <c r="I196" s="22" t="s">
         <v>50</v>
@@ -7837,7 +7849,7 @@
         <v>46231</v>
       </c>
       <c r="C197" s="49" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D197" s="26">
         <v>46226</v>
@@ -7852,7 +7864,7 @@
         <v>45</v>
       </c>
       <c r="H197" s="36" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="I197" s="22" t="s">
         <v>50</v>
@@ -7866,22 +7878,22 @@
         <v>46231</v>
       </c>
       <c r="C198" s="49" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D198" s="26">
         <v>46231</v>
       </c>
       <c r="E198" s="22" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F198" s="49" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G198" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H198" s="36" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="I198" s="22" t="s">
         <v>50</v>
@@ -7895,22 +7907,22 @@
         <v>46232</v>
       </c>
       <c r="C199" s="49" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D199" s="26">
         <v>46232</v>
       </c>
       <c r="E199" s="22" t="s">
+        <v>682</v>
+      </c>
+      <c r="F199" s="49" t="s">
         <v>683</v>
-      </c>
-      <c r="F199" s="49" t="s">
-        <v>684</v>
       </c>
       <c r="G199" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H199" s="36" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="I199" s="22" t="s">
         <v>50</v>
@@ -7924,7 +7936,7 @@
         <v>46233</v>
       </c>
       <c r="C200" s="49" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D200" s="26">
         <v>46232</v>
@@ -7933,13 +7945,13 @@
         <v>67</v>
       </c>
       <c r="F200" s="49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G200" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H200" s="36" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="I200" s="22" t="s">
         <v>185</v>
@@ -7953,7 +7965,7 @@
         <v>46233</v>
       </c>
       <c r="C201" s="49" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D201" s="26">
         <v>46221</v>
@@ -7962,16 +7974,16 @@
         <v>52</v>
       </c>
       <c r="F201" s="49" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G201" s="22" t="s">
         <v>52</v>
       </c>
       <c r="H201" s="36" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I201" s="22" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="202" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -7982,7 +7994,7 @@
         <v>46234</v>
       </c>
       <c r="C202" s="49" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D202" s="26">
         <v>46232</v>
@@ -7991,13 +8003,13 @@
         <v>67</v>
       </c>
       <c r="F202" s="49" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G202" s="22" t="s">
         <v>210</v>
       </c>
       <c r="H202" s="36" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I202" s="22" t="s">
         <v>185</v>
@@ -8011,7 +8023,7 @@
         <v>46234</v>
       </c>
       <c r="C203" s="49" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D203" s="26">
         <v>46233</v>
@@ -8026,7 +8038,7 @@
         <v>210</v>
       </c>
       <c r="H203" s="36" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="I203" s="22" t="s">
         <v>50</v>
@@ -8043,7 +8055,7 @@
         <v>46237</v>
       </c>
       <c r="C204" s="49" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D204" s="26">
         <v>46234</v>
@@ -8058,10 +8070,10 @@
         <v>45</v>
       </c>
       <c r="H204" s="36" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="I204" s="22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="205" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -8072,7 +8084,7 @@
         <v>46240</v>
       </c>
       <c r="C205" s="49" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D205" s="26">
         <v>46239</v>
@@ -8081,16 +8093,16 @@
         <v>67</v>
       </c>
       <c r="F205" s="49" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G205" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H205" s="36" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I205" s="22" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="206" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -8101,7 +8113,7 @@
         <v>46240</v>
       </c>
       <c r="C206" s="49" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D206" s="26">
         <v>46238</v>
@@ -8116,7 +8128,7 @@
         <v>45</v>
       </c>
       <c r="H206" s="36" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="I206" s="22" t="s">
         <v>50</v>
@@ -8130,7 +8142,7 @@
         <v>46240</v>
       </c>
       <c r="C207" s="49" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D207" s="26">
         <v>46238</v>
@@ -8139,13 +8151,13 @@
         <v>102</v>
       </c>
       <c r="F207" s="49" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G207" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H207" s="36" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I207" s="22" t="s">
         <v>50</v>
@@ -8159,19 +8171,19 @@
         <v>46241</v>
       </c>
       <c r="C208" s="49" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D208" s="26">
         <v>46234</v>
       </c>
       <c r="F208" s="49" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G208" s="22" t="s">
         <v>218</v>
       </c>
       <c r="H208" s="36" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I208" s="22" t="s">
         <v>50</v>
@@ -8185,7 +8197,7 @@
         <v>46241</v>
       </c>
       <c r="C209" s="49" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D209" s="26">
         <v>46239</v>
@@ -8194,10 +8206,10 @@
         <v>275</v>
       </c>
       <c r="F209" s="49" t="s">
+        <v>715</v>
+      </c>
+      <c r="H209" s="36" t="s">
         <v>716</v>
-      </c>
-      <c r="H209" s="36" t="s">
-        <v>717</v>
       </c>
       <c r="I209" s="22" t="s">
         <v>185</v>
@@ -8211,7 +8223,7 @@
         <v>46241</v>
       </c>
       <c r="C210" s="49" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D210" s="26">
         <v>46240</v>
@@ -8220,13 +8232,13 @@
         <v>102</v>
       </c>
       <c r="F210" s="49" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G210" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H210" s="36" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I210" s="22" t="s">
         <v>50</v>
@@ -8240,7 +8252,7 @@
         <v>46241</v>
       </c>
       <c r="C211" s="49" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D211" s="26">
         <v>46239</v>
@@ -8249,13 +8261,13 @@
         <v>78</v>
       </c>
       <c r="F211" s="49" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G211" s="22" t="s">
         <v>218</v>
       </c>
       <c r="H211" s="36" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="I211" s="22" t="s">
         <v>50</v>
@@ -8269,22 +8281,22 @@
         <v>46241</v>
       </c>
       <c r="C212" s="49" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D212" s="26">
         <v>46241</v>
       </c>
       <c r="E212" s="22" t="s">
+        <v>726</v>
+      </c>
+      <c r="F212" s="49" t="s">
         <v>727</v>
-      </c>
-      <c r="F212" s="49" t="s">
-        <v>728</v>
       </c>
       <c r="G212" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H212" s="36" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I212" s="22" t="s">
         <v>50</v>
@@ -8297,21 +8309,21 @@
       <c r="C213" s="49"/>
       <c r="F213" s="49"/>
       <c r="H213" s="36" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="214" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C214" s="49"/>
       <c r="F214" s="49"/>
       <c r="H214" s="36" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="215" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C215" s="49"/>
       <c r="F215" s="49"/>
       <c r="H215" s="36" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="216" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -8337,7 +8349,7 @@
         <v>48</v>
       </c>
       <c r="H216" s="36" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I216" s="22" t="s">
         <v>50</v>
@@ -8351,7 +8363,7 @@
         <v>46251</v>
       </c>
       <c r="C217" s="49" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D217" s="26">
         <v>46247</v>
@@ -8366,7 +8378,7 @@
         <v>45</v>
       </c>
       <c r="H217" s="36" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I217" s="22" t="s">
         <v>50</v>
@@ -8380,22 +8392,22 @@
         <v>46251</v>
       </c>
       <c r="C218" s="49" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D218" s="26">
         <v>46251</v>
       </c>
       <c r="E218" s="22" t="s">
+        <v>742</v>
+      </c>
+      <c r="F218" s="49" t="s">
         <v>743</v>
-      </c>
-      <c r="F218" s="49" t="s">
-        <v>744</v>
       </c>
       <c r="G218" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H218" s="36" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="I218" s="22">
         <v>1</v>
@@ -8406,10 +8418,10 @@
         <v>165</v>
       </c>
       <c r="B219" s="26" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C219" s="49" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D219" s="26">
         <v>46251</v>
@@ -8418,13 +8430,13 @@
         <v>41</v>
       </c>
       <c r="F219" s="49" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G219" s="22" t="s">
         <v>43</v>
       </c>
       <c r="H219" s="36" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="I219" s="22" t="s">
         <v>129</v>
@@ -8434,9 +8446,33 @@
       </c>
     </row>
     <row r="220" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C220" s="49"/>
-      <c r="F220" s="49"/>
-      <c r="H220" s="36"/>
+      <c r="A220" s="22">
+        <v>166</v>
+      </c>
+      <c r="B220" s="26">
+        <v>46259</v>
+      </c>
+      <c r="C220" s="49" t="s">
+        <v>754</v>
+      </c>
+      <c r="D220" s="26">
+        <v>46259</v>
+      </c>
+      <c r="E220" s="22" t="s">
+        <v>755</v>
+      </c>
+      <c r="F220" s="49" t="s">
+        <v>756</v>
+      </c>
+      <c r="G220" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H220" s="36" t="s">
+        <v>757</v>
+      </c>
+      <c r="I220" s="22" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="221" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C221" s="49"/>
@@ -12926,7 +12962,7 @@
         <v>13</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G24" s="46" t="s">
         <v>47</v>
@@ -13300,7 +13336,7 @@
         <v>13</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G38" s="45" t="s">
         <v>47</v>
@@ -13309,7 +13345,7 @@
         <v>43</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>280</v>
+        <v>753</v>
       </c>
       <c r="J38" s="27" t="s">
         <v>50</v>
@@ -13364,7 +13400,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G40" s="45" t="s">
         <v>47</v>
@@ -13431,7 +13467,7 @@
         <v>46140</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D43" s="55">
         <v>46140</v>
@@ -13440,7 +13476,7 @@
         <v>13</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G43" s="45" t="s">
         <v>47</v>
@@ -13449,7 +13485,7 @@
         <v>48</v>
       </c>
       <c r="I43" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J43" s="10" t="s">
         <v>50</v>
@@ -13472,7 +13508,7 @@
         <v>13</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G44" s="45" t="s">
         <v>47</v>
@@ -13481,7 +13517,7 @@
         <v>22</v>
       </c>
       <c r="I44" s="29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13501,7 +13537,7 @@
         <v>13</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G45" s="45" t="s">
         <v>21</v>
@@ -13510,7 +13546,7 @@
         <v>127</v>
       </c>
       <c r="I45" s="29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J45" s="10" t="s">
         <v>129</v>
@@ -13533,16 +13569,16 @@
         <v>13</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G46" s="45" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H46" s="45" t="s">
         <v>22</v>
       </c>
       <c r="I46" s="29" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J46" s="10" t="s">
         <v>50</v>
@@ -13556,7 +13592,7 @@
         <v>46149</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D47" s="55">
         <v>46148</v>
@@ -13565,7 +13601,7 @@
         <v>67</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G47" s="45" t="s">
         <v>47</v>
@@ -13574,10 +13610,10 @@
         <v>48</v>
       </c>
       <c r="I47" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13587,10 +13623,10 @@
       <c r="G48" s="45"/>
       <c r="H48" s="45"/>
       <c r="I48" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="J48" s="10" t="s">
         <v>335</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13601,7 +13637,7 @@
         <v>46149</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D49" s="55">
         <v>46148</v>
@@ -13619,10 +13655,10 @@
         <v>48</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13632,10 +13668,10 @@
       <c r="G50" s="45"/>
       <c r="H50" s="45"/>
       <c r="I50" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="J50" s="10" t="s">
         <v>350</v>
-      </c>
-      <c r="J50" s="10" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13655,7 +13691,7 @@
         <v>13</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G51" s="45" t="s">
         <v>47</v>
@@ -13664,7 +13700,7 @@
         <v>48</v>
       </c>
       <c r="I51" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J51" s="10" t="s">
         <v>50</v>
@@ -13687,7 +13723,7 @@
         <v>102</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G52" s="45" t="s">
         <v>47</v>
@@ -13696,7 +13732,7 @@
         <v>52</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J52" s="10" t="s">
         <v>50</v>
@@ -13719,7 +13755,7 @@
         <v>13</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G53" s="45" t="s">
         <v>47</v>
@@ -13728,7 +13764,7 @@
         <v>43</v>
       </c>
       <c r="I53" s="29" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J53" s="10" t="s">
         <v>50</v>
@@ -13751,7 +13787,7 @@
         <v>13</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G54" s="45" t="s">
         <v>47</v>
@@ -13760,7 +13796,7 @@
         <v>43</v>
       </c>
       <c r="I54" s="29" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J54" s="10" t="s">
         <v>50</v>
@@ -13783,7 +13819,7 @@
         <v>102</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G55" s="45" t="s">
         <v>47</v>
@@ -13792,7 +13828,7 @@
         <v>43</v>
       </c>
       <c r="I55" s="36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J55" s="10" t="s">
         <v>50</v>
@@ -13806,7 +13842,7 @@
         <v>46162</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D56" s="55">
         <v>46162</v>
@@ -13824,7 +13860,7 @@
         <v>48</v>
       </c>
       <c r="I56" s="29" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>50</v>
@@ -13847,16 +13883,16 @@
         <v>102</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G57" s="45" t="s">
         <v>47</v>
       </c>
       <c r="H57" s="45" t="s">
+        <v>412</v>
+      </c>
+      <c r="I57" s="29" t="s">
         <v>413</v>
-      </c>
-      <c r="I57" s="29" t="s">
-        <v>414</v>
       </c>
       <c r="J57" s="10" t="s">
         <v>50</v>
@@ -13888,7 +13924,7 @@
         <v>22</v>
       </c>
       <c r="I58" s="36" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J58" s="10" t="s">
         <v>50</v>
@@ -13920,7 +13956,7 @@
         <v>22</v>
       </c>
       <c r="I59" s="29" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J59" s="10" t="s">
         <v>50</v>
@@ -13934,7 +13970,7 @@
         <v>46169</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D60" s="55">
         <v>46169</v>
@@ -13952,7 +13988,7 @@
         <v>48</v>
       </c>
       <c r="I60" s="29" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J60" s="10" t="s">
         <v>50</v>
@@ -13965,7 +14001,7 @@
       <c r="G61" s="45"/>
       <c r="H61" s="45"/>
       <c r="I61" s="29" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -13985,7 +14021,7 @@
         <v>13</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G62" s="45" t="s">
         <v>47</v>
@@ -13994,7 +14030,7 @@
         <v>43</v>
       </c>
       <c r="I62" s="36" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J62" s="10" t="s">
         <v>50</v>
@@ -14008,7 +14044,7 @@
         <v>46171</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D63" s="55">
         <v>46171</v>
@@ -14020,13 +14056,13 @@
         <v>161</v>
       </c>
       <c r="G63" s="45" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H63" s="45" t="s">
         <v>43</v>
       </c>
       <c r="I63" s="29" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J63" s="10" t="s">
         <v>50</v>
@@ -14046,10 +14082,10 @@
         <v>46172</v>
       </c>
       <c r="E64" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>473</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>474</v>
       </c>
       <c r="G64" s="45" t="s">
         <v>47</v>
@@ -14058,7 +14094,7 @@
         <v>43</v>
       </c>
       <c r="I64" s="29" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J64" s="10" t="s">
         <v>50</v>
@@ -14090,7 +14126,7 @@
         <v>22</v>
       </c>
       <c r="I65" s="29" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J65" s="10" t="s">
         <v>50</v>
@@ -14119,7 +14155,7 @@
         <v>127</v>
       </c>
       <c r="I66" s="29" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J66" s="10" t="s">
         <v>214</v>
@@ -14151,7 +14187,7 @@
         <v>210</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J67" s="10" t="s">
         <v>50</v>
@@ -14174,7 +14210,7 @@
         <v>13</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G68" s="45" t="s">
         <v>47</v>
@@ -14183,7 +14219,7 @@
         <v>210</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J68" s="10" t="s">
         <v>50</v>
@@ -14215,7 +14251,7 @@
         <v>22</v>
       </c>
       <c r="I69" s="29" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J69" s="10" t="s">
         <v>50</v>
@@ -14238,7 +14274,7 @@
         <v>13</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G70" s="45" t="s">
         <v>47</v>
@@ -14247,7 +14283,7 @@
         <v>22</v>
       </c>
       <c r="I70" s="29" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J70" s="10" t="s">
         <v>50</v>
@@ -14279,7 +14315,7 @@
         <v>22</v>
       </c>
       <c r="I71" s="29" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J71" s="10" t="s">
         <v>50</v>
@@ -14293,7 +14329,7 @@
         <v>46192</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D72" s="55">
         <v>46191</v>
@@ -14302,7 +14338,7 @@
         <v>67</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G72" s="45" t="s">
         <v>47</v>
@@ -14311,10 +14347,10 @@
         <v>48</v>
       </c>
       <c r="I72" s="29" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14324,7 +14360,7 @@
       <c r="G73" s="45"/>
       <c r="H73" s="45"/>
       <c r="I73" s="36" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14335,7 +14371,7 @@
         <v>46192</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D74" s="55">
         <v>46191</v>
@@ -14353,10 +14389,10 @@
         <v>48</v>
       </c>
       <c r="I74" s="36" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14376,7 +14412,7 @@
         <v>102</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G75" s="45" t="s">
         <v>47</v>
@@ -14385,7 +14421,7 @@
         <v>52</v>
       </c>
       <c r="I75" s="36" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="J75" s="10" t="s">
         <v>50</v>
@@ -14399,7 +14435,7 @@
         <v>46196</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D76" s="55">
         <v>46196</v>
@@ -14417,7 +14453,7 @@
         <v>48</v>
       </c>
       <c r="I76" s="29" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J76" s="10" t="s">
         <v>50</v>
@@ -14440,7 +14476,7 @@
         <v>102</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G77" s="45" t="s">
         <v>47</v>
@@ -14449,7 +14485,7 @@
         <v>52</v>
       </c>
       <c r="I77" s="29" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J77" s="10" t="s">
         <v>50</v>
@@ -14472,7 +14508,7 @@
         <v>13</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G78" s="45" t="s">
         <v>47</v>
@@ -14481,7 +14517,7 @@
         <v>43</v>
       </c>
       <c r="I78" s="29" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>50</v>
@@ -14504,7 +14540,7 @@
         <v>102</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G79" s="45" t="s">
         <v>47</v>
@@ -14513,7 +14549,7 @@
         <v>43</v>
       </c>
       <c r="I79" s="29" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J79" s="10" t="s">
         <v>50</v>
@@ -14527,13 +14563,13 @@
         <v>46200</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D80" s="55">
         <v>46200</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>208</v>
@@ -14545,10 +14581,10 @@
         <v>48</v>
       </c>
       <c r="I80" s="29" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14558,7 +14594,7 @@
       <c r="G81" s="45"/>
       <c r="H81" s="45"/>
       <c r="I81" s="29" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14568,7 +14604,7 @@
       <c r="G82" s="45"/>
       <c r="H82" s="45"/>
       <c r="I82" s="29" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14578,7 +14614,7 @@
       <c r="G83" s="45"/>
       <c r="H83" s="45"/>
       <c r="I83" s="29" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14588,7 +14624,7 @@
       <c r="G84" s="45"/>
       <c r="H84" s="45"/>
       <c r="I84" s="29" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14617,7 +14653,7 @@
         <v>43</v>
       </c>
       <c r="I85" s="29" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J85" s="10" t="s">
         <v>50</v>
@@ -14630,7 +14666,7 @@
       <c r="G86" s="45"/>
       <c r="H86" s="45"/>
       <c r="I86" s="29" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14659,7 +14695,7 @@
         <v>22</v>
       </c>
       <c r="I87" s="29" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J87" s="10" t="s">
         <v>50</v>
@@ -14672,7 +14708,7 @@
       <c r="G88" s="45"/>
       <c r="H88" s="45"/>
       <c r="I88" s="29" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14692,7 +14728,7 @@
         <v>13</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G89" s="45" t="s">
         <v>47</v>
@@ -14701,7 +14737,7 @@
         <v>52</v>
       </c>
       <c r="I89" s="29" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="90" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14721,7 +14757,7 @@
         <v>271</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G90" s="45" t="s">
         <v>47</v>
@@ -14730,7 +14766,7 @@
         <v>22</v>
       </c>
       <c r="I90" s="29" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="91" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14747,10 +14783,10 @@
         <v>46212</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G91" s="45" t="s">
         <v>47</v>
@@ -14759,7 +14795,7 @@
         <v>210</v>
       </c>
       <c r="I91" s="29" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J91" s="10" t="s">
         <v>50</v>
@@ -14770,7 +14806,7 @@
         <v>68</v>
       </c>
       <c r="B92" s="45" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>40</v>
@@ -14791,7 +14827,7 @@
         <v>22</v>
       </c>
       <c r="I92" s="29" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J92" s="10" t="s">
         <v>50</v>
@@ -14823,7 +14859,7 @@
         <v>210</v>
       </c>
       <c r="I93" s="29" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J93" s="10" t="s">
         <v>50</v>
@@ -14837,7 +14873,7 @@
         <v>46211</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D94" s="55">
         <v>46211</v>
@@ -14855,7 +14891,7 @@
         <v>48</v>
       </c>
       <c r="I94" s="29" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J94" s="10" t="s">
         <v>50</v>
@@ -14869,7 +14905,7 @@
         <v>46206</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D95" s="55">
         <v>46206</v>
@@ -14878,7 +14914,7 @@
         <v>13</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G95" s="45" t="s">
         <v>47</v>
@@ -14887,10 +14923,10 @@
         <v>48</v>
       </c>
       <c r="I95" s="29" t="s">
+        <v>586</v>
+      </c>
+      <c r="J95" s="10" t="s">
         <v>587</v>
-      </c>
-      <c r="J95" s="10" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="96" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -14919,7 +14955,7 @@
         <v>48</v>
       </c>
       <c r="I96" s="29" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J96" s="10" t="s">
         <v>50</v>
@@ -14933,7 +14969,7 @@
         <v>46220</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D97" s="55">
         <v>46220</v>
@@ -14951,7 +14987,7 @@
         <v>48</v>
       </c>
       <c r="I97" s="29" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J97" s="10" t="s">
         <v>50</v>
@@ -14974,16 +15010,16 @@
         <v>102</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G98" s="45" t="s">
         <v>47</v>
       </c>
       <c r="H98" s="45" t="s">
+        <v>622</v>
+      </c>
+      <c r="I98" s="29" t="s">
         <v>623</v>
-      </c>
-      <c r="I98" s="29" t="s">
-        <v>624</v>
       </c>
       <c r="J98" s="10" t="s">
         <v>50</v>
@@ -15003,18 +15039,18 @@
         <v>46220</v>
       </c>
       <c r="E99" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="F99" s="10" t="s">
         <v>630</v>
-      </c>
-      <c r="F99" s="10" t="s">
-        <v>631</v>
       </c>
       <c r="G99" s="45"/>
       <c r="H99" s="45"/>
       <c r="I99" s="29" t="s">
+        <v>631</v>
+      </c>
+      <c r="J99" s="10" t="s">
         <v>632</v>
-      </c>
-      <c r="J99" s="10" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="100" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -15022,7 +15058,7 @@
         <v>76</v>
       </c>
       <c r="B100" s="45" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>40</v>
@@ -15043,7 +15079,7 @@
         <v>48</v>
       </c>
       <c r="I100" s="29" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="J100" s="10" t="s">
         <v>50</v>
@@ -15066,7 +15102,7 @@
         <v>13</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G101" s="45" t="s">
         <v>47</v>
@@ -15075,13 +15111,13 @@
         <v>43</v>
       </c>
       <c r="I101" s="29" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J101" s="10" t="s">
         <v>50</v>
       </c>
       <c r="K101" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -15101,7 +15137,7 @@
         <v>102</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G102" s="45" t="s">
         <v>47</v>
@@ -15110,7 +15146,7 @@
         <v>52</v>
       </c>
       <c r="I102" s="29" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J102" s="10" t="s">
         <v>50</v>
@@ -15142,7 +15178,7 @@
         <v>48</v>
       </c>
       <c r="I103" s="29" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="J103" s="10" t="s">
         <v>50</v>
@@ -15165,7 +15201,7 @@
         <v>13</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G104" s="45" t="s">
         <v>47</v>
@@ -15174,7 +15210,7 @@
         <v>48</v>
       </c>
       <c r="I104" s="29" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="J104" s="10" t="s">
         <v>50</v>
@@ -15197,16 +15233,16 @@
         <v>13</v>
       </c>
       <c r="F105" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="G105" s="45" t="s">
         <v>657</v>
-      </c>
-      <c r="G105" s="45" t="s">
-        <v>658</v>
       </c>
       <c r="H105" s="45" t="s">
         <v>48</v>
       </c>
       <c r="I105" s="29" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J105" s="10" t="s">
         <v>129</v>
@@ -15229,7 +15265,7 @@
         <v>13</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G106" s="45" t="s">
         <v>47</v>
@@ -15238,7 +15274,7 @@
         <v>22</v>
       </c>
       <c r="I106" s="29" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="J106" s="10" t="s">
         <v>50</v>
@@ -15252,7 +15288,7 @@
         <v>46230</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D107" s="55">
         <v>46230</v>
@@ -15268,7 +15304,7 @@
         <v>210</v>
       </c>
       <c r="I107" s="36" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="J107" s="10" t="s">
         <v>50</v>
@@ -15282,7 +15318,7 @@
         <v>46231</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D108" s="55">
         <v>46231</v>
@@ -15300,7 +15336,7 @@
         <v>210</v>
       </c>
       <c r="I108" s="29" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J108" s="10" t="s">
         <v>50</v>
@@ -15313,7 +15349,7 @@
       <c r="G109" s="45"/>
       <c r="H109" s="45"/>
       <c r="I109" s="29" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -15323,7 +15359,7 @@
       <c r="G110" s="45"/>
       <c r="H110" s="45"/>
       <c r="I110" s="29" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -15343,7 +15379,7 @@
         <v>13</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G111" s="45" t="s">
         <v>47</v>
@@ -15352,7 +15388,7 @@
         <v>52</v>
       </c>
       <c r="I111" s="29" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J111" s="10" t="s">
         <v>129</v>
@@ -15363,10 +15399,10 @@
         <v>86</v>
       </c>
       <c r="B112" s="45" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D112" s="55">
         <v>46234</v>
@@ -15375,7 +15411,7 @@
         <v>13</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G112" s="45" t="s">
         <v>125</v>
@@ -15384,7 +15420,7 @@
         <v>48</v>
       </c>
       <c r="I112" s="29" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="J112" s="10" t="s">
         <v>50</v>
@@ -15407,7 +15443,7 @@
         <v>13</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G113" s="45" t="s">
         <v>47</v>
@@ -15416,7 +15452,7 @@
         <v>43</v>
       </c>
       <c r="I113" s="29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="J113" s="10" t="s">
         <v>129</v>
@@ -15448,7 +15484,7 @@
         <v>48</v>
       </c>
       <c r="I114" s="36" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J114" s="10" t="s">
         <v>50</v>
@@ -15471,7 +15507,7 @@
         <v>13</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G115" s="45" t="s">
         <v>125</v>
@@ -15480,7 +15516,7 @@
         <v>43</v>
       </c>
       <c r="I115" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="J115" s="10" t="s">
         <v>50</v>
@@ -15503,7 +15539,7 @@
         <v>102</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G116" s="45" t="s">
         <v>47</v>
@@ -15512,7 +15548,7 @@
         <v>52</v>
       </c>
       <c r="I116" s="36" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J116" s="10" t="s">
         <v>50</v>
@@ -15544,7 +15580,7 @@
         <v>22</v>
       </c>
       <c r="I117" s="29" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="J117" s="10" t="s">
         <v>50</v>
@@ -15567,7 +15603,7 @@
         <v>13</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G118" s="45" t="s">
         <v>47</v>
@@ -15576,7 +15612,7 @@
         <v>22</v>
       </c>
       <c r="I118" s="29" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J118" s="10" t="s">
         <v>50</v>
@@ -15590,7 +15626,7 @@
         <v>46251</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D119" s="55">
         <v>46248</v>
@@ -15599,7 +15635,7 @@
         <v>13</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G119" s="45" t="s">
         <v>125</v>
@@ -15608,7 +15644,7 @@
         <v>22</v>
       </c>
       <c r="I119" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="J119" s="10" t="s">
         <v>50</v>
@@ -15640,7 +15676,7 @@
         <v>48</v>
       </c>
       <c r="I120" s="65" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="J120" s="10" t="s">
         <v>50</v>
@@ -15654,7 +15690,7 @@
         <v>46254</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D121" s="55">
         <v>46254</v>
@@ -15672,7 +15708,7 @@
         <v>48</v>
       </c>
       <c r="I121" s="29" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="J121" s="10" t="s">
         <v>50</v>
@@ -15695,16 +15731,16 @@
         <v>13</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G122" s="45" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H122" s="45" t="s">
         <v>210</v>
       </c>
       <c r="I122" s="29" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="J122" s="10" t="s">
         <v>50</v>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B56279-A55C-49CD-97DF-4D0E3A06C0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B032A7BE-FA16-4347-A922-ADC9B9B81D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="760">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2295,6 +2295,12 @@
   </si>
   <si>
     <t>Reagent Tray Bottom- Qty 12 Nos. / Test Tube  Holder - Qty 135 Nos. / Outer Cover- Qty 03 / Base Plate - Qty 02 / Switch Cover- Qty 3 / Flowcell cover- Qty 3</t>
+  </si>
+  <si>
+    <t>L26IN037968</t>
+  </si>
+  <si>
+    <t>Prt No. 690368181072 WR-MM Female Angled Connector Without Latch 10 Pins - Qty 3 Nos.</t>
   </si>
 </sst>
 </file>
@@ -8471,13 +8477,37 @@
         <v>757</v>
       </c>
       <c r="I220" s="22" t="s">
-        <v>171</v>
+        <v>335</v>
       </c>
     </row>
     <row r="221" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C221" s="49"/>
-      <c r="F221" s="49"/>
-      <c r="H221" s="36"/>
+      <c r="A221" s="22">
+        <v>167</v>
+      </c>
+      <c r="B221" s="26">
+        <v>46260</v>
+      </c>
+      <c r="C221" s="49" t="s">
+        <v>758</v>
+      </c>
+      <c r="D221" s="26">
+        <v>46260</v>
+      </c>
+      <c r="E221" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F221" s="49" t="s">
+        <v>289</v>
+      </c>
+      <c r="G221" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H221" s="36" t="s">
+        <v>759</v>
+      </c>
+      <c r="I221" s="22" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="222" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C222" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B032A7BE-FA16-4347-A922-ADC9B9B81D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2046E0-7261-45BE-BE0E-1B8F470B0926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="763">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2294,13 +2294,22 @@
     <t>Mapel Moulds &amp; Dies (India) Pvt Ltd.</t>
   </si>
   <si>
-    <t>Reagent Tray Bottom- Qty 12 Nos. / Test Tube  Holder - Qty 135 Nos. / Outer Cover- Qty 03 / Base Plate - Qty 02 / Switch Cover- Qty 3 / Flowcell cover- Qty 3</t>
-  </si>
-  <si>
     <t>L26IN037968</t>
   </si>
   <si>
     <t>Prt No. 690368181072 WR-MM Female Angled Connector Without Latch 10 Pins - Qty 3 Nos.</t>
+  </si>
+  <si>
+    <t>Reagent Tray Bottom- Qty 12 Nos. / Test Tube  Holder - Qty 125 Nos. / Outer Cover- Qty 03 / Base Plate - Qty 02 / Switch Cover- Qty 3 / Flowcell cover- Qty 3</t>
+  </si>
+  <si>
+    <t>Poatrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGT Top Plate - Qty </t>
+  </si>
+  <si>
+    <t>Nano Pi Bracket _Qty 5 Nos. / support Freame - Qty 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -8474,7 +8483,7 @@
         <v>45</v>
       </c>
       <c r="H220" s="36" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="I220" s="22" t="s">
         <v>335</v>
@@ -8488,7 +8497,7 @@
         <v>46260</v>
       </c>
       <c r="C221" s="49" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D221" s="26">
         <v>46260</v>
@@ -8503,21 +8512,69 @@
         <v>22</v>
       </c>
       <c r="H221" s="36" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="I221" s="22" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="222" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C222" s="49"/>
-      <c r="F222" s="49"/>
-      <c r="H222" s="36"/>
+      <c r="A222" s="22">
+        <v>168</v>
+      </c>
+      <c r="B222" s="26">
+        <v>46260</v>
+      </c>
+      <c r="C222" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D222" s="26">
+        <v>46260</v>
+      </c>
+      <c r="E222" s="22" t="s">
+        <v>760</v>
+      </c>
+      <c r="F222" s="49" t="s">
+        <v>756</v>
+      </c>
+      <c r="G222" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H222" s="36" t="s">
+        <v>761</v>
+      </c>
+      <c r="I222" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="223" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C223" s="49"/>
-      <c r="F223" s="49"/>
-      <c r="H223" s="36"/>
+      <c r="A223" s="22">
+        <v>169</v>
+      </c>
+      <c r="B223" s="26">
+        <v>46260</v>
+      </c>
+      <c r="C223" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="D223" s="26">
+        <v>46260</v>
+      </c>
+      <c r="E223" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F223" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="G223" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H223" s="36" t="s">
+        <v>762</v>
+      </c>
+      <c r="I223" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="224" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C224" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2046E0-7261-45BE-BE0E-1B8F470B0926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBADA5C-8451-43F8-AF81-4A7309E2251F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="784">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2306,10 +2306,73 @@
     <t>Poatrol</t>
   </si>
   <si>
-    <t xml:space="preserve">RGT Top Plate - Qty </t>
-  </si>
-  <si>
     <t>Nano Pi Bracket _Qty 5 Nos. / support Freame - Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Poarol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGT Top Plate (OLD) - Qty </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGT Top Plate(NEW) - Qty </t>
+  </si>
+  <si>
+    <t>JP/087/26-27</t>
+  </si>
+  <si>
+    <t>JP Medical System Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>Base Plate With Wiring- 1 Nos. / Flowcell- 1 Nos. / Display (Capacitive) with Bracket- 1 Nos. / Printer Mechanism- 1 Nos. / Display Junction PCB- 1 Nos.</t>
+  </si>
+  <si>
+    <t>Incubator Block- 1 Nos. / silicon Rubber Heater- 1 Nos. / temperature Sensor- 1 Nos. / Tube Guide Holder With SS Tube- 1 Nos. / Top Cover (Old)- 1 Nos.</t>
+  </si>
+  <si>
+    <t>R1 Yellow Bottle With White Caps- Qty 20 Nos. / Sample Cups - Qty 50 Nos.</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Photometer Halogrn Lamp Assy Bioelab FA 6V/10W- Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>168/2627</t>
+  </si>
+  <si>
+    <t>15 ml HDPE chemultra Brown Bottle with Brown Cap ( Qty- 3x1500= 3 Box / 1x500= 1 Box)</t>
+  </si>
+  <si>
+    <t>40 ml HDPE chemultra Brown Bottle with Brown Cap - Qty - 20x500= 20 Box</t>
+  </si>
+  <si>
+    <t>24 Box</t>
+  </si>
+  <si>
+    <t>AM/DOM/0007/2627</t>
+  </si>
+  <si>
+    <t>15 ml System Pack Brown Bottle with Brown Cap ( Qty- 3x1500= 3 Box / 1x500= 1 Box)</t>
+  </si>
+  <si>
+    <t>40 ml System Pack Brown  Bottle With Brown Cap -Qty 100000 ( 20 Box)</t>
+  </si>
+  <si>
+    <t>5 Invoice For the Month of August 2026</t>
+  </si>
+  <si>
+    <t>Aperture OD 10mm, ID 0.6mm - Qty 500 Nos.</t>
+  </si>
+  <si>
+    <t>AM/PP/0025/2627</t>
+  </si>
+  <si>
+    <t>AM/PP/0024/2627</t>
+  </si>
+  <si>
+    <t>Cuvettes (BS/PO/26-27/0089,0307) - Qty 240 Nos / Probe - Qty 3 Nos.</t>
   </si>
 </sst>
 </file>
@@ -8358,7 +8421,7 @@
         <v>13</v>
       </c>
       <c r="F216" s="49" t="s">
-        <v>79</v>
+        <v>770</v>
       </c>
       <c r="G216" s="22" t="s">
         <v>48</v>
@@ -8541,7 +8604,7 @@
         <v>210</v>
       </c>
       <c r="H222" s="36" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="I222" s="22" t="s">
         <v>50</v>
@@ -8570,93 +8633,193 @@
         <v>210</v>
       </c>
       <c r="H223" s="36" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="I223" s="22" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="224" spans="1:13" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C224" s="49"/>
-      <c r="F224" s="49"/>
-      <c r="H224" s="36"/>
-    </row>
-    <row r="225" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C225" s="49"/>
-      <c r="F225" s="49"/>
-      <c r="H225" s="36"/>
-    </row>
-    <row r="226" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A224" s="22">
+        <v>170</v>
+      </c>
+      <c r="B224" s="26">
+        <v>46261</v>
+      </c>
+      <c r="C224" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D224" s="26">
+        <v>46261</v>
+      </c>
+      <c r="E224" s="22" t="s">
+        <v>762</v>
+      </c>
+      <c r="F224" s="49" t="s">
+        <v>756</v>
+      </c>
+      <c r="G224" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H224" s="36" t="s">
+        <v>764</v>
+      </c>
+      <c r="I224" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A225" s="22">
+        <v>171</v>
+      </c>
+      <c r="B225" s="26">
+        <v>46263</v>
+      </c>
+      <c r="C225" s="49" t="s">
+        <v>765</v>
+      </c>
+      <c r="D225" s="26">
+        <v>46261</v>
+      </c>
+      <c r="E225" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F225" s="49" t="s">
+        <v>766</v>
+      </c>
+      <c r="G225" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H225" s="36" t="s">
+        <v>767</v>
+      </c>
+      <c r="I225" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C226" s="49"/>
       <c r="F226" s="49"/>
-      <c r="H226" s="36"/>
-    </row>
-    <row r="227" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C227" s="49"/>
-      <c r="F227" s="49"/>
-      <c r="H227" s="36"/>
-    </row>
-    <row r="228" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C228" s="49"/>
-      <c r="F228" s="49"/>
-      <c r="H228" s="36"/>
-    </row>
-    <row r="229" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="H226" s="36" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A227" s="22">
+        <v>172</v>
+      </c>
+      <c r="B227" s="26">
+        <v>46263</v>
+      </c>
+      <c r="C227" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D227" s="26">
+        <v>46263</v>
+      </c>
+      <c r="E227" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F227" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="G227" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H227" s="36" t="s">
+        <v>771</v>
+      </c>
+      <c r="I227" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A228" s="22">
+        <v>173</v>
+      </c>
+      <c r="B228" s="26">
+        <v>46263</v>
+      </c>
+      <c r="C228" s="49" t="s">
+        <v>772</v>
+      </c>
+      <c r="D228" s="26">
+        <v>46259</v>
+      </c>
+      <c r="E228" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F228" s="49" t="s">
+        <v>220</v>
+      </c>
+      <c r="G228" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H228" s="36" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C229" s="49"/>
       <c r="F229" s="49"/>
-      <c r="H229" s="36"/>
-    </row>
-    <row r="230" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="H229" s="36" t="s">
+        <v>774</v>
+      </c>
+      <c r="I229" s="22" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C230" s="49"/>
       <c r="F230" s="49"/>
       <c r="H230" s="36"/>
     </row>
-    <row r="231" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="231" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C231" s="49"/>
       <c r="F231" s="49"/>
       <c r="H231" s="36"/>
     </row>
-    <row r="232" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="232" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C232" s="49"/>
       <c r="F232" s="49"/>
       <c r="H232" s="36"/>
     </row>
-    <row r="233" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="233" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C233" s="49"/>
       <c r="F233" s="49"/>
       <c r="H233" s="36"/>
     </row>
-    <row r="234" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="234" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C234" s="49"/>
       <c r="F234" s="49"/>
       <c r="H234" s="36"/>
     </row>
-    <row r="235" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="235" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C235" s="49"/>
       <c r="F235" s="49"/>
       <c r="H235" s="36"/>
     </row>
-    <row r="236" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="236" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C236" s="49"/>
       <c r="F236" s="49"/>
       <c r="H236" s="36"/>
     </row>
-    <row r="237" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="237" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C237" s="49"/>
       <c r="F237" s="49"/>
       <c r="H237" s="36"/>
     </row>
-    <row r="238" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="238" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C238" s="49"/>
       <c r="F238" s="49"/>
       <c r="H238" s="36"/>
     </row>
-    <row r="239" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="239" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C239" s="49"/>
       <c r="F239" s="49"/>
       <c r="H239" s="36"/>
     </row>
-    <row r="240" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="240" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C240" s="49"/>
       <c r="F240" s="49"/>
       <c r="H240" s="36"/>
@@ -15834,20 +15997,68 @@
       </c>
     </row>
     <row r="123" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A123" s="27"/>
-      <c r="B123" s="45"/>
-      <c r="D123" s="45"/>
-      <c r="G123" s="45"/>
-      <c r="H123" s="45"/>
-      <c r="I123" s="29"/>
+      <c r="A123" s="27">
+        <v>97</v>
+      </c>
+      <c r="B123" s="55">
+        <v>46261</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D123" s="55">
+        <v>46261</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="G123" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H123" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="I123" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="J123" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A124" s="27"/>
-      <c r="B124" s="45"/>
-      <c r="D124" s="45"/>
-      <c r="G124" s="45"/>
-      <c r="H124" s="45"/>
-      <c r="I124" s="29"/>
+      <c r="A124" s="27">
+        <v>98</v>
+      </c>
+      <c r="B124" s="55">
+        <v>46263</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="D124" s="55">
+        <v>46260</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F124" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="G124" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H124" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I124" s="29" t="s">
+        <v>778</v>
+      </c>
+      <c r="J124" s="10" t="s">
+        <v>775</v>
+      </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A125" s="27"/>
@@ -15855,31 +16066,100 @@
       <c r="D125" s="45"/>
       <c r="G125" s="45"/>
       <c r="H125" s="45"/>
-      <c r="I125" s="29"/>
+      <c r="I125" s="29" t="s">
+        <v>777</v>
+      </c>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A126" s="27"/>
-      <c r="B126" s="45"/>
-      <c r="D126" s="45"/>
-      <c r="G126" s="45"/>
-      <c r="H126" s="45"/>
-      <c r="I126" s="29"/>
+      <c r="A126" s="27">
+        <v>99</v>
+      </c>
+      <c r="B126" s="55">
+        <v>46265</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="D126" s="55">
+        <v>46265</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G126" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H126" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I126" s="29" t="s">
+        <v>780</v>
+      </c>
+      <c r="J126" s="10" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="127" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A127" s="27"/>
-      <c r="B127" s="45"/>
-      <c r="D127" s="45"/>
-      <c r="G127" s="45"/>
-      <c r="H127" s="45"/>
-      <c r="I127" s="29"/>
+      <c r="B127" s="55">
+        <v>46265</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D127" s="55">
+        <v>46265</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G127" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H127" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="I127" s="29" t="s">
+        <v>779</v>
+      </c>
+      <c r="J127" s="10" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="128" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A128" s="27"/>
-      <c r="B128" s="45"/>
-      <c r="D128" s="45"/>
-      <c r="G128" s="45"/>
-      <c r="H128" s="45"/>
-      <c r="I128" s="29"/>
+      <c r="A128" s="27">
+        <v>100</v>
+      </c>
+      <c r="B128" s="55">
+        <v>46265</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>782</v>
+      </c>
+      <c r="D128" s="55">
+        <v>46265</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G128" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H128" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I128" s="29" t="s">
+        <v>783</v>
+      </c>
     </row>
     <row r="129" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A129" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBADA5C-8451-43F8-AF81-4A7309E2251F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B359D82-0008-4D3B-9B96-7A857EE63D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="787">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2373,6 +2373,15 @@
   </si>
   <si>
     <t>Cuvettes (BS/PO/26-27/0089,0307) - Qty 240 Nos / Probe - Qty 3 Nos.</t>
+  </si>
+  <si>
+    <t>Inv. No- 18</t>
+  </si>
+  <si>
+    <t>RCT Jacket_400, BSHRD-07-MA-02-02-001 - Qty 4 Nos. / RGT  Container_400, BSHRD -07-MA-03-02-001 - Qty 4 Nos.</t>
+  </si>
+  <si>
+    <t>Sample Tray Container_400, BSHRD-07-MA-04-02-001 - Qty 4 Nos.</t>
   </si>
 </sst>
 </file>
@@ -8770,14 +8779,40 @@
       </c>
     </row>
     <row r="230" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C230" s="49"/>
-      <c r="F230" s="49"/>
-      <c r="H230" s="36"/>
+      <c r="A230" s="22">
+        <v>174</v>
+      </c>
+      <c r="B230" s="26">
+        <v>46266</v>
+      </c>
+      <c r="C230" s="49" t="s">
+        <v>784</v>
+      </c>
+      <c r="D230" s="26">
+        <v>46266</v>
+      </c>
+      <c r="E230" s="22" t="s">
+        <v>726</v>
+      </c>
+      <c r="F230" s="49" t="s">
+        <v>727</v>
+      </c>
+      <c r="G230" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H230" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="I230" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="231" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C231" s="49"/>
       <c r="F231" s="49"/>
-      <c r="H231" s="36"/>
+      <c r="H231" s="36" t="s">
+        <v>786</v>
+      </c>
     </row>
     <row r="232" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C232" s="49"/>
@@ -16162,8 +16197,10 @@
       </c>
     </row>
     <row r="129" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A129" s="27"/>
-      <c r="B129" s="45"/>
+      <c r="A129" s="27">
+        <v>101</v>
+      </c>
+      <c r="B129" s="55"/>
       <c r="D129" s="45"/>
       <c r="G129" s="45"/>
       <c r="H129" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B359D82-0008-4D3B-9B96-7A857EE63D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3BCC55-6576-48A2-A064-13D4325F7B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="790">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2382,6 +2382,15 @@
   </si>
   <si>
     <t>Sample Tray Container_400, BSHRD-07-MA-04-02-001 - Qty 4 Nos.</t>
+  </si>
+  <si>
+    <t>AM/DOM/0008/2627</t>
+  </si>
+  <si>
+    <t>Micro Sample Cups- Qty 2000 Nos. ( 500x4)</t>
+  </si>
+  <si>
+    <t>Photometer Halogen Lamp Assy Bioelab FA 6V/10W- Qty 1 Nos</t>
   </si>
 </sst>
 </file>
@@ -16196,25 +16205,71 @@
         <v>783</v>
       </c>
     </row>
-    <row r="129" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="129" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A129" s="27">
         <v>101</v>
       </c>
-      <c r="B129" s="55"/>
-      <c r="D129" s="45"/>
-      <c r="G129" s="45"/>
-      <c r="H129" s="45"/>
-      <c r="I129" s="29"/>
-    </row>
-    <row r="130" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A130" s="27"/>
-      <c r="B130" s="45"/>
-      <c r="D130" s="45"/>
-      <c r="G130" s="45"/>
-      <c r="H130" s="45"/>
-      <c r="I130" s="29"/>
-    </row>
-    <row r="131" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B129" s="55">
+        <v>46267</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>787</v>
+      </c>
+      <c r="D129" s="55">
+        <v>46265</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="G129" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H129" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I129" s="29" t="s">
+        <v>788</v>
+      </c>
+      <c r="J129" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A130" s="27">
+        <v>102</v>
+      </c>
+      <c r="B130" s="55">
+        <v>46267</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D130" s="55">
+        <v>46267</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G130" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H130" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I130" s="29" t="s">
+        <v>789</v>
+      </c>
+      <c r="J130" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A131" s="27"/>
       <c r="B131" s="45"/>
       <c r="D131" s="45"/>
@@ -16222,7 +16277,7 @@
       <c r="H131" s="45"/>
       <c r="I131" s="29"/>
     </row>
-    <row r="132" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="132" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A132" s="27"/>
       <c r="B132" s="45"/>
       <c r="D132" s="45"/>
@@ -16230,7 +16285,7 @@
       <c r="H132" s="45"/>
       <c r="I132" s="29"/>
     </row>
-    <row r="133" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="133" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A133" s="27"/>
       <c r="B133" s="45"/>
       <c r="D133" s="45"/>
@@ -16238,7 +16293,7 @@
       <c r="H133" s="45"/>
       <c r="I133" s="29"/>
     </row>
-    <row r="134" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="134" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A134" s="27"/>
       <c r="B134" s="45"/>
       <c r="D134" s="45"/>
@@ -16246,7 +16301,7 @@
       <c r="H134" s="45"/>
       <c r="I134" s="29"/>
     </row>
-    <row r="135" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="135" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A135" s="27"/>
       <c r="B135" s="45"/>
       <c r="D135" s="45"/>
@@ -16254,7 +16309,7 @@
       <c r="H135" s="45"/>
       <c r="I135" s="29"/>
     </row>
-    <row r="136" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="136" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A136" s="27"/>
       <c r="B136" s="45"/>
       <c r="D136" s="45"/>
@@ -16262,7 +16317,7 @@
       <c r="H136" s="45"/>
       <c r="I136" s="29"/>
     </row>
-    <row r="137" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="137" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A137" s="27"/>
       <c r="B137" s="45"/>
       <c r="D137" s="45"/>
@@ -16270,7 +16325,7 @@
       <c r="H137" s="45"/>
       <c r="I137" s="29"/>
     </row>
-    <row r="138" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="138" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A138" s="27"/>
       <c r="B138" s="45"/>
       <c r="D138" s="45"/>
@@ -16278,7 +16333,7 @@
       <c r="H138" s="45"/>
       <c r="I138" s="29"/>
     </row>
-    <row r="139" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="139" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A139" s="27"/>
       <c r="B139" s="45"/>
       <c r="D139" s="45"/>
@@ -16286,7 +16341,7 @@
       <c r="H139" s="45"/>
       <c r="I139" s="29"/>
     </row>
-    <row r="140" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="140" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A140" s="27"/>
       <c r="B140" s="45"/>
       <c r="D140" s="45"/>
@@ -16294,7 +16349,7 @@
       <c r="H140" s="45"/>
       <c r="I140" s="29"/>
     </row>
-    <row r="141" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="141" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A141" s="27"/>
       <c r="B141" s="45"/>
       <c r="D141" s="45"/>
@@ -16302,7 +16357,7 @@
       <c r="H141" s="45"/>
       <c r="I141" s="29"/>
     </row>
-    <row r="142" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="142" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A142" s="27"/>
       <c r="B142" s="45"/>
       <c r="D142" s="45"/>
@@ -16310,7 +16365,7 @@
       <c r="H142" s="45"/>
       <c r="I142" s="29"/>
     </row>
-    <row r="143" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="143" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A143" s="27"/>
       <c r="B143" s="45"/>
       <c r="D143" s="45"/>
@@ -16318,7 +16373,7 @@
       <c r="H143" s="45"/>
       <c r="I143" s="29"/>
     </row>
-    <row r="144" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="144" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A144" s="27"/>
       <c r="B144" s="45"/>
       <c r="D144" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3BCC55-6576-48A2-A064-13D4325F7B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C05270-CAF9-4C52-8BBD-5EF0AB3A00FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="797">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2387,10 +2387,31 @@
     <t>AM/DOM/0008/2627</t>
   </si>
   <si>
-    <t>Micro Sample Cups- Qty 2000 Nos. ( 500x4)</t>
-  </si>
-  <si>
     <t>Photometer Halogen Lamp Assy Bioelab FA 6V/10W- Qty 1 Nos</t>
+  </si>
+  <si>
+    <t>3 Septembere 2026</t>
+  </si>
+  <si>
+    <t>DC0071</t>
+  </si>
+  <si>
+    <t>BioSci 240 (Fully Automatic Analyser ) With All Accessories -Qty 1 Nos. ( Packing List)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hitachi Micro Sample Cups- Qty 19500 Nos. ( 500x19) </t>
+  </si>
+  <si>
+    <t>D Healthcare Industries</t>
+  </si>
+  <si>
+    <t>JP/090/26-27</t>
+  </si>
+  <si>
+    <t>Incubator Block- 1 Nos. / 30 Pin FRC Cable - Qty 1 Nos. / 40 Pin FRC Cable- Qty 1 Nos. / Aspiration Switch Bracket (SS) - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Hitachi Micro Sample Cups- Qty 2000 Nos. ( 500x4)</t>
   </si>
 </sst>
 </file>
@@ -8824,14 +8845,62 @@
       </c>
     </row>
     <row r="232" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C232" s="49"/>
-      <c r="F232" s="49"/>
-      <c r="H232" s="36"/>
+      <c r="A232" s="22">
+        <v>175</v>
+      </c>
+      <c r="B232" s="26">
+        <v>46267</v>
+      </c>
+      <c r="C232" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D232" s="26">
+        <v>46267</v>
+      </c>
+      <c r="E232" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F232" s="49" t="s">
+        <v>793</v>
+      </c>
+      <c r="G232" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H232" s="29" t="s">
+        <v>792</v>
+      </c>
+      <c r="I232" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="233" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C233" s="49"/>
-      <c r="F233" s="49"/>
-      <c r="H233" s="36"/>
+      <c r="A233" s="22">
+        <v>176</v>
+      </c>
+      <c r="B233" s="26">
+        <v>46267</v>
+      </c>
+      <c r="C233" s="49" t="s">
+        <v>794</v>
+      </c>
+      <c r="D233" s="26">
+        <v>46266</v>
+      </c>
+      <c r="E233" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F233" s="49" t="s">
+        <v>766</v>
+      </c>
+      <c r="G233" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H233" s="36" t="s">
+        <v>795</v>
+      </c>
+      <c r="I233" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="234" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C234" s="49"/>
@@ -16231,7 +16300,7 @@
         <v>48</v>
       </c>
       <c r="I129" s="29" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="J129" s="10" t="s">
         <v>50</v>
@@ -16263,19 +16332,40 @@
         <v>48</v>
       </c>
       <c r="I130" s="29" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="J130" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="131" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A131" s="27"/>
-      <c r="B131" s="45"/>
-      <c r="D131" s="45"/>
-      <c r="G131" s="45"/>
-      <c r="H131" s="45"/>
-      <c r="I131" s="29"/>
+      <c r="A131" s="27">
+        <v>103</v>
+      </c>
+      <c r="B131" s="45" t="s">
+        <v>789</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="D131" s="55">
+        <v>46267</v>
+      </c>
+      <c r="F131" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="G131" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H131" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I131" s="29" t="s">
+        <v>791</v>
+      </c>
+      <c r="J131" s="10" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="132" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A132" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C05270-CAF9-4C52-8BBD-5EF0AB3A00FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E480B46A-639C-499E-B37F-18F155FBD671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="799">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2390,9 +2390,6 @@
     <t>Photometer Halogen Lamp Assy Bioelab FA 6V/10W- Qty 1 Nos</t>
   </si>
   <si>
-    <t>3 Septembere 2026</t>
-  </si>
-  <si>
     <t>DC0071</t>
   </si>
   <si>
@@ -2412,6 +2409,15 @@
   </si>
   <si>
     <t>Hitachi Micro Sample Cups- Qty 2000 Nos. ( 500x4)</t>
+  </si>
+  <si>
+    <t>Printer Cover- Qty 10 Nos.</t>
+  </si>
+  <si>
+    <t>Pen Drive 32 GB - qty 1 Nos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier OR Customer Name </t>
   </si>
 </sst>
 </file>
@@ -8861,13 +8867,13 @@
         <v>64</v>
       </c>
       <c r="F232" s="49" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G232" s="22" t="s">
         <v>48</v>
       </c>
       <c r="H232" s="29" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="I232" s="22" t="s">
         <v>50</v>
@@ -8881,7 +8887,7 @@
         <v>46267</v>
       </c>
       <c r="C233" s="49" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D233" s="26">
         <v>46266</v>
@@ -8896,7 +8902,7 @@
         <v>45</v>
       </c>
       <c r="H233" s="36" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="I233" s="22" t="s">
         <v>50</v>
@@ -12722,7 +12728,9 @@
       <c r="E2" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="61"/>
+      <c r="F2" s="61" t="s">
+        <v>798</v>
+      </c>
       <c r="G2" s="42" t="s">
         <v>19</v>
       </c>
@@ -16300,7 +16308,7 @@
         <v>48</v>
       </c>
       <c r="I129" s="29" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J129" s="10" t="s">
         <v>50</v>
@@ -16342,11 +16350,11 @@
       <c r="A131" s="27">
         <v>103</v>
       </c>
-      <c r="B131" s="45" t="s">
+      <c r="B131" s="55">
+        <v>46268</v>
+      </c>
+      <c r="C131" s="10" t="s">
         <v>789</v>
-      </c>
-      <c r="C131" s="10" t="s">
-        <v>790</v>
       </c>
       <c r="D131" s="55">
         <v>46267</v>
@@ -16361,27 +16369,75 @@
         <v>48</v>
       </c>
       <c r="I131" s="29" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="J131" s="10" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="132" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A132" s="27"/>
-      <c r="B132" s="45"/>
-      <c r="D132" s="45"/>
-      <c r="G132" s="45"/>
-      <c r="H132" s="45"/>
-      <c r="I132" s="29"/>
+      <c r="A132" s="27">
+        <v>104</v>
+      </c>
+      <c r="B132" s="55">
+        <v>46268</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D132" s="55">
+        <v>46268</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="G132" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H132" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I132" s="29" t="s">
+        <v>796</v>
+      </c>
+      <c r="J132" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="133" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A133" s="27"/>
-      <c r="B133" s="45"/>
-      <c r="D133" s="45"/>
-      <c r="G133" s="45"/>
-      <c r="H133" s="45"/>
-      <c r="I133" s="29"/>
+      <c r="A133" s="27">
+        <v>105</v>
+      </c>
+      <c r="B133" s="55">
+        <v>46268</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D133" s="55">
+        <v>46268</v>
+      </c>
+      <c r="E133" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="G133" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H133" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I133" s="29" t="s">
+        <v>797</v>
+      </c>
+      <c r="J133" s="10" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="134" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A134" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E480B46A-639C-499E-B37F-18F155FBD671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A2A89E-D6CF-4206-9415-3A9609E528AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="810">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2418,6 +2418,39 @@
   </si>
   <si>
     <t xml:space="preserve">Supplier OR Customer Name </t>
+  </si>
+  <si>
+    <t>04 Zseptember</t>
+  </si>
+  <si>
+    <t>Vijay Patil</t>
+  </si>
+  <si>
+    <t>Nilesh sir</t>
+  </si>
+  <si>
+    <t>Inv. No. 600053</t>
+  </si>
+  <si>
+    <t>Bio Systems</t>
+  </si>
+  <si>
+    <t>Mi91014- Vega360( Clinical Chemistry Analayser- Semi Automated)- Qty 1 Nos. /  Mi91018 Chem Smart+ Clinical Chemistry Analyser (Semi Automated)- Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Mi91018  Chem Smart + Clinical Chemistry Analyser (Semi Automated) - Qty 1 Nos. / Mi91014 Vega360( Clinical Chemistry analyser -Semi Auotmated)- Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>4 Box</t>
+  </si>
+  <si>
+    <t>Cuveete- Qty 120 Nos. / Proab - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Akshat (7793023739)</t>
+  </si>
+  <si>
+    <t>Cuvettes - Qty 90 Nos.</t>
   </si>
 </sst>
 </file>
@@ -8909,19 +8942,69 @@
       </c>
     </row>
     <row r="234" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C234" s="49"/>
-      <c r="F234" s="49"/>
-      <c r="H234" s="36"/>
+      <c r="A234" s="22">
+        <v>177</v>
+      </c>
+      <c r="B234" s="26">
+        <v>46268</v>
+      </c>
+      <c r="C234" s="49" t="s">
+        <v>802</v>
+      </c>
+      <c r="D234" s="26">
+        <v>46267</v>
+      </c>
+      <c r="E234" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F234" s="49" t="s">
+        <v>803</v>
+      </c>
+      <c r="G234" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H234" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="I234" s="22" t="s">
+        <v>806</v>
+      </c>
     </row>
     <row r="235" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C235" s="49"/>
       <c r="F235" s="49"/>
-      <c r="H235" s="36"/>
+      <c r="H235" s="36" t="s">
+        <v>805</v>
+      </c>
     </row>
     <row r="236" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C236" s="49"/>
-      <c r="F236" s="49"/>
-      <c r="H236" s="36"/>
+      <c r="A236" s="22">
+        <v>178</v>
+      </c>
+      <c r="B236" s="26">
+        <v>46269</v>
+      </c>
+      <c r="C236" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D236" s="26">
+        <v>46269</v>
+      </c>
+      <c r="E236" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F236" s="49" t="s">
+        <v>808</v>
+      </c>
+      <c r="G236" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H236" s="36" t="s">
+        <v>807</v>
+      </c>
+      <c r="I236" s="22" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="237" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C237" s="49"/>
@@ -16440,12 +16523,36 @@
       </c>
     </row>
     <row r="134" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A134" s="27"/>
-      <c r="B134" s="45"/>
-      <c r="D134" s="45"/>
-      <c r="G134" s="45"/>
-      <c r="H134" s="45"/>
-      <c r="I134" s="29"/>
+      <c r="A134" s="27">
+        <v>106</v>
+      </c>
+      <c r="B134" s="45" t="s">
+        <v>799</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D134" s="55">
+        <v>46269</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="G134" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H134" s="45" t="s">
+        <v>801</v>
+      </c>
+      <c r="I134" s="29" t="s">
+        <v>809</v>
+      </c>
+      <c r="J134" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="135" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A135" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A2A89E-D6CF-4206-9415-3A9609E528AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1EABCC-4D4E-4654-A798-30BF9BDC1144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="817">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2451,6 +2451,27 @@
   </si>
   <si>
     <t>Cuvettes - Qty 90 Nos.</t>
+  </si>
+  <si>
+    <t>07 Septmber 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AM/PP/0027/2627</t>
+  </si>
+  <si>
+    <t>Sumtor NEMA 14 Hybrid Stepper Motor 35 Frame Size - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Photometer Halogen Lamp Assy Bioelab FA 6V/10W- Qty 9 Nos.</t>
+  </si>
+  <si>
+    <t>AWB# 7x110896205</t>
+  </si>
+  <si>
+    <t>Photometer Halogen Lamp Assy Bioelab FA 6V/10W- Qty 11Nos.</t>
+  </si>
+  <si>
+    <t>2 Box join</t>
   </si>
 </sst>
 </file>
@@ -9007,9 +9028,33 @@
       </c>
     </row>
     <row r="237" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C237" s="49"/>
-      <c r="F237" s="49"/>
-      <c r="H237" s="36"/>
+      <c r="A237" s="22">
+        <v>179</v>
+      </c>
+      <c r="B237" s="26">
+        <v>46267</v>
+      </c>
+      <c r="C237" s="49" t="s">
+        <v>814</v>
+      </c>
+      <c r="D237" s="26">
+        <v>46267</v>
+      </c>
+      <c r="E237" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F237" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G237" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H237" s="29" t="s">
+        <v>815</v>
+      </c>
+      <c r="I237" s="22" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="238" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C238" s="49"/>
@@ -16555,20 +16600,65 @@
       </c>
     </row>
     <row r="135" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A135" s="27"/>
-      <c r="B135" s="45"/>
-      <c r="D135" s="45"/>
-      <c r="G135" s="45"/>
-      <c r="H135" s="45"/>
-      <c r="I135" s="29"/>
+      <c r="A135" s="27">
+        <v>107</v>
+      </c>
+      <c r="B135" s="45" t="s">
+        <v>810</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="D135" s="55">
+        <v>46272</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="G135" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H135" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I135" s="29" t="s">
+        <v>812</v>
+      </c>
+      <c r="J135" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="136" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A136" s="27"/>
-      <c r="B136" s="45"/>
-      <c r="D136" s="45"/>
-      <c r="G136" s="45"/>
-      <c r="H136" s="45"/>
-      <c r="I136" s="29"/>
+      <c r="A136" s="27">
+        <v>108</v>
+      </c>
+      <c r="B136" s="55">
+        <v>46272</v>
+      </c>
+      <c r="D136" s="55">
+        <v>46272</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G136" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H136" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I136" s="29" t="s">
+        <v>813</v>
+      </c>
+      <c r="J136" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="137" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A137" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1EABCC-4D4E-4654-A798-30BF9BDC1144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512A2D2D-D91C-410D-AC93-E8B9A76C0764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="821">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2472,6 +2472,18 @@
   </si>
   <si>
     <t>2 Box join</t>
+  </si>
+  <si>
+    <t>QWQH-13522</t>
+  </si>
+  <si>
+    <t>Nilesh Jha</t>
+  </si>
+  <si>
+    <t>Micro Tube 0.5ml - Qty 500 Nos.</t>
+  </si>
+  <si>
+    <t>Photomater Moulding Cover - Qty 50 ( Revert to BioSci )</t>
   </si>
 </sst>
 </file>
@@ -8767,7 +8779,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="225" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="225" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A225" s="22">
         <v>171</v>
       </c>
@@ -8796,14 +8808,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="226" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="226" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C226" s="49"/>
       <c r="F226" s="49"/>
       <c r="H226" s="36" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="227" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="227" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A227" s="22">
         <v>172</v>
       </c>
@@ -8832,7 +8844,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="228" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="228" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A228" s="22">
         <v>173</v>
       </c>
@@ -8858,7 +8870,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="229" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="229" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C229" s="49"/>
       <c r="F229" s="49"/>
       <c r="H229" s="36" t="s">
@@ -8868,7 +8880,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="230" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="230" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A230" s="22">
         <v>174</v>
       </c>
@@ -8897,14 +8909,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="231" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C231" s="49"/>
       <c r="F231" s="49"/>
       <c r="H231" s="36" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="232" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="232" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A232" s="22">
         <v>175</v>
       </c>
@@ -8933,7 +8945,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="233" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="233" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A233" s="22">
         <v>176</v>
       </c>
@@ -8962,7 +8974,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="234" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="234" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A234" s="22">
         <v>177</v>
       </c>
@@ -8991,14 +9003,14 @@
         <v>806</v>
       </c>
     </row>
-    <row r="235" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="235" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C235" s="49"/>
       <c r="F235" s="49"/>
       <c r="H235" s="36" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="236" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="236" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A236" s="22">
         <v>178</v>
       </c>
@@ -9027,7 +9039,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="237" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="237" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A237" s="22">
         <v>179</v>
       </c>
@@ -9056,17 +9068,57 @@
         <v>816</v>
       </c>
     </row>
-    <row r="238" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C238" s="49"/>
-      <c r="F238" s="49"/>
-      <c r="H238" s="36"/>
-    </row>
-    <row r="239" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="238" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A238" s="22">
+        <v>180</v>
+      </c>
+      <c r="B238" s="26">
+        <v>46272</v>
+      </c>
+      <c r="C238" s="49" t="s">
+        <v>817</v>
+      </c>
+      <c r="D238" s="26">
+        <v>46268</v>
+      </c>
+      <c r="E238" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="F238" s="49" t="s">
+        <v>818</v>
+      </c>
+      <c r="G238" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H238" s="36" t="s">
+        <v>819</v>
+      </c>
+      <c r="I238" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A239" s="22">
+        <v>181</v>
+      </c>
       <c r="C239" s="49"/>
-      <c r="F239" s="49"/>
-      <c r="H239" s="36"/>
-    </row>
-    <row r="240" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="F239" s="49" t="s">
+        <v>756</v>
+      </c>
+      <c r="G239" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H239" s="36" t="s">
+        <v>820</v>
+      </c>
+      <c r="I239" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="J239" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C240" s="49"/>
       <c r="F240" s="49"/>
       <c r="H240" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512A2D2D-D91C-410D-AC93-E8B9A76C0764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156EEC9C-CAFD-4392-BDAC-4251C6DD2268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="822">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2420,9 +2420,6 @@
     <t xml:space="preserve">Supplier OR Customer Name </t>
   </si>
   <si>
-    <t>04 Zseptember</t>
-  </si>
-  <si>
     <t>Vijay Patil</t>
   </si>
   <si>
@@ -2484,6 +2481,12 @@
   </si>
   <si>
     <t>Photomater Moulding Cover - Qty 50 ( Revert to BioSci )</t>
+  </si>
+  <si>
+    <t>36x26x19 = 4 Kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Printer Cover Moulding -Qty 50 Nos. &amp; Cable 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -8982,7 +8985,7 @@
         <v>46268</v>
       </c>
       <c r="C234" s="49" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D234" s="26">
         <v>46267</v>
@@ -8991,23 +8994,23 @@
         <v>67</v>
       </c>
       <c r="F234" s="49" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G234" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H234" s="36" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I234" s="22" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="235" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C235" s="49"/>
       <c r="F235" s="49"/>
       <c r="H235" s="36" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="236" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -9027,13 +9030,13 @@
         <v>37</v>
       </c>
       <c r="F236" s="49" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G236" s="22" t="s">
         <v>48</v>
       </c>
       <c r="H236" s="36" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="I236" s="22" t="s">
         <v>335</v>
@@ -9047,7 +9050,7 @@
         <v>46267</v>
       </c>
       <c r="C237" s="49" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D237" s="26">
         <v>46267</v>
@@ -9062,10 +9065,10 @@
         <v>48</v>
       </c>
       <c r="H237" s="29" t="s">
+        <v>814</v>
+      </c>
+      <c r="I237" s="22" t="s">
         <v>815</v>
-      </c>
-      <c r="I237" s="22" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="238" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -9076,7 +9079,7 @@
         <v>46272</v>
       </c>
       <c r="C238" s="49" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D238" s="26">
         <v>46268</v>
@@ -9085,13 +9088,13 @@
         <v>319</v>
       </c>
       <c r="F238" s="49" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G238" s="22" t="s">
         <v>45</v>
       </c>
       <c r="H238" s="36" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I238" s="22" t="s">
         <v>50</v>
@@ -9109,7 +9112,7 @@
         <v>210</v>
       </c>
       <c r="H239" s="36" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I239" s="22" t="s">
         <v>50</v>
@@ -16462,7 +16465,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="129" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="129" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A129" s="27">
         <v>101</v>
       </c>
@@ -16494,7 +16497,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="130" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A130" s="27">
         <v>102</v>
       </c>
@@ -16526,7 +16529,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="131" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="131" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A131" s="27">
         <v>103</v>
       </c>
@@ -16555,7 +16558,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="132" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="132" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A132" s="27">
         <v>104</v>
       </c>
@@ -16587,7 +16590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="133" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="133" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A133" s="27">
         <v>105</v>
       </c>
@@ -16619,12 +16622,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="134" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A134" s="27">
         <v>106</v>
       </c>
-      <c r="B134" s="45" t="s">
-        <v>799</v>
+      <c r="B134" s="55">
+        <v>46269</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>40</v>
@@ -16636,30 +16639,30 @@
         <v>102</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G134" s="45" t="s">
         <v>47</v>
       </c>
       <c r="H134" s="45" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="I134" s="29" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="J134" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="135" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="135" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A135" s="27">
         <v>107</v>
       </c>
       <c r="B135" s="45" t="s">
+        <v>809</v>
+      </c>
+      <c r="C135" s="10" t="s">
         <v>810</v>
-      </c>
-      <c r="C135" s="10" t="s">
-        <v>811</v>
       </c>
       <c r="D135" s="55">
         <v>46272</v>
@@ -16677,19 +16680,22 @@
         <v>48</v>
       </c>
       <c r="I135" s="29" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J135" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="136" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="136" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A136" s="27">
         <v>108</v>
       </c>
       <c r="B136" s="55">
         <v>46272</v>
       </c>
+      <c r="C136" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="D136" s="55">
         <v>46272</v>
       </c>
@@ -16706,29 +16712,58 @@
         <v>48</v>
       </c>
       <c r="I136" s="29" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J136" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A137" s="27"/>
-      <c r="B137" s="45"/>
-      <c r="D137" s="45"/>
-      <c r="G137" s="45"/>
-      <c r="H137" s="45"/>
-      <c r="I137" s="29"/>
-    </row>
-    <row r="138" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A138" s="27"/>
+    <row r="137" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A137" s="27">
+        <v>109</v>
+      </c>
+      <c r="B137" s="55">
+        <v>46273</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D137" s="55">
+        <v>46273</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F137" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G137" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H137" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I137" s="29" t="s">
+        <v>821</v>
+      </c>
+      <c r="J137" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N137" s="10" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A138" s="27">
+        <v>110</v>
+      </c>
       <c r="B138" s="45"/>
       <c r="D138" s="45"/>
       <c r="G138" s="45"/>
       <c r="H138" s="45"/>
       <c r="I138" s="29"/>
     </row>
-    <row r="139" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="139" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A139" s="27"/>
       <c r="B139" s="45"/>
       <c r="D139" s="45"/>
@@ -16736,7 +16771,7 @@
       <c r="H139" s="45"/>
       <c r="I139" s="29"/>
     </row>
-    <row r="140" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="140" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A140" s="27"/>
       <c r="B140" s="45"/>
       <c r="D140" s="45"/>
@@ -16744,7 +16779,7 @@
       <c r="H140" s="45"/>
       <c r="I140" s="29"/>
     </row>
-    <row r="141" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="141" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A141" s="27"/>
       <c r="B141" s="45"/>
       <c r="D141" s="45"/>
@@ -16752,7 +16787,7 @@
       <c r="H141" s="45"/>
       <c r="I141" s="29"/>
     </row>
-    <row r="142" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="142" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A142" s="27"/>
       <c r="B142" s="45"/>
       <c r="D142" s="45"/>
@@ -16760,7 +16795,7 @@
       <c r="H142" s="45"/>
       <c r="I142" s="29"/>
     </row>
-    <row r="143" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="143" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A143" s="27"/>
       <c r="B143" s="45"/>
       <c r="D143" s="45"/>
@@ -16768,7 +16803,7 @@
       <c r="H143" s="45"/>
       <c r="I143" s="29"/>
     </row>
-    <row r="144" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="144" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A144" s="27"/>
       <c r="B144" s="45"/>
       <c r="D144" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156EEC9C-CAFD-4392-BDAC-4251C6DD2268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3085B7-6C7F-41D8-8BA0-E8A94142A2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="822">
   <si>
     <t>Sr No.</t>
   </si>
@@ -9104,7 +9104,15 @@
       <c r="A239" s="22">
         <v>181</v>
       </c>
-      <c r="C239" s="49"/>
+      <c r="B239" s="26">
+        <v>46272</v>
+      </c>
+      <c r="C239" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="E239" s="22" t="s">
+        <v>760</v>
+      </c>
       <c r="F239" s="49" t="s">
         <v>756</v>
       </c>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3085B7-6C7F-41D8-8BA0-E8A94142A2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFAA4E7-D621-4E78-9BF4-1F0A1F75C386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="829">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2487,6 +2487,27 @@
   </si>
   <si>
     <t xml:space="preserve"> Printer Cover Moulding -Qty 50 Nos. &amp; Cable 1 Nos.</t>
+  </si>
+  <si>
+    <t>AWB#K110900763</t>
+  </si>
+  <si>
+    <t>Photometer Halogen lamp assy Bioelab FA 6V/10W -Qty 20 Pcs</t>
+  </si>
+  <si>
+    <t>UC10 Regant / BarCoad 240</t>
+  </si>
+  <si>
+    <t>Challan No. 600054</t>
+  </si>
+  <si>
+    <t>Lamp  Holder - Qty 4 Nos. / Filter  Wheel - qty 4 Nos. / G4 Lamp Holder- Qty 4 Nos. / G4 Lamp( Specification 6V-10W)- Qty 4 Nos.</t>
+  </si>
+  <si>
+    <t>L26IN041209</t>
+  </si>
+  <si>
+    <t>Prt No. 824015- TVS Diode Array WE-TVS Sot23-6L 5V;2pF - Qty 20 Nos.</t>
   </si>
 </sst>
 </file>
@@ -9130,86 +9151,182 @@
       </c>
     </row>
     <row r="240" spans="1:10" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C240" s="49"/>
-      <c r="F240" s="49"/>
-      <c r="H240" s="36"/>
-    </row>
-    <row r="241" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C241" s="49"/>
-      <c r="F241" s="49"/>
-      <c r="H241" s="36"/>
-    </row>
-    <row r="242" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C242" s="49"/>
-      <c r="F242" s="49"/>
-      <c r="H242" s="36"/>
-    </row>
-    <row r="243" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C243" s="49"/>
-      <c r="F243" s="49"/>
-      <c r="H243" s="36"/>
-    </row>
-    <row r="244" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A240" s="22">
+        <v>182</v>
+      </c>
+      <c r="B240" s="26">
+        <v>46275</v>
+      </c>
+      <c r="C240" s="49" t="s">
+        <v>822</v>
+      </c>
+      <c r="D240" s="26">
+        <v>46272</v>
+      </c>
+      <c r="E240" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F240" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G240" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H240" s="36" t="s">
+        <v>823</v>
+      </c>
+      <c r="I240" s="22" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A241" s="22">
+        <v>183</v>
+      </c>
+      <c r="B241" s="58">
+        <v>46275</v>
+      </c>
+      <c r="C241" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D241" s="26">
+        <v>46275</v>
+      </c>
+      <c r="E241" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F241" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="G241" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H241" s="36" t="s">
+        <v>824</v>
+      </c>
+      <c r="I241" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A242" s="22">
+        <v>184</v>
+      </c>
+      <c r="B242" s="26">
+        <v>46275</v>
+      </c>
+      <c r="C242" s="49" t="s">
+        <v>825</v>
+      </c>
+      <c r="D242" s="26">
+        <v>46273</v>
+      </c>
+      <c r="E242" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F242" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="G242" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H242" s="36" t="s">
+        <v>826</v>
+      </c>
+      <c r="I242" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A243" s="22">
+        <v>185</v>
+      </c>
+      <c r="B243" s="26">
+        <v>46276</v>
+      </c>
+      <c r="C243" s="49" t="s">
+        <v>827</v>
+      </c>
+      <c r="D243" s="26">
+        <v>46275</v>
+      </c>
+      <c r="E243" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F243" s="49" t="s">
+        <v>289</v>
+      </c>
+      <c r="G243" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H243" s="36" t="s">
+        <v>828</v>
+      </c>
+      <c r="I243" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C244" s="49"/>
       <c r="F244" s="49"/>
       <c r="H244" s="36"/>
     </row>
-    <row r="245" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="245" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C245" s="49"/>
       <c r="F245" s="49"/>
       <c r="H245" s="36"/>
     </row>
-    <row r="246" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="246" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C246" s="49"/>
       <c r="F246" s="49"/>
       <c r="H246" s="36"/>
     </row>
-    <row r="247" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="247" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C247" s="49"/>
       <c r="F247" s="49"/>
       <c r="H247" s="36"/>
     </row>
-    <row r="248" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="248" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C248" s="49"/>
       <c r="F248" s="49"/>
       <c r="H248" s="36"/>
     </row>
-    <row r="249" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="249" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C249" s="49"/>
       <c r="F249" s="49"/>
       <c r="H249" s="36"/>
     </row>
-    <row r="250" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="250" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C250" s="49"/>
       <c r="F250" s="49"/>
       <c r="H250" s="36"/>
     </row>
-    <row r="251" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="251" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C251" s="49"/>
       <c r="F251" s="49"/>
       <c r="H251" s="36"/>
     </row>
-    <row r="252" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="252" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C252" s="49"/>
       <c r="F252" s="49"/>
       <c r="H252" s="36"/>
     </row>
-    <row r="253" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="253" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C253" s="49"/>
       <c r="F253" s="49"/>
       <c r="H253" s="36"/>
     </row>
-    <row r="254" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="254" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C254" s="49"/>
       <c r="F254" s="49"/>
       <c r="H254" s="36"/>
     </row>
-    <row r="255" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="255" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C255" s="49"/>
       <c r="F255" s="49"/>
       <c r="H255" s="36"/>
     </row>
-    <row r="256" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="256" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C256" s="49"/>
       <c r="F256" s="49"/>
       <c r="H256" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFAA4E7-D621-4E78-9BF4-1F0A1F75C386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C08C24-FF1C-4F0F-9205-8F262BFC4738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="837">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2508,6 +2508,30 @@
   </si>
   <si>
     <t>Prt No. 824015- TVS Diode Array WE-TVS Sot23-6L 5V;2pF - Qty 20 Nos.</t>
+  </si>
+  <si>
+    <t>MH-425685673-2627</t>
+  </si>
+  <si>
+    <t>ANYD Materials Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>Anyd Carbon Conducting Spray- Qty 1 Bottel</t>
+  </si>
+  <si>
+    <t>AWB#7X110902020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bioelab Cuvette For Fully Auto Biochemistry analyser - 100 Pcs. </t>
+  </si>
+  <si>
+    <t>Akshat Biomedical</t>
+  </si>
+  <si>
+    <t>W1000944050</t>
+  </si>
+  <si>
+    <t>Cuvett -Qty 300 Pcs. (40X7 &amp; 1x 20 )</t>
   </si>
 </sst>
 </file>
@@ -9267,19 +9291,91 @@
       </c>
     </row>
     <row r="244" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C244" s="49"/>
-      <c r="F244" s="49"/>
-      <c r="H244" s="36"/>
+      <c r="A244" s="22">
+        <v>186</v>
+      </c>
+      <c r="B244" s="26">
+        <v>46276</v>
+      </c>
+      <c r="C244" s="49" t="s">
+        <v>829</v>
+      </c>
+      <c r="D244" s="26">
+        <v>46273</v>
+      </c>
+      <c r="E244" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="F244" s="49" t="s">
+        <v>830</v>
+      </c>
+      <c r="G244" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H244" s="36" t="s">
+        <v>831</v>
+      </c>
+      <c r="I244" s="22" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="245" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C245" s="49"/>
-      <c r="F245" s="49"/>
-      <c r="H245" s="36"/>
+      <c r="A245" s="22">
+        <v>187</v>
+      </c>
+      <c r="B245" s="26">
+        <v>46276</v>
+      </c>
+      <c r="C245" s="49" t="s">
+        <v>832</v>
+      </c>
+      <c r="D245" s="26">
+        <v>46274</v>
+      </c>
+      <c r="E245" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F245" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G245" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H245" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="I245" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="246" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C246" s="49"/>
-      <c r="F246" s="49"/>
-      <c r="H246" s="36"/>
+      <c r="A246" s="22">
+        <v>188</v>
+      </c>
+      <c r="B246" s="26">
+        <v>46276</v>
+      </c>
+      <c r="C246" s="49" t="s">
+        <v>835</v>
+      </c>
+      <c r="D246" s="26">
+        <v>46276</v>
+      </c>
+      <c r="E246" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F246" s="49" t="s">
+        <v>834</v>
+      </c>
+      <c r="G246" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H246" s="36" t="s">
+        <v>836</v>
+      </c>
+      <c r="I246" s="22" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="247" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C247" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C08C24-FF1C-4F0F-9205-8F262BFC4738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F7848B-B527-4B14-A100-AB2D6722F590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="839">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2532,6 +2532,12 @@
   </si>
   <si>
     <t>Cuvett -Qty 300 Pcs. (40X7 &amp; 1x 20 )</t>
+  </si>
+  <si>
+    <t>AM/PP/0028/2627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamp House Assembly- Autochem Xpert- Qty 10 Nos </t>
   </si>
 </sst>
 </file>
@@ -16978,11 +16984,33 @@
       <c r="A138" s="27">
         <v>110</v>
       </c>
-      <c r="B138" s="45"/>
-      <c r="D138" s="45"/>
-      <c r="G138" s="45"/>
-      <c r="H138" s="45"/>
-      <c r="I138" s="29"/>
+      <c r="B138" s="55">
+        <v>46276</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="D138" s="55">
+        <v>46276</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G138" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H138" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I138" s="29" t="s">
+        <v>838</v>
+      </c>
+      <c r="J138" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="139" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A139" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F7848B-B527-4B14-A100-AB2D6722F590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2ACC7AE-1F38-4C6E-B6DB-3EBEEA7F645C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="844">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2538,6 +2538,21 @@
   </si>
   <si>
     <t xml:space="preserve">Lamp House Assembly- Autochem Xpert- Qty 10 Nos </t>
+  </si>
+  <si>
+    <t>386 kg</t>
+  </si>
+  <si>
+    <t>378 kg</t>
+  </si>
+  <si>
+    <t>NV50 Flowcell (PO:0290)- Qty 2 Nos. / Biosci 240 Lamp-6V assembly (PO:0307)- Qty 5 nos. / Wise Road- Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Nilesh Zsir</t>
+  </si>
+  <si>
+    <t>AM/PP?0029/2627</t>
   </si>
 </sst>
 </file>
@@ -17011,14 +17026,44 @@
       <c r="J138" s="10" t="s">
         <v>50</v>
       </c>
+      <c r="N138" s="10" t="s">
+        <v>839</v>
+      </c>
     </row>
     <row r="139" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A139" s="27"/>
-      <c r="B139" s="45"/>
-      <c r="D139" s="45"/>
-      <c r="G139" s="45"/>
-      <c r="H139" s="45"/>
-      <c r="I139" s="29"/>
+      <c r="A139" s="27">
+        <v>111</v>
+      </c>
+      <c r="B139" s="55">
+        <v>46276</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="D139" s="55">
+        <v>46276</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F139" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G139" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H139" s="45" t="s">
+        <v>842</v>
+      </c>
+      <c r="I139" s="29" t="s">
+        <v>841</v>
+      </c>
+      <c r="J139" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N139" s="10" t="s">
+        <v>840</v>
+      </c>
     </row>
     <row r="140" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A140" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2ACC7AE-1F38-4C6E-B6DB-3EBEEA7F645C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B4F1BE-9ABE-4937-9F80-1BC85D89B12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17066,7 +17066,9 @@
       </c>
     </row>
     <row r="140" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A140" s="27"/>
+      <c r="A140" s="27">
+        <v>112</v>
+      </c>
       <c r="B140" s="45"/>
       <c r="D140" s="45"/>
       <c r="G140" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B4F1BE-9ABE-4937-9F80-1BC85D89B12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08793F1E-7237-4B9C-AC5E-F1F5135B151D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="846">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2553,6 +2553,12 @@
   </si>
   <si>
     <t>AM/PP?0029/2627</t>
+  </si>
+  <si>
+    <t>M5001004798</t>
+  </si>
+  <si>
+    <t>W1-Sample Bottle</t>
   </si>
 </sst>
 </file>
@@ -9399,9 +9405,30 @@
       </c>
     </row>
     <row r="247" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C247" s="49"/>
-      <c r="F247" s="49"/>
-      <c r="H247" s="36"/>
+      <c r="A247" s="22">
+        <v>189</v>
+      </c>
+      <c r="B247" s="26">
+        <v>46276</v>
+      </c>
+      <c r="C247" s="49" t="s">
+        <v>844</v>
+      </c>
+      <c r="D247" s="26">
+        <v>46276</v>
+      </c>
+      <c r="E247" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F247" s="49" t="s">
+        <v>299</v>
+      </c>
+      <c r="G247" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H247" s="36" t="s">
+        <v>845</v>
+      </c>
     </row>
     <row r="248" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C248" s="49"/>
